--- a/translation_jobs_all_days.xlsx
+++ b/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AI$501</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AI$561</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI501"/>
+  <dimension ref="A1:AI561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -68540,8 +68540,8390 @@
         <v>4428</v>
       </c>
     </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2171</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F502" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H502" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I502" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J502" s="2" t="inlineStr">
+        <is>
+          <t>09:08:59.870</t>
+        </is>
+      </c>
+      <c r="K502" s="2" t="inlineStr">
+        <is>
+          <t>09:08:59.885</t>
+        </is>
+      </c>
+      <c r="L502" s="2" t="inlineStr">
+        <is>
+          <t>09:09:00.080</t>
+        </is>
+      </c>
+      <c r="M502" s="2" t="inlineStr">
+        <is>
+          <t>09:09:17.964</t>
+        </is>
+      </c>
+      <c r="N502" s="2" t="inlineStr">
+        <is>
+          <t>09:09:18.043</t>
+        </is>
+      </c>
+      <c r="O502" s="2" t="inlineStr">
+        <is>
+          <t>09:09:18.106</t>
+        </is>
+      </c>
+      <c r="P502" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q502" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R502" s="2" t="n">
+        <v>18094</v>
+      </c>
+      <c r="S502" s="2" t="inlineStr">
+        <is>
+          <t>18.1s</t>
+        </is>
+      </c>
+      <c r="T502" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="U502" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V502" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W502" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X502" s="2" t="n">
+        <v>18236</v>
+      </c>
+      <c r="Y502" s="2" t="inlineStr">
+        <is>
+          <t>18.2s</t>
+        </is>
+      </c>
+      <c r="Z502" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA502" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB502" s="2" t="inlineStr"/>
+      <c r="AC502" s="2" t="inlineStr"/>
+      <c r="AD502" s="2" t="inlineStr"/>
+      <c r="AE502" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF502" s="2" t="n">
+        <v>2507</v>
+      </c>
+      <c r="AG502" s="2" t="n">
+        <v>1042</v>
+      </c>
+      <c r="AH502" s="2" t="n">
+        <v>3549</v>
+      </c>
+      <c r="AI502" s="2" t="n">
+        <v>17424</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B503" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C503" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2172</t>
+        </is>
+      </c>
+      <c r="D503" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F503" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G503" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H503" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I503" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J503" s="2" t="inlineStr">
+        <is>
+          <t>09:48:13.470</t>
+        </is>
+      </c>
+      <c r="K503" s="2" t="inlineStr">
+        <is>
+          <t>09:48:13.491</t>
+        </is>
+      </c>
+      <c r="L503" s="2" t="inlineStr">
+        <is>
+          <t>09:48:13.786</t>
+        </is>
+      </c>
+      <c r="M503" s="2" t="inlineStr">
+        <is>
+          <t>09:48:25.106</t>
+        </is>
+      </c>
+      <c r="N503" s="2" t="inlineStr">
+        <is>
+          <t>09:48:25.163</t>
+        </is>
+      </c>
+      <c r="O503" s="2" t="inlineStr">
+        <is>
+          <t>09:48:25.225</t>
+        </is>
+      </c>
+      <c r="P503" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="Q503" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R503" s="2" t="n">
+        <v>11636</v>
+      </c>
+      <c r="S503" s="2" t="inlineStr">
+        <is>
+          <t>11.6s</t>
+        </is>
+      </c>
+      <c r="T503" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U503" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V503" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="W503" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X503" s="2" t="n">
+        <v>11755</v>
+      </c>
+      <c r="Y503" s="2" t="inlineStr">
+        <is>
+          <t>11.8s</t>
+        </is>
+      </c>
+      <c r="Z503" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA503" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB503" s="2" t="inlineStr"/>
+      <c r="AC503" s="2" t="inlineStr"/>
+      <c r="AD503" s="2" t="inlineStr"/>
+      <c r="AE503" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF503" s="2" t="n">
+        <v>1417</v>
+      </c>
+      <c r="AG503" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH503" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="AI503" s="2" t="n">
+        <v>10758</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2173</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G504" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H504" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I504" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J504" s="2" t="inlineStr">
+        <is>
+          <t>09:50:28.814</t>
+        </is>
+      </c>
+      <c r="K504" s="2" t="inlineStr">
+        <is>
+          <t>09:50:28.834</t>
+        </is>
+      </c>
+      <c r="L504" s="2" t="inlineStr">
+        <is>
+          <t>09:50:29.045</t>
+        </is>
+      </c>
+      <c r="M504" s="2" t="inlineStr">
+        <is>
+          <t>09:50:39.650</t>
+        </is>
+      </c>
+      <c r="N504" s="2" t="inlineStr">
+        <is>
+          <t>09:50:39.704</t>
+        </is>
+      </c>
+      <c r="O504" s="2" t="inlineStr">
+        <is>
+          <t>09:50:39.776</t>
+        </is>
+      </c>
+      <c r="P504" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="Q504" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R504" s="2" t="n">
+        <v>10836</v>
+      </c>
+      <c r="S504" s="2" t="inlineStr">
+        <is>
+          <t>10.8s</t>
+        </is>
+      </c>
+      <c r="T504" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U504" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V504" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="W504" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X504" s="2" t="n">
+        <v>10962</v>
+      </c>
+      <c r="Y504" s="2" t="inlineStr">
+        <is>
+          <t>11.0s</t>
+        </is>
+      </c>
+      <c r="Z504" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA504" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB504" s="2" t="inlineStr"/>
+      <c r="AC504" s="2" t="inlineStr"/>
+      <c r="AD504" s="2" t="inlineStr"/>
+      <c r="AE504" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF504" s="2" t="n">
+        <v>3301</v>
+      </c>
+      <c r="AG504" s="2" t="n">
+        <v>1818</v>
+      </c>
+      <c r="AH504" s="2" t="n">
+        <v>5119</v>
+      </c>
+      <c r="AI504" s="2" t="n">
+        <v>10028</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2174</t>
+        </is>
+      </c>
+      <c r="D505" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F505" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G505" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H505" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I505" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J505" s="2" t="inlineStr">
+        <is>
+          <t>10:44:33.223</t>
+        </is>
+      </c>
+      <c r="K505" s="2" t="inlineStr">
+        <is>
+          <t>10:44:33.243</t>
+        </is>
+      </c>
+      <c r="L505" s="2" t="inlineStr">
+        <is>
+          <t>10:44:33.777</t>
+        </is>
+      </c>
+      <c r="M505" s="2" t="inlineStr">
+        <is>
+          <t>10:44:40.463</t>
+        </is>
+      </c>
+      <c r="N505" s="2" t="inlineStr">
+        <is>
+          <t>10:44:40.521</t>
+        </is>
+      </c>
+      <c r="O505" s="2" t="inlineStr">
+        <is>
+          <t>10:44:40.643</t>
+        </is>
+      </c>
+      <c r="P505" s="2" t="n">
+        <v>534</v>
+      </c>
+      <c r="Q505" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R505" s="2" t="n">
+        <v>7240</v>
+      </c>
+      <c r="S505" s="2" t="inlineStr">
+        <is>
+          <t>7.2s</t>
+        </is>
+      </c>
+      <c r="T505" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U505" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V505" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="W505" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X505" s="2" t="n">
+        <v>7420</v>
+      </c>
+      <c r="Y505" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="Z505" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA505" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB505" s="2" t="inlineStr"/>
+      <c r="AC505" s="2" t="inlineStr"/>
+      <c r="AD505" s="2" t="inlineStr"/>
+      <c r="AE505" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF505" s="2" t="n">
+        <v>17796</v>
+      </c>
+      <c r="AG505" s="2" t="n">
+        <v>1851</v>
+      </c>
+      <c r="AH505" s="2" t="n">
+        <v>19647</v>
+      </c>
+      <c r="AI505" s="2" t="n">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2175</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H506" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I506" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J506" s="2" t="inlineStr">
+        <is>
+          <t>10:44:42.463</t>
+        </is>
+      </c>
+      <c r="K506" s="2" t="inlineStr">
+        <is>
+          <t>10:44:42.544</t>
+        </is>
+      </c>
+      <c r="L506" s="2" t="inlineStr">
+        <is>
+          <t>10:44:43.032</t>
+        </is>
+      </c>
+      <c r="M506" s="2" t="inlineStr">
+        <is>
+          <t>10:44:48.439</t>
+        </is>
+      </c>
+      <c r="N506" s="2" t="inlineStr">
+        <is>
+          <t>10:44:48.507</t>
+        </is>
+      </c>
+      <c r="O506" s="2" t="inlineStr">
+        <is>
+          <t>10:44:48.613</t>
+        </is>
+      </c>
+      <c r="P506" s="2" t="n">
+        <v>488</v>
+      </c>
+      <c r="Q506" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R506" s="2" t="n">
+        <v>5976</v>
+      </c>
+      <c r="S506" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="T506" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="U506" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V506" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="W506" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X506" s="2" t="n">
+        <v>6150</v>
+      </c>
+      <c r="Y506" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="Z506" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA506" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB506" s="2" t="inlineStr"/>
+      <c r="AC506" s="2" t="inlineStr"/>
+      <c r="AD506" s="2" t="inlineStr"/>
+      <c r="AE506" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF506" s="2" t="n">
+        <v>17796</v>
+      </c>
+      <c r="AG506" s="2" t="n">
+        <v>1851</v>
+      </c>
+      <c r="AH506" s="2" t="n">
+        <v>19647</v>
+      </c>
+      <c r="AI506" s="2" t="n">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2176</t>
+        </is>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F507" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G507" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H507" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I507" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J507" s="2" t="inlineStr">
+        <is>
+          <t>10:44:50.571</t>
+        </is>
+      </c>
+      <c r="K507" s="2" t="inlineStr">
+        <is>
+          <t>10:44:50.589</t>
+        </is>
+      </c>
+      <c r="L507" s="2" t="inlineStr">
+        <is>
+          <t>10:44:51.127</t>
+        </is>
+      </c>
+      <c r="M507" s="2" t="inlineStr">
+        <is>
+          <t>10:44:55.513</t>
+        </is>
+      </c>
+      <c r="N507" s="2" t="inlineStr">
+        <is>
+          <t>10:44:55.571</t>
+        </is>
+      </c>
+      <c r="O507" s="2" t="inlineStr">
+        <is>
+          <t>10:44:55.680</t>
+        </is>
+      </c>
+      <c r="P507" s="2" t="n">
+        <v>538</v>
+      </c>
+      <c r="Q507" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R507" s="2" t="n">
+        <v>4942</v>
+      </c>
+      <c r="S507" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="T507" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U507" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V507" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="W507" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X507" s="2" t="n">
+        <v>5109</v>
+      </c>
+      <c r="Y507" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="Z507" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA507" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB507" s="2" t="inlineStr"/>
+      <c r="AC507" s="2" t="inlineStr"/>
+      <c r="AD507" s="2" t="inlineStr"/>
+      <c r="AE507" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF507" s="2" t="n">
+        <v>17796</v>
+      </c>
+      <c r="AG507" s="2" t="n">
+        <v>1851</v>
+      </c>
+      <c r="AH507" s="2" t="n">
+        <v>19647</v>
+      </c>
+      <c r="AI507" s="2" t="n">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2177</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I508" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J508" s="2" t="inlineStr">
+        <is>
+          <t>10:44:57.824</t>
+        </is>
+      </c>
+      <c r="K508" s="2" t="inlineStr">
+        <is>
+          <t>10:44:57.847</t>
+        </is>
+      </c>
+      <c r="L508" s="2" t="inlineStr">
+        <is>
+          <t>10:44:58.215</t>
+        </is>
+      </c>
+      <c r="M508" s="2" t="inlineStr">
+        <is>
+          <t>10:45:05.864</t>
+        </is>
+      </c>
+      <c r="N508" s="2" t="inlineStr">
+        <is>
+          <t>10:45:05.923</t>
+        </is>
+      </c>
+      <c r="O508" s="2" t="inlineStr">
+        <is>
+          <t>10:45:06.049</t>
+        </is>
+      </c>
+      <c r="P508" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="Q508" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R508" s="2" t="n">
+        <v>8040</v>
+      </c>
+      <c r="S508" s="2" t="inlineStr">
+        <is>
+          <t>8.0s</t>
+        </is>
+      </c>
+      <c r="T508" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U508" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V508" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="W508" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X508" s="2" t="n">
+        <v>8225</v>
+      </c>
+      <c r="Y508" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="Z508" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA508" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB508" s="2" t="inlineStr"/>
+      <c r="AC508" s="2" t="inlineStr"/>
+      <c r="AD508" s="2" t="inlineStr"/>
+      <c r="AE508" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF508" s="2" t="n">
+        <v>17796</v>
+      </c>
+      <c r="AG508" s="2" t="n">
+        <v>1851</v>
+      </c>
+      <c r="AH508" s="2" t="n">
+        <v>19647</v>
+      </c>
+      <c r="AI508" s="2" t="n">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C509" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2178</t>
+        </is>
+      </c>
+      <c r="D509" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F509" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G509" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H509" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I509" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J509" s="2" t="inlineStr">
+        <is>
+          <t>10:45:08.057</t>
+        </is>
+      </c>
+      <c r="K509" s="2" t="inlineStr">
+        <is>
+          <t>10:45:08.074</t>
+        </is>
+      </c>
+      <c r="L509" s="2" t="inlineStr">
+        <is>
+          <t>10:45:08.564</t>
+        </is>
+      </c>
+      <c r="M509" s="2" t="inlineStr">
+        <is>
+          <t>10:45:13.829</t>
+        </is>
+      </c>
+      <c r="N509" s="2" t="inlineStr">
+        <is>
+          <t>10:45:13.898</t>
+        </is>
+      </c>
+      <c r="O509" s="2" t="inlineStr">
+        <is>
+          <t>10:45:14.066</t>
+        </is>
+      </c>
+      <c r="P509" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="Q509" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R509" s="2" t="n">
+        <v>5772</v>
+      </c>
+      <c r="S509" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="T509" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="U509" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V509" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="W509" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X509" s="2" t="n">
+        <v>6009</v>
+      </c>
+      <c r="Y509" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="Z509" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA509" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB509" s="2" t="inlineStr"/>
+      <c r="AC509" s="2" t="inlineStr"/>
+      <c r="AD509" s="2" t="inlineStr"/>
+      <c r="AE509" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF509" s="2" t="n">
+        <v>17796</v>
+      </c>
+      <c r="AG509" s="2" t="n">
+        <v>1851</v>
+      </c>
+      <c r="AH509" s="2" t="n">
+        <v>19647</v>
+      </c>
+      <c r="AI509" s="2" t="n">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2179</t>
+        </is>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H510" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I510" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J510" s="2" t="inlineStr">
+        <is>
+          <t>10:45:15.916</t>
+        </is>
+      </c>
+      <c r="K510" s="2" t="inlineStr">
+        <is>
+          <t>10:45:15.934</t>
+        </is>
+      </c>
+      <c r="L510" s="2" t="inlineStr">
+        <is>
+          <t>10:45:16.344</t>
+        </is>
+      </c>
+      <c r="M510" s="2" t="inlineStr">
+        <is>
+          <t>10:45:22.852</t>
+        </is>
+      </c>
+      <c r="N510" s="2" t="inlineStr">
+        <is>
+          <t>10:45:22.903</t>
+        </is>
+      </c>
+      <c r="O510" s="2" t="inlineStr">
+        <is>
+          <t>10:45:23.013</t>
+        </is>
+      </c>
+      <c r="P510" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="Q510" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R510" s="2" t="n">
+        <v>6936</v>
+      </c>
+      <c r="S510" s="2" t="inlineStr">
+        <is>
+          <t>6.9s</t>
+        </is>
+      </c>
+      <c r="T510" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U510" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V510" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="W510" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X510" s="2" t="n">
+        <v>7097</v>
+      </c>
+      <c r="Y510" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="Z510" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA510" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB510" s="2" t="inlineStr"/>
+      <c r="AC510" s="2" t="inlineStr"/>
+      <c r="AD510" s="2" t="inlineStr"/>
+      <c r="AE510" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF510" s="2" t="n">
+        <v>17796</v>
+      </c>
+      <c r="AG510" s="2" t="n">
+        <v>1851</v>
+      </c>
+      <c r="AH510" s="2" t="n">
+        <v>19647</v>
+      </c>
+      <c r="AI510" s="2" t="n">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C511" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1151</t>
+        </is>
+      </c>
+      <c r="D511" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F511" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G511" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H511" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I511" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J511" s="2" t="inlineStr">
+        <is>
+          <t>11:18:07.453</t>
+        </is>
+      </c>
+      <c r="K511" s="2" t="inlineStr">
+        <is>
+          <t>11:18:07.476</t>
+        </is>
+      </c>
+      <c r="L511" s="2" t="inlineStr">
+        <is>
+          <t>11:18:07.830</t>
+        </is>
+      </c>
+      <c r="M511" s="2" t="inlineStr">
+        <is>
+          <t>11:18:29.882</t>
+        </is>
+      </c>
+      <c r="N511" s="2" t="inlineStr">
+        <is>
+          <t>11:18:29.940</t>
+        </is>
+      </c>
+      <c r="O511" s="2" t="inlineStr">
+        <is>
+          <t>11:18:30.023</t>
+        </is>
+      </c>
+      <c r="P511" s="2" t="n">
+        <v>354</v>
+      </c>
+      <c r="Q511" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R511" s="2" t="n">
+        <v>22429</v>
+      </c>
+      <c r="S511" s="2" t="inlineStr">
+        <is>
+          <t>22.4s</t>
+        </is>
+      </c>
+      <c r="T511" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U511" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V511" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="W511" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X511" s="2" t="n">
+        <v>22570</v>
+      </c>
+      <c r="Y511" s="2" t="inlineStr">
+        <is>
+          <t>22.6s</t>
+        </is>
+      </c>
+      <c r="Z511" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA511" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB511" s="2" t="inlineStr"/>
+      <c r="AC511" s="2" t="inlineStr"/>
+      <c r="AD511" s="2" t="inlineStr"/>
+      <c r="AE511" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF511" s="2" t="n">
+        <v>8499</v>
+      </c>
+      <c r="AG511" s="2" t="n">
+        <v>438</v>
+      </c>
+      <c r="AH511" s="2" t="n">
+        <v>8937</v>
+      </c>
+      <c r="AI511" s="2" t="n">
+        <v>5142</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1152</t>
+        </is>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G512" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I512" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J512" s="2" t="inlineStr">
+        <is>
+          <t>11:18:31.141</t>
+        </is>
+      </c>
+      <c r="K512" s="2" t="inlineStr">
+        <is>
+          <t>11:18:31.160</t>
+        </is>
+      </c>
+      <c r="L512" s="2" t="inlineStr">
+        <is>
+          <t>11:18:31.393</t>
+        </is>
+      </c>
+      <c r="M512" s="2" t="inlineStr">
+        <is>
+          <t>11:18:34.614</t>
+        </is>
+      </c>
+      <c r="N512" s="2" t="inlineStr">
+        <is>
+          <t>11:18:34.676</t>
+        </is>
+      </c>
+      <c r="O512" s="2" t="inlineStr">
+        <is>
+          <t>11:18:34.751</t>
+        </is>
+      </c>
+      <c r="P512" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="Q512" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R512" s="2" t="n">
+        <v>3473</v>
+      </c>
+      <c r="S512" s="2" t="inlineStr">
+        <is>
+          <t>3.5s</t>
+        </is>
+      </c>
+      <c r="T512" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U512" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V512" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W512" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X512" s="2" t="n">
+        <v>3610</v>
+      </c>
+      <c r="Y512" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="Z512" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA512" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB512" s="2" t="inlineStr"/>
+      <c r="AC512" s="2" t="inlineStr"/>
+      <c r="AD512" s="2" t="inlineStr"/>
+      <c r="AE512" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF512" s="2" t="n">
+        <v>8499</v>
+      </c>
+      <c r="AG512" s="2" t="n">
+        <v>438</v>
+      </c>
+      <c r="AH512" s="2" t="n">
+        <v>8937</v>
+      </c>
+      <c r="AI512" s="2" t="n">
+        <v>5142</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1153</t>
+        </is>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F513" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G513" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H513" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I513" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J513" s="2" t="inlineStr">
+        <is>
+          <t>11:18:35.861</t>
+        </is>
+      </c>
+      <c r="K513" s="2" t="inlineStr">
+        <is>
+          <t>11:18:35.889</t>
+        </is>
+      </c>
+      <c r="L513" s="2" t="inlineStr">
+        <is>
+          <t>11:18:36.127</t>
+        </is>
+      </c>
+      <c r="M513" s="2" t="inlineStr">
+        <is>
+          <t>11:18:37.780</t>
+        </is>
+      </c>
+      <c r="N513" s="2" t="inlineStr">
+        <is>
+          <t>11:18:37.836</t>
+        </is>
+      </c>
+      <c r="O513" s="2" t="inlineStr">
+        <is>
+          <t>11:18:37.894</t>
+        </is>
+      </c>
+      <c r="P513" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q513" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R513" s="2" t="n">
+        <v>1919</v>
+      </c>
+      <c r="S513" s="2" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="T513" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U513" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V513" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W513" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X513" s="2" t="n">
+        <v>2033</v>
+      </c>
+      <c r="Y513" s="2" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="Z513" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA513" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB513" s="2" t="inlineStr"/>
+      <c r="AC513" s="2" t="inlineStr"/>
+      <c r="AD513" s="2" t="inlineStr"/>
+      <c r="AE513" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF513" s="2" t="n">
+        <v>8499</v>
+      </c>
+      <c r="AG513" s="2" t="n">
+        <v>438</v>
+      </c>
+      <c r="AH513" s="2" t="n">
+        <v>8937</v>
+      </c>
+      <c r="AI513" s="2" t="n">
+        <v>5142</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1154</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G514" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H514" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I514" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J514" s="2" t="inlineStr">
+        <is>
+          <t>11:18:39.068</t>
+        </is>
+      </c>
+      <c r="K514" s="2" t="inlineStr">
+        <is>
+          <t>11:18:39.087</t>
+        </is>
+      </c>
+      <c r="L514" s="2" t="inlineStr">
+        <is>
+          <t>11:18:39.577</t>
+        </is>
+      </c>
+      <c r="M514" s="2" t="inlineStr">
+        <is>
+          <t>11:18:42.692</t>
+        </is>
+      </c>
+      <c r="N514" s="2" t="inlineStr">
+        <is>
+          <t>11:18:42.755</t>
+        </is>
+      </c>
+      <c r="O514" s="2" t="inlineStr">
+        <is>
+          <t>11:18:42.828</t>
+        </is>
+      </c>
+      <c r="P514" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="Q514" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R514" s="2" t="n">
+        <v>3624</v>
+      </c>
+      <c r="S514" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="T514" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U514" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V514" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="W514" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X514" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="Y514" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="Z514" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA514" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB514" s="2" t="inlineStr"/>
+      <c r="AC514" s="2" t="inlineStr"/>
+      <c r="AD514" s="2" t="inlineStr"/>
+      <c r="AE514" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF514" s="2" t="n">
+        <v>8499</v>
+      </c>
+      <c r="AG514" s="2" t="n">
+        <v>438</v>
+      </c>
+      <c r="AH514" s="2" t="n">
+        <v>8937</v>
+      </c>
+      <c r="AI514" s="2" t="n">
+        <v>5142</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B515" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C515" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1155</t>
+        </is>
+      </c>
+      <c r="D515" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F515" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G515" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H515" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I515" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J515" s="2" t="inlineStr">
+        <is>
+          <t>11:18:43.983</t>
+        </is>
+      </c>
+      <c r="K515" s="2" t="inlineStr">
+        <is>
+          <t>11:18:44.003</t>
+        </is>
+      </c>
+      <c r="L515" s="2" t="inlineStr">
+        <is>
+          <t>11:18:44.260</t>
+        </is>
+      </c>
+      <c r="M515" s="2" t="inlineStr">
+        <is>
+          <t>11:18:46.605</t>
+        </is>
+      </c>
+      <c r="N515" s="2" t="inlineStr">
+        <is>
+          <t>11:18:46.668</t>
+        </is>
+      </c>
+      <c r="O515" s="2" t="inlineStr">
+        <is>
+          <t>11:18:46.734</t>
+        </is>
+      </c>
+      <c r="P515" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q515" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R515" s="2" t="n">
+        <v>2622</v>
+      </c>
+      <c r="S515" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="T515" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U515" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V515" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="W515" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X515" s="2" t="n">
+        <v>2751</v>
+      </c>
+      <c r="Y515" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="Z515" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA515" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB515" s="2" t="inlineStr"/>
+      <c r="AC515" s="2" t="inlineStr"/>
+      <c r="AD515" s="2" t="inlineStr"/>
+      <c r="AE515" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF515" s="2" t="n">
+        <v>8499</v>
+      </c>
+      <c r="AG515" s="2" t="n">
+        <v>438</v>
+      </c>
+      <c r="AH515" s="2" t="n">
+        <v>8937</v>
+      </c>
+      <c r="AI515" s="2" t="n">
+        <v>5142</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1156</t>
+        </is>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G516" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H516" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I516" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J516" s="2" t="inlineStr">
+        <is>
+          <t>11:18:47.907</t>
+        </is>
+      </c>
+      <c r="K516" s="2" t="inlineStr">
+        <is>
+          <t>11:18:47.937</t>
+        </is>
+      </c>
+      <c r="L516" s="2" t="inlineStr">
+        <is>
+          <t>11:18:48.347</t>
+        </is>
+      </c>
+      <c r="M516" s="2" t="inlineStr">
+        <is>
+          <t>11:18:50.700</t>
+        </is>
+      </c>
+      <c r="N516" s="2" t="inlineStr">
+        <is>
+          <t>11:18:50.761</t>
+        </is>
+      </c>
+      <c r="O516" s="2" t="inlineStr">
+        <is>
+          <t>11:18:50.829</t>
+        </is>
+      </c>
+      <c r="P516" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="Q516" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R516" s="2" t="n">
+        <v>2793</v>
+      </c>
+      <c r="S516" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="T516" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U516" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V516" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="W516" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X516" s="2" t="n">
+        <v>2922</v>
+      </c>
+      <c r="Y516" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="Z516" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA516" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB516" s="2" t="inlineStr"/>
+      <c r="AC516" s="2" t="inlineStr"/>
+      <c r="AD516" s="2" t="inlineStr"/>
+      <c r="AE516" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF516" s="2" t="n">
+        <v>8499</v>
+      </c>
+      <c r="AG516" s="2" t="n">
+        <v>438</v>
+      </c>
+      <c r="AH516" s="2" t="n">
+        <v>8937</v>
+      </c>
+      <c r="AI516" s="2" t="n">
+        <v>5142</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B517" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C517" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2180</t>
+        </is>
+      </c>
+      <c r="D517" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F517" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G517" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H517" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I517" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J517" s="2" t="inlineStr">
+        <is>
+          <t>11:30:49.968</t>
+        </is>
+      </c>
+      <c r="K517" s="2" t="inlineStr">
+        <is>
+          <t>11:30:49.986</t>
+        </is>
+      </c>
+      <c r="L517" s="2" t="inlineStr">
+        <is>
+          <t>11:30:50.244</t>
+        </is>
+      </c>
+      <c r="M517" s="2" t="inlineStr">
+        <is>
+          <t>11:30:54.210</t>
+        </is>
+      </c>
+      <c r="N517" s="2" t="inlineStr">
+        <is>
+          <t>11:30:54.267</t>
+        </is>
+      </c>
+      <c r="O517" s="2" t="inlineStr">
+        <is>
+          <t>11:30:54.330</t>
+        </is>
+      </c>
+      <c r="P517" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="Q517" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R517" s="2" t="n">
+        <v>4242</v>
+      </c>
+      <c r="S517" s="2" t="inlineStr">
+        <is>
+          <t>4.2s</t>
+        </is>
+      </c>
+      <c r="T517" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="U517" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V517" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W517" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X517" s="2" t="n">
+        <v>4362</v>
+      </c>
+      <c r="Y517" s="2" t="inlineStr">
+        <is>
+          <t>4.4s</t>
+        </is>
+      </c>
+      <c r="Z517" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA517" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB517" s="2" t="inlineStr"/>
+      <c r="AC517" s="2" t="inlineStr"/>
+      <c r="AD517" s="2" t="inlineStr"/>
+      <c r="AE517" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF517" s="2" t="n">
+        <v>9897</v>
+      </c>
+      <c r="AG517" s="2" t="n">
+        <v>2059</v>
+      </c>
+      <c r="AH517" s="2" t="n">
+        <v>11956</v>
+      </c>
+      <c r="AI517" s="2" t="n">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2181</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G518" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H518" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I518" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J518" s="2" t="inlineStr">
+        <is>
+          <t>11:30:55.977</t>
+        </is>
+      </c>
+      <c r="K518" s="2" t="inlineStr">
+        <is>
+          <t>11:30:55.996</t>
+        </is>
+      </c>
+      <c r="L518" s="2" t="inlineStr">
+        <is>
+          <t>11:30:56.225</t>
+        </is>
+      </c>
+      <c r="M518" s="2" t="inlineStr">
+        <is>
+          <t>11:31:00.606</t>
+        </is>
+      </c>
+      <c r="N518" s="2" t="inlineStr">
+        <is>
+          <t>11:31:00.670</t>
+        </is>
+      </c>
+      <c r="O518" s="2" t="inlineStr">
+        <is>
+          <t>11:31:00.748</t>
+        </is>
+      </c>
+      <c r="P518" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q518" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R518" s="2" t="n">
+        <v>4629</v>
+      </c>
+      <c r="S518" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="T518" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U518" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V518" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="W518" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X518" s="2" t="n">
+        <v>4771</v>
+      </c>
+      <c r="Y518" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="Z518" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA518" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB518" s="2" t="inlineStr"/>
+      <c r="AC518" s="2" t="inlineStr"/>
+      <c r="AD518" s="2" t="inlineStr"/>
+      <c r="AE518" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF518" s="2" t="n">
+        <v>9897</v>
+      </c>
+      <c r="AG518" s="2" t="n">
+        <v>2059</v>
+      </c>
+      <c r="AH518" s="2" t="n">
+        <v>11956</v>
+      </c>
+      <c r="AI518" s="2" t="n">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C519" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2182</t>
+        </is>
+      </c>
+      <c r="D519" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E519" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F519" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G519" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H519" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I519" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J519" s="2" t="inlineStr">
+        <is>
+          <t>11:31:02.671</t>
+        </is>
+      </c>
+      <c r="K519" s="2" t="inlineStr">
+        <is>
+          <t>11:31:02.688</t>
+        </is>
+      </c>
+      <c r="L519" s="2" t="inlineStr">
+        <is>
+          <t>11:31:02.916</t>
+        </is>
+      </c>
+      <c r="M519" s="2" t="inlineStr">
+        <is>
+          <t>11:31:06.229</t>
+        </is>
+      </c>
+      <c r="N519" s="2" t="inlineStr">
+        <is>
+          <t>11:31:06.307</t>
+        </is>
+      </c>
+      <c r="O519" s="2" t="inlineStr">
+        <is>
+          <t>11:31:06.441</t>
+        </is>
+      </c>
+      <c r="P519" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q519" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R519" s="2" t="n">
+        <v>3558</v>
+      </c>
+      <c r="S519" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="T519" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="U519" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V519" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="W519" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X519" s="2" t="n">
+        <v>3770</v>
+      </c>
+      <c r="Y519" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="Z519" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA519" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB519" s="2" t="inlineStr"/>
+      <c r="AC519" s="2" t="inlineStr"/>
+      <c r="AD519" s="2" t="inlineStr"/>
+      <c r="AE519" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF519" s="2" t="n">
+        <v>9897</v>
+      </c>
+      <c r="AG519" s="2" t="n">
+        <v>2059</v>
+      </c>
+      <c r="AH519" s="2" t="n">
+        <v>11956</v>
+      </c>
+      <c r="AI519" s="2" t="n">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2183</t>
+        </is>
+      </c>
+      <c r="D520" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F520" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G520" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H520" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I520" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J520" s="2" t="inlineStr">
+        <is>
+          <t>11:31:08.367</t>
+        </is>
+      </c>
+      <c r="K520" s="2" t="inlineStr">
+        <is>
+          <t>11:31:08.384</t>
+        </is>
+      </c>
+      <c r="L520" s="2" t="inlineStr">
+        <is>
+          <t>11:31:08.611</t>
+        </is>
+      </c>
+      <c r="M520" s="2" t="inlineStr">
+        <is>
+          <t>11:31:14.764</t>
+        </is>
+      </c>
+      <c r="N520" s="2" t="inlineStr">
+        <is>
+          <t>11:31:14.823</t>
+        </is>
+      </c>
+      <c r="O520" s="2" t="inlineStr">
+        <is>
+          <t>11:31:14.908</t>
+        </is>
+      </c>
+      <c r="P520" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="Q520" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R520" s="2" t="n">
+        <v>6397</v>
+      </c>
+      <c r="S520" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="T520" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U520" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V520" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="W520" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X520" s="2" t="n">
+        <v>6541</v>
+      </c>
+      <c r="Y520" s="2" t="inlineStr">
+        <is>
+          <t>6.5s</t>
+        </is>
+      </c>
+      <c r="Z520" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA520" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB520" s="2" t="inlineStr"/>
+      <c r="AC520" s="2" t="inlineStr"/>
+      <c r="AD520" s="2" t="inlineStr"/>
+      <c r="AE520" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF520" s="2" t="n">
+        <v>9897</v>
+      </c>
+      <c r="AG520" s="2" t="n">
+        <v>2059</v>
+      </c>
+      <c r="AH520" s="2" t="n">
+        <v>11956</v>
+      </c>
+      <c r="AI520" s="2" t="n">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B521" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C521" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2184</t>
+        </is>
+      </c>
+      <c r="D521" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E521" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F521" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G521" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H521" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I521" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J521" s="2" t="inlineStr">
+        <is>
+          <t>11:31:16.911</t>
+        </is>
+      </c>
+      <c r="K521" s="2" t="inlineStr">
+        <is>
+          <t>11:31:16.933</t>
+        </is>
+      </c>
+      <c r="L521" s="2" t="inlineStr">
+        <is>
+          <t>11:31:18.013</t>
+        </is>
+      </c>
+      <c r="M521" s="2" t="inlineStr">
+        <is>
+          <t>11:31:21.862</t>
+        </is>
+      </c>
+      <c r="N521" s="2" t="inlineStr">
+        <is>
+          <t>11:31:21.921</t>
+        </is>
+      </c>
+      <c r="O521" s="2" t="inlineStr">
+        <is>
+          <t>11:31:21.996</t>
+        </is>
+      </c>
+      <c r="P521" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="Q521" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R521" s="2" t="n">
+        <v>4951</v>
+      </c>
+      <c r="S521" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="T521" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U521" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V521" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W521" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X521" s="2" t="n">
+        <v>5085</v>
+      </c>
+      <c r="Y521" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="Z521" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA521" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB521" s="2" t="inlineStr"/>
+      <c r="AC521" s="2" t="inlineStr"/>
+      <c r="AD521" s="2" t="inlineStr"/>
+      <c r="AE521" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF521" s="2" t="n">
+        <v>9897</v>
+      </c>
+      <c r="AG521" s="2" t="n">
+        <v>2059</v>
+      </c>
+      <c r="AH521" s="2" t="n">
+        <v>11956</v>
+      </c>
+      <c r="AI521" s="2" t="n">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2185</t>
+        </is>
+      </c>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F522" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G522" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H522" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I522" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J522" s="2" t="inlineStr">
+        <is>
+          <t>11:31:23.979</t>
+        </is>
+      </c>
+      <c r="K522" s="2" t="inlineStr">
+        <is>
+          <t>11:31:23.996</t>
+        </is>
+      </c>
+      <c r="L522" s="2" t="inlineStr">
+        <is>
+          <t>11:31:24.231</t>
+        </is>
+      </c>
+      <c r="M522" s="2" t="inlineStr">
+        <is>
+          <t>11:31:31.140</t>
+        </is>
+      </c>
+      <c r="N522" s="2" t="inlineStr">
+        <is>
+          <t>11:31:31.208</t>
+        </is>
+      </c>
+      <c r="O522" s="2" t="inlineStr">
+        <is>
+          <t>11:31:31.304</t>
+        </is>
+      </c>
+      <c r="P522" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="Q522" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R522" s="2" t="n">
+        <v>7161</v>
+      </c>
+      <c r="S522" s="2" t="inlineStr">
+        <is>
+          <t>7.2s</t>
+        </is>
+      </c>
+      <c r="T522" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="U522" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V522" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="W522" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X522" s="2" t="n">
+        <v>7325</v>
+      </c>
+      <c r="Y522" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="Z522" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA522" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB522" s="2" t="inlineStr"/>
+      <c r="AC522" s="2" t="inlineStr"/>
+      <c r="AD522" s="2" t="inlineStr"/>
+      <c r="AE522" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF522" s="2" t="n">
+        <v>9897</v>
+      </c>
+      <c r="AG522" s="2" t="n">
+        <v>2059</v>
+      </c>
+      <c r="AH522" s="2" t="n">
+        <v>11956</v>
+      </c>
+      <c r="AI522" s="2" t="n">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B523" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C523" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1837</t>
+        </is>
+      </c>
+      <c r="D523" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F523" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G523" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H523" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I523" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J523" s="2" t="inlineStr">
+        <is>
+          <t>17:11:57.622</t>
+        </is>
+      </c>
+      <c r="K523" s="2" t="inlineStr">
+        <is>
+          <t>17:12:02.269</t>
+        </is>
+      </c>
+      <c r="L523" s="2" t="inlineStr">
+        <is>
+          <t>17:12:02.335</t>
+        </is>
+      </c>
+      <c r="M523" s="2" t="inlineStr">
+        <is>
+          <t>17:12:06.969</t>
+        </is>
+      </c>
+      <c r="N523" s="2" t="inlineStr">
+        <is>
+          <t>17:12:07.056</t>
+        </is>
+      </c>
+      <c r="O523" s="2" t="inlineStr">
+        <is>
+          <t>17:12:07.151</t>
+        </is>
+      </c>
+      <c r="P523" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q523" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="R523" s="2" t="n">
+        <v>9347</v>
+      </c>
+      <c r="S523" s="2" t="inlineStr">
+        <is>
+          <t>9.3s</t>
+        </is>
+      </c>
+      <c r="T523" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="U523" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V523" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="W523" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X523" s="2" t="n">
+        <v>9529</v>
+      </c>
+      <c r="Y523" s="2" t="inlineStr">
+        <is>
+          <t>9.5s</t>
+        </is>
+      </c>
+      <c r="Z523" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA523" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB523" s="2" t="inlineStr"/>
+      <c r="AC523" s="2" t="inlineStr"/>
+      <c r="AD523" s="2" t="inlineStr"/>
+      <c r="AE523" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF523" s="2" t="n">
+        <v>5773</v>
+      </c>
+      <c r="AG523" s="2" t="n">
+        <v>2108</v>
+      </c>
+      <c r="AH523" s="2" t="n">
+        <v>7881</v>
+      </c>
+      <c r="AI523" s="2" t="n">
+        <v>7378</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1838</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F524" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G524" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H524" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I524" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J524" s="2" t="inlineStr">
+        <is>
+          <t>17:12:04.874</t>
+        </is>
+      </c>
+      <c r="K524" s="2" t="inlineStr">
+        <is>
+          <t>17:12:04.895</t>
+        </is>
+      </c>
+      <c r="L524" s="2" t="inlineStr">
+        <is>
+          <t>17:12:05.162</t>
+        </is>
+      </c>
+      <c r="M524" s="2" t="inlineStr">
+        <is>
+          <t>17:12:09.460</t>
+        </is>
+      </c>
+      <c r="N524" s="2" t="inlineStr">
+        <is>
+          <t>17:12:09.562</t>
+        </is>
+      </c>
+      <c r="O524" s="2" t="inlineStr">
+        <is>
+          <t>17:12:09.654</t>
+        </is>
+      </c>
+      <c r="P524" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="Q524" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R524" s="2" t="n">
+        <v>4586</v>
+      </c>
+      <c r="S524" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="T524" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="U524" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V524" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="W524" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X524" s="2" t="n">
+        <v>4780</v>
+      </c>
+      <c r="Y524" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="Z524" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA524" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB524" s="2" t="inlineStr"/>
+      <c r="AC524" s="2" t="inlineStr"/>
+      <c r="AD524" s="2" t="inlineStr"/>
+      <c r="AE524" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF524" s="2" t="n">
+        <v>5773</v>
+      </c>
+      <c r="AG524" s="2" t="n">
+        <v>2108</v>
+      </c>
+      <c r="AH524" s="2" t="n">
+        <v>7881</v>
+      </c>
+      <c r="AI524" s="2" t="n">
+        <v>7378</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B525" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C525" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1839</t>
+        </is>
+      </c>
+      <c r="D525" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F525" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G525" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H525" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I525" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J525" s="2" t="inlineStr">
+        <is>
+          <t>17:12:12.579</t>
+        </is>
+      </c>
+      <c r="K525" s="2" t="inlineStr">
+        <is>
+          <t>17:12:12.656</t>
+        </is>
+      </c>
+      <c r="L525" s="2" t="inlineStr">
+        <is>
+          <t>17:12:13.465</t>
+        </is>
+      </c>
+      <c r="M525" s="2" t="inlineStr">
+        <is>
+          <t>17:12:20.067</t>
+        </is>
+      </c>
+      <c r="N525" s="2" t="inlineStr">
+        <is>
+          <t>17:12:20.138</t>
+        </is>
+      </c>
+      <c r="O525" s="2" t="inlineStr">
+        <is>
+          <t>17:12:20.234</t>
+        </is>
+      </c>
+      <c r="P525" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="Q525" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R525" s="2" t="n">
+        <v>7488</v>
+      </c>
+      <c r="S525" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="T525" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="U525" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V525" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="W525" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X525" s="2" t="n">
+        <v>7655</v>
+      </c>
+      <c r="Y525" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="Z525" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA525" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB525" s="2" t="inlineStr"/>
+      <c r="AC525" s="2" t="inlineStr"/>
+      <c r="AD525" s="2" t="inlineStr"/>
+      <c r="AE525" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF525" s="2" t="n">
+        <v>5773</v>
+      </c>
+      <c r="AG525" s="2" t="n">
+        <v>2108</v>
+      </c>
+      <c r="AH525" s="2" t="n">
+        <v>7881</v>
+      </c>
+      <c r="AI525" s="2" t="n">
+        <v>7378</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1840</t>
+        </is>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F526" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G526" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H526" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I526" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J526" s="2" t="inlineStr">
+        <is>
+          <t>17:12:15.789</t>
+        </is>
+      </c>
+      <c r="K526" s="2" t="inlineStr">
+        <is>
+          <t>17:12:15.813</t>
+        </is>
+      </c>
+      <c r="L526" s="2" t="inlineStr">
+        <is>
+          <t>17:12:16.120</t>
+        </is>
+      </c>
+      <c r="M526" s="2" t="inlineStr">
+        <is>
+          <t>17:12:24.798</t>
+        </is>
+      </c>
+      <c r="N526" s="2" t="inlineStr">
+        <is>
+          <t>17:12:24.915</t>
+        </is>
+      </c>
+      <c r="O526" s="2" t="inlineStr">
+        <is>
+          <t>17:12:24.994</t>
+        </is>
+      </c>
+      <c r="P526" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="Q526" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R526" s="2" t="n">
+        <v>9009</v>
+      </c>
+      <c r="S526" s="2" t="inlineStr">
+        <is>
+          <t>9.0s</t>
+        </is>
+      </c>
+      <c r="T526" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="U526" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V526" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="W526" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X526" s="2" t="n">
+        <v>9205</v>
+      </c>
+      <c r="Y526" s="2" t="inlineStr">
+        <is>
+          <t>9.2s</t>
+        </is>
+      </c>
+      <c r="Z526" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA526" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB526" s="2" t="inlineStr"/>
+      <c r="AC526" s="2" t="inlineStr"/>
+      <c r="AD526" s="2" t="inlineStr"/>
+      <c r="AE526" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF526" s="2" t="n">
+        <v>5773</v>
+      </c>
+      <c r="AG526" s="2" t="n">
+        <v>2108</v>
+      </c>
+      <c r="AH526" s="2" t="n">
+        <v>7881</v>
+      </c>
+      <c r="AI526" s="2" t="n">
+        <v>7378</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B527" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1841</t>
+        </is>
+      </c>
+      <c r="D527" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F527" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G527" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H527" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I527" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J527" s="2" t="inlineStr">
+        <is>
+          <t>17:12:22.187</t>
+        </is>
+      </c>
+      <c r="K527" s="2" t="inlineStr">
+        <is>
+          <t>17:12:22.210</t>
+        </is>
+      </c>
+      <c r="L527" s="2" t="inlineStr">
+        <is>
+          <t>17:12:22.523</t>
+        </is>
+      </c>
+      <c r="M527" s="2" t="inlineStr">
+        <is>
+          <t>17:12:27.995</t>
+        </is>
+      </c>
+      <c r="N527" s="2" t="inlineStr">
+        <is>
+          <t>17:12:28.143</t>
+        </is>
+      </c>
+      <c r="O527" s="2" t="inlineStr">
+        <is>
+          <t>17:12:28.273</t>
+        </is>
+      </c>
+      <c r="P527" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="Q527" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R527" s="2" t="n">
+        <v>5808</v>
+      </c>
+      <c r="S527" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="T527" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="U527" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V527" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="W527" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X527" s="2" t="n">
+        <v>6086</v>
+      </c>
+      <c r="Y527" s="2" t="inlineStr">
+        <is>
+          <t>6.1s</t>
+        </is>
+      </c>
+      <c r="Z527" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA527" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB527" s="2" t="inlineStr"/>
+      <c r="AC527" s="2" t="inlineStr"/>
+      <c r="AD527" s="2" t="inlineStr"/>
+      <c r="AE527" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF527" s="2" t="n">
+        <v>5852</v>
+      </c>
+      <c r="AG527" s="2" t="n">
+        <v>1892</v>
+      </c>
+      <c r="AH527" s="2" t="n">
+        <v>7744</v>
+      </c>
+      <c r="AI527" s="2" t="n">
+        <v>6464</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1842</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F528" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G528" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H528" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I528" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J528" s="2" t="inlineStr">
+        <is>
+          <t>17:12:27.475</t>
+        </is>
+      </c>
+      <c r="K528" s="2" t="inlineStr">
+        <is>
+          <t>17:12:27.506</t>
+        </is>
+      </c>
+      <c r="L528" s="2" t="inlineStr">
+        <is>
+          <t>17:12:27.788</t>
+        </is>
+      </c>
+      <c r="M528" s="2" t="inlineStr">
+        <is>
+          <t>17:12:38.676</t>
+        </is>
+      </c>
+      <c r="N528" s="2" t="inlineStr">
+        <is>
+          <t>17:12:38.764</t>
+        </is>
+      </c>
+      <c r="O528" s="2" t="inlineStr">
+        <is>
+          <t>17:12:38.845</t>
+        </is>
+      </c>
+      <c r="P528" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="Q528" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R528" s="2" t="n">
+        <v>11201</v>
+      </c>
+      <c r="S528" s="2" t="inlineStr">
+        <is>
+          <t>11.2s</t>
+        </is>
+      </c>
+      <c r="T528" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="U528" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V528" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="W528" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X528" s="2" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Y528" s="2" t="inlineStr">
+        <is>
+          <t>11.4s</t>
+        </is>
+      </c>
+      <c r="Z528" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA528" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB528" s="2" t="inlineStr"/>
+      <c r="AC528" s="2" t="inlineStr"/>
+      <c r="AD528" s="2" t="inlineStr"/>
+      <c r="AE528" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF528" s="2" t="n">
+        <v>5773</v>
+      </c>
+      <c r="AG528" s="2" t="n">
+        <v>2108</v>
+      </c>
+      <c r="AH528" s="2" t="n">
+        <v>7881</v>
+      </c>
+      <c r="AI528" s="2" t="n">
+        <v>7378</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B529" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C529" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1843</t>
+        </is>
+      </c>
+      <c r="D529" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F529" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G529" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H529" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I529" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J529" s="2" t="inlineStr">
+        <is>
+          <t>19:05:22.160</t>
+        </is>
+      </c>
+      <c r="K529" s="2" t="inlineStr">
+        <is>
+          <t>19:05:22.177</t>
+        </is>
+      </c>
+      <c r="L529" s="2" t="inlineStr">
+        <is>
+          <t>19:05:22.570</t>
+        </is>
+      </c>
+      <c r="M529" s="2" t="inlineStr">
+        <is>
+          <t>19:05:27.633</t>
+        </is>
+      </c>
+      <c r="N529" s="2" t="inlineStr">
+        <is>
+          <t>19:05:27.681</t>
+        </is>
+      </c>
+      <c r="O529" s="2" t="inlineStr">
+        <is>
+          <t>19:05:27.775</t>
+        </is>
+      </c>
+      <c r="P529" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="Q529" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R529" s="2" t="n">
+        <v>5473</v>
+      </c>
+      <c r="S529" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="T529" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U529" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V529" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="W529" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X529" s="2" t="n">
+        <v>5615</v>
+      </c>
+      <c r="Y529" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="Z529" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA529" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB529" s="2" t="inlineStr"/>
+      <c r="AC529" s="2" t="inlineStr"/>
+      <c r="AD529" s="2" t="inlineStr"/>
+      <c r="AE529" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF529" s="2" t="n">
+        <v>17502</v>
+      </c>
+      <c r="AG529" s="2" t="n">
+        <v>1549</v>
+      </c>
+      <c r="AH529" s="2" t="n">
+        <v>19051</v>
+      </c>
+      <c r="AI529" s="2" t="n">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1844</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F530" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G530" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H530" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I530" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J530" s="2" t="inlineStr">
+        <is>
+          <t>19:05:26.130</t>
+        </is>
+      </c>
+      <c r="K530" s="2" t="inlineStr">
+        <is>
+          <t>19:05:26.146</t>
+        </is>
+      </c>
+      <c r="L530" s="2" t="inlineStr">
+        <is>
+          <t>19:05:26.478</t>
+        </is>
+      </c>
+      <c r="M530" s="2" t="inlineStr">
+        <is>
+          <t>19:05:28.555</t>
+        </is>
+      </c>
+      <c r="N530" s="2" t="inlineStr">
+        <is>
+          <t>19:05:28.602</t>
+        </is>
+      </c>
+      <c r="O530" s="2" t="inlineStr">
+        <is>
+          <t>19:05:29.268</t>
+        </is>
+      </c>
+      <c r="P530" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="Q530" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R530" s="2" t="n">
+        <v>2425</v>
+      </c>
+      <c r="S530" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="T530" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U530" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V530" s="2" t="n">
+        <v>666</v>
+      </c>
+      <c r="W530" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="X530" s="2" t="n">
+        <v>3138</v>
+      </c>
+      <c r="Y530" s="2" t="inlineStr">
+        <is>
+          <t>3.1s</t>
+        </is>
+      </c>
+      <c r="Z530" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA530" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB530" s="2" t="inlineStr"/>
+      <c r="AC530" s="2" t="inlineStr"/>
+      <c r="AD530" s="2" t="inlineStr"/>
+      <c r="AE530" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF530" s="2" t="n">
+        <v>1382</v>
+      </c>
+      <c r="AG530" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH530" s="2" t="n">
+        <v>1411</v>
+      </c>
+      <c r="AI530" s="2" t="n">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B531" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C531" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1845</t>
+        </is>
+      </c>
+      <c r="D531" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E531" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F531" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G531" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H531" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I531" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J531" s="2" t="inlineStr">
+        <is>
+          <t>19:05:29.518</t>
+        </is>
+      </c>
+      <c r="K531" s="2" t="inlineStr">
+        <is>
+          <t>19:05:29.534</t>
+        </is>
+      </c>
+      <c r="L531" s="2" t="inlineStr">
+        <is>
+          <t>19:05:30.040</t>
+        </is>
+      </c>
+      <c r="M531" s="2" t="inlineStr">
+        <is>
+          <t>19:05:35.970</t>
+        </is>
+      </c>
+      <c r="N531" s="2" t="inlineStr">
+        <is>
+          <t>19:05:36.023</t>
+        </is>
+      </c>
+      <c r="O531" s="2" t="inlineStr">
+        <is>
+          <t>19:05:36.122</t>
+        </is>
+      </c>
+      <c r="P531" s="2" t="n">
+        <v>506</v>
+      </c>
+      <c r="Q531" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R531" s="2" t="n">
+        <v>6452</v>
+      </c>
+      <c r="S531" s="2" t="inlineStr">
+        <is>
+          <t>6.5s</t>
+        </is>
+      </c>
+      <c r="T531" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U531" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V531" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="W531" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X531" s="2" t="n">
+        <v>6604</v>
+      </c>
+      <c r="Y531" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="Z531" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA531" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB531" s="2" t="inlineStr"/>
+      <c r="AC531" s="2" t="inlineStr"/>
+      <c r="AD531" s="2" t="inlineStr"/>
+      <c r="AE531" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF531" s="2" t="n">
+        <v>17502</v>
+      </c>
+      <c r="AG531" s="2" t="n">
+        <v>1549</v>
+      </c>
+      <c r="AH531" s="2" t="n">
+        <v>19051</v>
+      </c>
+      <c r="AI531" s="2" t="n">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1846</t>
+        </is>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G532" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H532" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I532" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J532" s="2" t="inlineStr">
+        <is>
+          <t>19:05:37.536</t>
+        </is>
+      </c>
+      <c r="K532" s="2" t="inlineStr">
+        <is>
+          <t>19:05:37.551</t>
+        </is>
+      </c>
+      <c r="L532" s="2" t="inlineStr">
+        <is>
+          <t>19:05:37.974</t>
+        </is>
+      </c>
+      <c r="M532" s="2" t="inlineStr">
+        <is>
+          <t>19:05:42.011</t>
+        </is>
+      </c>
+      <c r="N532" s="2" t="inlineStr">
+        <is>
+          <t>19:05:42.060</t>
+        </is>
+      </c>
+      <c r="O532" s="2" t="inlineStr">
+        <is>
+          <t>19:05:42.171</t>
+        </is>
+      </c>
+      <c r="P532" s="2" t="n">
+        <v>423</v>
+      </c>
+      <c r="Q532" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R532" s="2" t="n">
+        <v>4475</v>
+      </c>
+      <c r="S532" s="2" t="inlineStr">
+        <is>
+          <t>4.5s</t>
+        </is>
+      </c>
+      <c r="T532" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U532" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V532" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="W532" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X532" s="2" t="n">
+        <v>4635</v>
+      </c>
+      <c r="Y532" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="Z532" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA532" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB532" s="2" t="inlineStr"/>
+      <c r="AC532" s="2" t="inlineStr"/>
+      <c r="AD532" s="2" t="inlineStr"/>
+      <c r="AE532" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF532" s="2" t="n">
+        <v>17502</v>
+      </c>
+      <c r="AG532" s="2" t="n">
+        <v>1549</v>
+      </c>
+      <c r="AH532" s="2" t="n">
+        <v>19051</v>
+      </c>
+      <c r="AI532" s="2" t="n">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B533" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1847</t>
+        </is>
+      </c>
+      <c r="D533" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F533" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G533" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H533" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I533" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J533" s="2" t="inlineStr">
+        <is>
+          <t>19:05:43.609</t>
+        </is>
+      </c>
+      <c r="K533" s="2" t="inlineStr">
+        <is>
+          <t>19:05:43.624</t>
+        </is>
+      </c>
+      <c r="L533" s="2" t="inlineStr">
+        <is>
+          <t>19:05:44.124</t>
+        </is>
+      </c>
+      <c r="M533" s="2" t="inlineStr">
+        <is>
+          <t>19:05:50.455</t>
+        </is>
+      </c>
+      <c r="N533" s="2" t="inlineStr">
+        <is>
+          <t>19:05:50.504</t>
+        </is>
+      </c>
+      <c r="O533" s="2" t="inlineStr">
+        <is>
+          <t>19:05:50.611</t>
+        </is>
+      </c>
+      <c r="P533" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q533" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R533" s="2" t="n">
+        <v>6846</v>
+      </c>
+      <c r="S533" s="2" t="inlineStr">
+        <is>
+          <t>6.8s</t>
+        </is>
+      </c>
+      <c r="T533" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U533" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V533" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="W533" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X533" s="2" t="n">
+        <v>7002</v>
+      </c>
+      <c r="Y533" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="Z533" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA533" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB533" s="2" t="inlineStr"/>
+      <c r="AC533" s="2" t="inlineStr"/>
+      <c r="AD533" s="2" t="inlineStr"/>
+      <c r="AE533" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF533" s="2" t="n">
+        <v>17502</v>
+      </c>
+      <c r="AG533" s="2" t="n">
+        <v>1549</v>
+      </c>
+      <c r="AH533" s="2" t="n">
+        <v>19051</v>
+      </c>
+      <c r="AI533" s="2" t="n">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1848</t>
+        </is>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F534" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G534" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H534" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I534" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J534" s="2" t="inlineStr">
+        <is>
+          <t>19:05:52.178</t>
+        </is>
+      </c>
+      <c r="K534" s="2" t="inlineStr">
+        <is>
+          <t>19:05:52.195</t>
+        </is>
+      </c>
+      <c r="L534" s="2" t="inlineStr">
+        <is>
+          <t>19:05:52.608</t>
+        </is>
+      </c>
+      <c r="M534" s="2" t="inlineStr">
+        <is>
+          <t>19:05:57.547</t>
+        </is>
+      </c>
+      <c r="N534" s="2" t="inlineStr">
+        <is>
+          <t>19:05:57.594</t>
+        </is>
+      </c>
+      <c r="O534" s="2" t="inlineStr">
+        <is>
+          <t>19:05:57.715</t>
+        </is>
+      </c>
+      <c r="P534" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="Q534" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R534" s="2" t="n">
+        <v>5369</v>
+      </c>
+      <c r="S534" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="T534" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U534" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V534" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="W534" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X534" s="2" t="n">
+        <v>5537</v>
+      </c>
+      <c r="Y534" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="Z534" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA534" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB534" s="2" t="inlineStr"/>
+      <c r="AC534" s="2" t="inlineStr"/>
+      <c r="AD534" s="2" t="inlineStr"/>
+      <c r="AE534" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF534" s="2" t="n">
+        <v>17502</v>
+      </c>
+      <c r="AG534" s="2" t="n">
+        <v>1549</v>
+      </c>
+      <c r="AH534" s="2" t="n">
+        <v>19051</v>
+      </c>
+      <c r="AI534" s="2" t="n">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C535" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1849</t>
+        </is>
+      </c>
+      <c r="D535" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F535" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G535" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H535" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I535" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J535" s="2" t="inlineStr">
+        <is>
+          <t>19:05:59.236</t>
+        </is>
+      </c>
+      <c r="K535" s="2" t="inlineStr">
+        <is>
+          <t>19:05:59.252</t>
+        </is>
+      </c>
+      <c r="L535" s="2" t="inlineStr">
+        <is>
+          <t>19:05:59.738</t>
+        </is>
+      </c>
+      <c r="M535" s="2" t="inlineStr">
+        <is>
+          <t>19:06:07.107</t>
+        </is>
+      </c>
+      <c r="N535" s="2" t="inlineStr">
+        <is>
+          <t>19:06:07.158</t>
+        </is>
+      </c>
+      <c r="O535" s="2" t="inlineStr">
+        <is>
+          <t>19:06:07.259</t>
+        </is>
+      </c>
+      <c r="P535" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="Q535" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R535" s="2" t="n">
+        <v>7871</v>
+      </c>
+      <c r="S535" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="T535" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U535" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V535" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="W535" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X535" s="2" t="n">
+        <v>8023</v>
+      </c>
+      <c r="Y535" s="2" t="inlineStr">
+        <is>
+          <t>8.0s</t>
+        </is>
+      </c>
+      <c r="Z535" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA535" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB535" s="2" t="inlineStr"/>
+      <c r="AC535" s="2" t="inlineStr"/>
+      <c r="AD535" s="2" t="inlineStr"/>
+      <c r="AE535" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF535" s="2" t="n">
+        <v>17502</v>
+      </c>
+      <c r="AG535" s="2" t="n">
+        <v>1549</v>
+      </c>
+      <c r="AH535" s="2" t="n">
+        <v>19051</v>
+      </c>
+      <c r="AI535" s="2" t="n">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1850</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I536" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J536" s="2" t="inlineStr">
+        <is>
+          <t>20:43:30.284</t>
+        </is>
+      </c>
+      <c r="K536" s="2" t="inlineStr">
+        <is>
+          <t>20:43:30.402</t>
+        </is>
+      </c>
+      <c r="L536" s="2" t="inlineStr">
+        <is>
+          <t>20:43:30.714</t>
+        </is>
+      </c>
+      <c r="M536" s="2" t="inlineStr">
+        <is>
+          <t>20:43:36.399</t>
+        </is>
+      </c>
+      <c r="N536" s="2" t="inlineStr">
+        <is>
+          <t>20:43:36.462</t>
+        </is>
+      </c>
+      <c r="O536" s="2" t="inlineStr">
+        <is>
+          <t>20:43:36.542</t>
+        </is>
+      </c>
+      <c r="P536" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q536" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R536" s="2" t="n">
+        <v>6115</v>
+      </c>
+      <c r="S536" s="2" t="inlineStr">
+        <is>
+          <t>6.1s</t>
+        </is>
+      </c>
+      <c r="T536" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U536" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V536" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="W536" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X536" s="2" t="n">
+        <v>6258</v>
+      </c>
+      <c r="Y536" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="Z536" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA536" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB536" s="2" t="inlineStr"/>
+      <c r="AC536" s="2" t="inlineStr"/>
+      <c r="AD536" s="2" t="inlineStr"/>
+      <c r="AE536" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF536" s="2" t="n">
+        <v>6270</v>
+      </c>
+      <c r="AG536" s="2" t="n">
+        <v>1177</v>
+      </c>
+      <c r="AH536" s="2" t="n">
+        <v>7447</v>
+      </c>
+      <c r="AI536" s="2" t="n">
+        <v>3488</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1851</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F537" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G537" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H537" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I537" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J537" s="2" t="inlineStr">
+        <is>
+          <t>20:43:35.346</t>
+        </is>
+      </c>
+      <c r="K537" s="2" t="inlineStr">
+        <is>
+          <t>20:43:35.363</t>
+        </is>
+      </c>
+      <c r="L537" s="2" t="inlineStr">
+        <is>
+          <t>20:43:35.616</t>
+        </is>
+      </c>
+      <c r="M537" s="2" t="inlineStr">
+        <is>
+          <t>20:43:38.829</t>
+        </is>
+      </c>
+      <c r="N537" s="2" t="inlineStr">
+        <is>
+          <t>20:43:38.889</t>
+        </is>
+      </c>
+      <c r="O537" s="2" t="inlineStr">
+        <is>
+          <t>20:43:38.994</t>
+        </is>
+      </c>
+      <c r="P537" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="Q537" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R537" s="2" t="n">
+        <v>3483</v>
+      </c>
+      <c r="S537" s="2" t="inlineStr">
+        <is>
+          <t>3.5s</t>
+        </is>
+      </c>
+      <c r="T537" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U537" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V537" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="W537" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X537" s="2" t="n">
+        <v>3648</v>
+      </c>
+      <c r="Y537" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="Z537" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA537" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB537" s="2" t="inlineStr"/>
+      <c r="AC537" s="2" t="inlineStr"/>
+      <c r="AD537" s="2" t="inlineStr"/>
+      <c r="AE537" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF537" s="2" t="n">
+        <v>3285</v>
+      </c>
+      <c r="AG537" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="AH537" s="2" t="n">
+        <v>3781</v>
+      </c>
+      <c r="AI537" s="2" t="n">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1852</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G538" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I538" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J538" s="2" t="inlineStr">
+        <is>
+          <t>20:43:39.934</t>
+        </is>
+      </c>
+      <c r="K538" s="2" t="inlineStr">
+        <is>
+          <t>20:43:39.936</t>
+        </is>
+      </c>
+      <c r="L538" s="2" t="inlineStr">
+        <is>
+          <t>20:43:40.558</t>
+        </is>
+      </c>
+      <c r="M538" s="2" t="inlineStr">
+        <is>
+          <t>20:43:42.461</t>
+        </is>
+      </c>
+      <c r="N538" s="2" t="inlineStr">
+        <is>
+          <t>20:43:42.522</t>
+        </is>
+      </c>
+      <c r="O538" s="2" t="inlineStr">
+        <is>
+          <t>20:43:42.601</t>
+        </is>
+      </c>
+      <c r="P538" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="Q538" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R538" s="2" t="n">
+        <v>2527</v>
+      </c>
+      <c r="S538" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="T538" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U538" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V538" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="W538" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X538" s="2" t="n">
+        <v>2667</v>
+      </c>
+      <c r="Y538" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="Z538" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA538" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB538" s="2" t="inlineStr"/>
+      <c r="AC538" s="2" t="inlineStr"/>
+      <c r="AD538" s="2" t="inlineStr"/>
+      <c r="AE538" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF538" s="2" t="n">
+        <v>3285</v>
+      </c>
+      <c r="AG538" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="AH538" s="2" t="n">
+        <v>3781</v>
+      </c>
+      <c r="AI538" s="2" t="n">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1853</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F539" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G539" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H539" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I539" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J539" s="2" t="inlineStr">
+        <is>
+          <t>20:43:42.913</t>
+        </is>
+      </c>
+      <c r="K539" s="2" t="inlineStr">
+        <is>
+          <t>20:43:42.933</t>
+        </is>
+      </c>
+      <c r="L539" s="2" t="inlineStr">
+        <is>
+          <t>20:43:43.220</t>
+        </is>
+      </c>
+      <c r="M539" s="2" t="inlineStr">
+        <is>
+          <t>20:43:46.439</t>
+        </is>
+      </c>
+      <c r="N539" s="2" t="inlineStr">
+        <is>
+          <t>20:43:46.501</t>
+        </is>
+      </c>
+      <c r="O539" s="2" t="inlineStr">
+        <is>
+          <t>20:43:46.572</t>
+        </is>
+      </c>
+      <c r="P539" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q539" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R539" s="2" t="n">
+        <v>3526</v>
+      </c>
+      <c r="S539" s="2" t="inlineStr">
+        <is>
+          <t>3.5s</t>
+        </is>
+      </c>
+      <c r="T539" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U539" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V539" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="W539" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X539" s="2" t="n">
+        <v>3659</v>
+      </c>
+      <c r="Y539" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="Z539" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA539" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB539" s="2" t="inlineStr"/>
+      <c r="AC539" s="2" t="inlineStr"/>
+      <c r="AD539" s="2" t="inlineStr"/>
+      <c r="AE539" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF539" s="2" t="n">
+        <v>6270</v>
+      </c>
+      <c r="AG539" s="2" t="n">
+        <v>1177</v>
+      </c>
+      <c r="AH539" s="2" t="n">
+        <v>7447</v>
+      </c>
+      <c r="AI539" s="2" t="n">
+        <v>3488</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1854</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I540" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J540" s="2" t="inlineStr">
+        <is>
+          <t>20:43:48.830</t>
+        </is>
+      </c>
+      <c r="K540" s="2" t="inlineStr">
+        <is>
+          <t>20:43:48.849</t>
+        </is>
+      </c>
+      <c r="L540" s="2" t="inlineStr">
+        <is>
+          <t>20:43:49.172</t>
+        </is>
+      </c>
+      <c r="M540" s="2" t="inlineStr">
+        <is>
+          <t>20:43:52.228</t>
+        </is>
+      </c>
+      <c r="N540" s="2" t="inlineStr">
+        <is>
+          <t>20:43:52.290</t>
+        </is>
+      </c>
+      <c r="O540" s="2" t="inlineStr">
+        <is>
+          <t>20:43:52.364</t>
+        </is>
+      </c>
+      <c r="P540" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q540" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R540" s="2" t="n">
+        <v>3398</v>
+      </c>
+      <c r="S540" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="T540" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U540" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V540" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="W540" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X540" s="2" t="n">
+        <v>3534</v>
+      </c>
+      <c r="Y540" s="2" t="inlineStr">
+        <is>
+          <t>3.5s</t>
+        </is>
+      </c>
+      <c r="Z540" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA540" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB540" s="2" t="inlineStr"/>
+      <c r="AC540" s="2" t="inlineStr"/>
+      <c r="AD540" s="2" t="inlineStr"/>
+      <c r="AE540" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF540" s="2" t="n">
+        <v>6270</v>
+      </c>
+      <c r="AG540" s="2" t="n">
+        <v>1177</v>
+      </c>
+      <c r="AH540" s="2" t="n">
+        <v>7447</v>
+      </c>
+      <c r="AI540" s="2" t="n">
+        <v>3488</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1855</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F541" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G541" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H541" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I541" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J541" s="2" t="inlineStr">
+        <is>
+          <t>20:43:54.556</t>
+        </is>
+      </c>
+      <c r="K541" s="2" t="inlineStr">
+        <is>
+          <t>20:43:54.576</t>
+        </is>
+      </c>
+      <c r="L541" s="2" t="inlineStr">
+        <is>
+          <t>20:43:54.841</t>
+        </is>
+      </c>
+      <c r="M541" s="2" t="inlineStr">
+        <is>
+          <t>20:43:59.135</t>
+        </is>
+      </c>
+      <c r="N541" s="2" t="inlineStr">
+        <is>
+          <t>20:43:59.194</t>
+        </is>
+      </c>
+      <c r="O541" s="2" t="inlineStr">
+        <is>
+          <t>20:43:59.303</t>
+        </is>
+      </c>
+      <c r="P541" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="Q541" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R541" s="2" t="n">
+        <v>4579</v>
+      </c>
+      <c r="S541" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="T541" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U541" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V541" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="W541" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X541" s="2" t="n">
+        <v>4747</v>
+      </c>
+      <c r="Y541" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="Z541" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA541" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB541" s="2" t="inlineStr"/>
+      <c r="AC541" s="2" t="inlineStr"/>
+      <c r="AD541" s="2" t="inlineStr"/>
+      <c r="AE541" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF541" s="2" t="n">
+        <v>6270</v>
+      </c>
+      <c r="AG541" s="2" t="n">
+        <v>1177</v>
+      </c>
+      <c r="AH541" s="2" t="n">
+        <v>7447</v>
+      </c>
+      <c r="AI541" s="2" t="n">
+        <v>3488</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1856</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G542" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H542" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I542" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J542" s="2" t="inlineStr">
+        <is>
+          <t>22:00:27.886</t>
+        </is>
+      </c>
+      <c r="K542" s="2" t="inlineStr">
+        <is>
+          <t>22:00:27.910</t>
+        </is>
+      </c>
+      <c r="L542" s="2" t="inlineStr">
+        <is>
+          <t>22:00:28.623</t>
+        </is>
+      </c>
+      <c r="M542" s="2" t="inlineStr">
+        <is>
+          <t>22:00:34.521</t>
+        </is>
+      </c>
+      <c r="N542" s="2" t="inlineStr">
+        <is>
+          <t>22:00:34.814</t>
+        </is>
+      </c>
+      <c r="O542" s="2" t="inlineStr">
+        <is>
+          <t>22:00:35.133</t>
+        </is>
+      </c>
+      <c r="P542" s="2" t="n">
+        <v>713</v>
+      </c>
+      <c r="Q542" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R542" s="2" t="n">
+        <v>6635</v>
+      </c>
+      <c r="S542" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="T542" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="U542" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="V542" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="W542" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X542" s="2" t="n">
+        <v>7247</v>
+      </c>
+      <c r="Y542" s="2" t="inlineStr">
+        <is>
+          <t>7.2s</t>
+        </is>
+      </c>
+      <c r="Z542" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA542" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB542" s="2" t="inlineStr"/>
+      <c r="AC542" s="2" t="inlineStr"/>
+      <c r="AD542" s="2" t="inlineStr"/>
+      <c r="AE542" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF542" s="2" t="n">
+        <v>1785</v>
+      </c>
+      <c r="AG542" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="AH542" s="2" t="n">
+        <v>2248</v>
+      </c>
+      <c r="AI542" s="2" t="n">
+        <v>4451</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B543" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="C543" s="4" t="inlineStr">
+        <is>
+          <t>translationjob1857</t>
+        </is>
+      </c>
+      <c r="D543" s="4" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E543" s="4" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F543" s="4" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G543" s="4" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H543" s="4" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I543" s="4" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J543" s="4" t="inlineStr">
+        <is>
+          <t>22:00:36.216</t>
+        </is>
+      </c>
+      <c r="K543" s="4" t="inlineStr">
+        <is>
+          <t>22:00:36.247</t>
+        </is>
+      </c>
+      <c r="L543" s="4" t="inlineStr">
+        <is>
+          <t>22:00:36.474</t>
+        </is>
+      </c>
+      <c r="M543" s="4" t="inlineStr">
+        <is>
+          <t>22:00:36.810</t>
+        </is>
+      </c>
+      <c r="N543" s="4" t="inlineStr"/>
+      <c r="O543" s="4" t="inlineStr"/>
+      <c r="P543" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="Q543" s="4" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R543" s="4" t="n">
+        <v>594</v>
+      </c>
+      <c r="S543" s="4" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="T543" s="4" t="inlineStr"/>
+      <c r="U543" s="4" t="inlineStr"/>
+      <c r="V543" s="4" t="inlineStr"/>
+      <c r="W543" s="4" t="inlineStr"/>
+      <c r="X543" s="4" t="inlineStr"/>
+      <c r="Y543" s="4" t="inlineStr"/>
+      <c r="Z543" s="4" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:0, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA543" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB543" s="4" t="inlineStr"/>
+      <c r="AC543" s="4" t="inlineStr"/>
+      <c r="AD543" s="4" t="inlineStr"/>
+      <c r="AE543" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF543" s="4" t="n">
+        <v>8886</v>
+      </c>
+      <c r="AG543" s="4" t="n">
+        <v>2416</v>
+      </c>
+      <c r="AH543" s="4" t="n">
+        <v>11302</v>
+      </c>
+      <c r="AI543" s="4" t="n">
+        <v>4512</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1858</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I544" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J544" s="2" t="inlineStr">
+        <is>
+          <t>22:00:39.986</t>
+        </is>
+      </c>
+      <c r="K544" s="2" t="inlineStr">
+        <is>
+          <t>22:00:40.014</t>
+        </is>
+      </c>
+      <c r="L544" s="2" t="inlineStr">
+        <is>
+          <t>22:00:41.283</t>
+        </is>
+      </c>
+      <c r="M544" s="2" t="inlineStr">
+        <is>
+          <t>22:00:47.118</t>
+        </is>
+      </c>
+      <c r="N544" s="2" t="inlineStr">
+        <is>
+          <t>22:00:47.189</t>
+        </is>
+      </c>
+      <c r="O544" s="2" t="inlineStr">
+        <is>
+          <t>22:00:47.393</t>
+        </is>
+      </c>
+      <c r="P544" s="2" t="n">
+        <v>1269</v>
+      </c>
+      <c r="Q544" s="2" t="inlineStr">
+        <is>
+          <t>1.3s</t>
+        </is>
+      </c>
+      <c r="R544" s="2" t="n">
+        <v>7132</v>
+      </c>
+      <c r="S544" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="T544" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="U544" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V544" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="W544" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X544" s="2" t="n">
+        <v>7407</v>
+      </c>
+      <c r="Y544" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="Z544" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA544" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB544" s="2" t="inlineStr"/>
+      <c r="AC544" s="2" t="inlineStr"/>
+      <c r="AD544" s="2" t="inlineStr"/>
+      <c r="AE544" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF544" s="2" t="n">
+        <v>8886</v>
+      </c>
+      <c r="AG544" s="2" t="n">
+        <v>2416</v>
+      </c>
+      <c r="AH544" s="2" t="n">
+        <v>11302</v>
+      </c>
+      <c r="AI544" s="2" t="n">
+        <v>4512</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1859</t>
+        </is>
+      </c>
+      <c r="D545" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F545" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G545" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H545" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I545" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J545" s="2" t="inlineStr">
+        <is>
+          <t>22:00:50.387</t>
+        </is>
+      </c>
+      <c r="K545" s="2" t="inlineStr">
+        <is>
+          <t>22:00:50.415</t>
+        </is>
+      </c>
+      <c r="L545" s="2" t="inlineStr">
+        <is>
+          <t>22:00:51.316</t>
+        </is>
+      </c>
+      <c r="M545" s="2" t="inlineStr">
+        <is>
+          <t>22:00:56.553</t>
+        </is>
+      </c>
+      <c r="N545" s="2" t="inlineStr">
+        <is>
+          <t>22:00:56.650</t>
+        </is>
+      </c>
+      <c r="O545" s="2" t="inlineStr">
+        <is>
+          <t>22:00:56.882</t>
+        </is>
+      </c>
+      <c r="P545" s="2" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q545" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="R545" s="2" t="n">
+        <v>6166</v>
+      </c>
+      <c r="S545" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="T545" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="U545" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V545" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="W545" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X545" s="2" t="n">
+        <v>6495</v>
+      </c>
+      <c r="Y545" s="2" t="inlineStr">
+        <is>
+          <t>6.5s</t>
+        </is>
+      </c>
+      <c r="Z545" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA545" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB545" s="2" t="inlineStr"/>
+      <c r="AC545" s="2" t="inlineStr"/>
+      <c r="AD545" s="2" t="inlineStr"/>
+      <c r="AE545" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF545" s="2" t="n">
+        <v>8886</v>
+      </c>
+      <c r="AG545" s="2" t="n">
+        <v>2416</v>
+      </c>
+      <c r="AH545" s="2" t="n">
+        <v>11302</v>
+      </c>
+      <c r="AI545" s="2" t="n">
+        <v>4512</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1860</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G546" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H546" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I546" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J546" s="2" t="inlineStr">
+        <is>
+          <t>22:00:59.811</t>
+        </is>
+      </c>
+      <c r="K546" s="2" t="inlineStr">
+        <is>
+          <t>22:00:59.901</t>
+        </is>
+      </c>
+      <c r="L546" s="2" t="inlineStr">
+        <is>
+          <t>22:01:00.883</t>
+        </is>
+      </c>
+      <c r="M546" s="2" t="inlineStr">
+        <is>
+          <t>22:01:06.118</t>
+        </is>
+      </c>
+      <c r="N546" s="2" t="inlineStr">
+        <is>
+          <t>22:01:06.317</t>
+        </is>
+      </c>
+      <c r="O546" s="2" t="inlineStr">
+        <is>
+          <t>22:01:06.543</t>
+        </is>
+      </c>
+      <c r="P546" s="2" t="n">
+        <v>982</v>
+      </c>
+      <c r="Q546" s="2" t="inlineStr">
+        <is>
+          <t>1.0s</t>
+        </is>
+      </c>
+      <c r="R546" s="2" t="n">
+        <v>6307</v>
+      </c>
+      <c r="S546" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="T546" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="U546" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V546" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="W546" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X546" s="2" t="n">
+        <v>6732</v>
+      </c>
+      <c r="Y546" s="2" t="inlineStr">
+        <is>
+          <t>6.7s</t>
+        </is>
+      </c>
+      <c r="Z546" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA546" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB546" s="2" t="inlineStr"/>
+      <c r="AC546" s="2" t="inlineStr"/>
+      <c r="AD546" s="2" t="inlineStr"/>
+      <c r="AE546" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF546" s="2" t="n">
+        <v>8886</v>
+      </c>
+      <c r="AG546" s="2" t="n">
+        <v>2416</v>
+      </c>
+      <c r="AH546" s="2" t="n">
+        <v>11302</v>
+      </c>
+      <c r="AI546" s="2" t="n">
+        <v>4512</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1861</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F547" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G547" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H547" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I547" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J547" s="2" t="inlineStr">
+        <is>
+          <t>22:01:09.706</t>
+        </is>
+      </c>
+      <c r="K547" s="2" t="inlineStr">
+        <is>
+          <t>22:01:09.731</t>
+        </is>
+      </c>
+      <c r="L547" s="2" t="inlineStr">
+        <is>
+          <t>22:01:10.411</t>
+        </is>
+      </c>
+      <c r="M547" s="2" t="inlineStr">
+        <is>
+          <t>22:01:14.677</t>
+        </is>
+      </c>
+      <c r="N547" s="2" t="inlineStr">
+        <is>
+          <t>22:01:14.800</t>
+        </is>
+      </c>
+      <c r="O547" s="2" t="inlineStr">
+        <is>
+          <t>22:01:15.191</t>
+        </is>
+      </c>
+      <c r="P547" s="2" t="n">
+        <v>680</v>
+      </c>
+      <c r="Q547" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R547" s="2" t="n">
+        <v>4971</v>
+      </c>
+      <c r="S547" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="T547" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="U547" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V547" s="2" t="n">
+        <v>391</v>
+      </c>
+      <c r="W547" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X547" s="2" t="n">
+        <v>5485</v>
+      </c>
+      <c r="Y547" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="Z547" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA547" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB547" s="2" t="inlineStr"/>
+      <c r="AC547" s="2" t="inlineStr"/>
+      <c r="AD547" s="2" t="inlineStr"/>
+      <c r="AE547" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF547" s="2" t="n">
+        <v>8886</v>
+      </c>
+      <c r="AG547" s="2" t="n">
+        <v>2416</v>
+      </c>
+      <c r="AH547" s="2" t="n">
+        <v>11302</v>
+      </c>
+      <c r="AI547" s="2" t="n">
+        <v>4512</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1862</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G548" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I548" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J548" s="2" t="inlineStr">
+        <is>
+          <t>22:01:18.353</t>
+        </is>
+      </c>
+      <c r="K548" s="2" t="inlineStr">
+        <is>
+          <t>22:01:18.380</t>
+        </is>
+      </c>
+      <c r="L548" s="2" t="inlineStr">
+        <is>
+          <t>22:01:19.368</t>
+        </is>
+      </c>
+      <c r="M548" s="2" t="inlineStr">
+        <is>
+          <t>22:01:25.208</t>
+        </is>
+      </c>
+      <c r="N548" s="2" t="inlineStr">
+        <is>
+          <t>22:01:25.304</t>
+        </is>
+      </c>
+      <c r="O548" s="2" t="inlineStr">
+        <is>
+          <t>22:01:25.916</t>
+        </is>
+      </c>
+      <c r="P548" s="2" t="n">
+        <v>988</v>
+      </c>
+      <c r="Q548" s="2" t="inlineStr">
+        <is>
+          <t>1.0s</t>
+        </is>
+      </c>
+      <c r="R548" s="2" t="n">
+        <v>6855</v>
+      </c>
+      <c r="S548" s="2" t="inlineStr">
+        <is>
+          <t>6.9s</t>
+        </is>
+      </c>
+      <c r="T548" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="U548" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V548" s="2" t="n">
+        <v>612</v>
+      </c>
+      <c r="W548" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="X548" s="2" t="n">
+        <v>7563</v>
+      </c>
+      <c r="Y548" s="2" t="inlineStr">
+        <is>
+          <t>7.6s</t>
+        </is>
+      </c>
+      <c r="Z548" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA548" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB548" s="2" t="inlineStr"/>
+      <c r="AC548" s="2" t="inlineStr"/>
+      <c r="AD548" s="2" t="inlineStr"/>
+      <c r="AE548" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF548" s="2" t="n">
+        <v>8886</v>
+      </c>
+      <c r="AG548" s="2" t="n">
+        <v>2416</v>
+      </c>
+      <c r="AH548" s="2" t="n">
+        <v>11302</v>
+      </c>
+      <c r="AI548" s="2" t="n">
+        <v>4512</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1863</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F549" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G549" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I549" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J549" s="2" t="inlineStr">
+        <is>
+          <t>22:02:10.298</t>
+        </is>
+      </c>
+      <c r="K549" s="2" t="inlineStr">
+        <is>
+          <t>22:02:10.382</t>
+        </is>
+      </c>
+      <c r="L549" s="2" t="inlineStr">
+        <is>
+          <t>22:02:12.415</t>
+        </is>
+      </c>
+      <c r="M549" s="2" t="inlineStr">
+        <is>
+          <t>22:02:17.517</t>
+        </is>
+      </c>
+      <c r="N549" s="2" t="inlineStr">
+        <is>
+          <t>22:02:17.842</t>
+        </is>
+      </c>
+      <c r="O549" s="2" t="inlineStr">
+        <is>
+          <t>22:02:18.223</t>
+        </is>
+      </c>
+      <c r="P549" s="2" t="n">
+        <v>2033</v>
+      </c>
+      <c r="Q549" s="2" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="R549" s="2" t="n">
+        <v>7219</v>
+      </c>
+      <c r="S549" s="2" t="inlineStr">
+        <is>
+          <t>7.2s</t>
+        </is>
+      </c>
+      <c r="T549" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="U549" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="V549" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="W549" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X549" s="2" t="n">
+        <v>7925</v>
+      </c>
+      <c r="Y549" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="Z549" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA549" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB549" s="2" t="inlineStr"/>
+      <c r="AC549" s="2" t="inlineStr"/>
+      <c r="AD549" s="2" t="inlineStr"/>
+      <c r="AE549" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF549" s="2" t="n">
+        <v>7499</v>
+      </c>
+      <c r="AG549" s="2" t="n">
+        <v>2383</v>
+      </c>
+      <c r="AH549" s="2" t="n">
+        <v>9882</v>
+      </c>
+      <c r="AI549" s="2" t="n">
+        <v>5570</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1864</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I550" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J550" s="2" t="inlineStr">
+        <is>
+          <t>22:02:15.950</t>
+        </is>
+      </c>
+      <c r="K550" s="2" t="inlineStr">
+        <is>
+          <t>22:02:15.983</t>
+        </is>
+      </c>
+      <c r="L550" s="2" t="inlineStr">
+        <is>
+          <t>22:02:17.559</t>
+        </is>
+      </c>
+      <c r="M550" s="2" t="inlineStr">
+        <is>
+          <t>22:02:22.540</t>
+        </is>
+      </c>
+      <c r="N550" s="2" t="inlineStr">
+        <is>
+          <t>22:02:22.697</t>
+        </is>
+      </c>
+      <c r="O550" s="2" t="inlineStr">
+        <is>
+          <t>22:02:22.970</t>
+        </is>
+      </c>
+      <c r="P550" s="2" t="n">
+        <v>1576</v>
+      </c>
+      <c r="Q550" s="2" t="inlineStr">
+        <is>
+          <t>1.6s</t>
+        </is>
+      </c>
+      <c r="R550" s="2" t="n">
+        <v>6590</v>
+      </c>
+      <c r="S550" s="2" t="inlineStr">
+        <is>
+          <t>6.6s</t>
+        </is>
+      </c>
+      <c r="T550" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="U550" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V550" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="W550" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X550" s="2" t="n">
+        <v>7020</v>
+      </c>
+      <c r="Y550" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="Z550" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA550" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB550" s="2" t="inlineStr"/>
+      <c r="AC550" s="2" t="inlineStr"/>
+      <c r="AD550" s="2" t="inlineStr"/>
+      <c r="AE550" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF550" s="2" t="n">
+        <v>7499</v>
+      </c>
+      <c r="AG550" s="2" t="n">
+        <v>2383</v>
+      </c>
+      <c r="AH550" s="2" t="n">
+        <v>9882</v>
+      </c>
+      <c r="AI550" s="2" t="n">
+        <v>5570</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B551" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C551" s="4" t="inlineStr">
+        <is>
+          <t>translationjob1865</t>
+        </is>
+      </c>
+      <c r="D551" s="4" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E551" s="4" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F551" s="4" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G551" s="4" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H551" s="4" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I551" s="4" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J551" s="4" t="inlineStr">
+        <is>
+          <t>22:02:21.594</t>
+        </is>
+      </c>
+      <c r="K551" s="4" t="inlineStr">
+        <is>
+          <t>22:02:21.621</t>
+        </is>
+      </c>
+      <c r="L551" s="4" t="inlineStr">
+        <is>
+          <t>22:02:21.818</t>
+        </is>
+      </c>
+      <c r="M551" s="4" t="inlineStr">
+        <is>
+          <t>22:02:22.205</t>
+        </is>
+      </c>
+      <c r="N551" s="4" t="inlineStr"/>
+      <c r="O551" s="4" t="inlineStr"/>
+      <c r="P551" s="4" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q551" s="4" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R551" s="4" t="n">
+        <v>611</v>
+      </c>
+      <c r="S551" s="4" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="T551" s="4" t="inlineStr"/>
+      <c r="U551" s="4" t="inlineStr"/>
+      <c r="V551" s="4" t="inlineStr"/>
+      <c r="W551" s="4" t="inlineStr"/>
+      <c r="X551" s="4" t="inlineStr"/>
+      <c r="Y551" s="4" t="inlineStr"/>
+      <c r="Z551" s="4" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:0, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA551" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB551" s="4" t="inlineStr"/>
+      <c r="AC551" s="4" t="inlineStr"/>
+      <c r="AD551" s="4" t="inlineStr"/>
+      <c r="AE551" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF551" s="4" t="n">
+        <v>1876</v>
+      </c>
+      <c r="AG551" s="4" t="n">
+        <v>555</v>
+      </c>
+      <c r="AH551" s="4" t="n">
+        <v>2431</v>
+      </c>
+      <c r="AI551" s="4" t="n">
+        <v>4608</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1866</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I552" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J552" s="2" t="inlineStr">
+        <is>
+          <t>22:02:27.314</t>
+        </is>
+      </c>
+      <c r="K552" s="2" t="inlineStr">
+        <is>
+          <t>22:02:27.348</t>
+        </is>
+      </c>
+      <c r="L552" s="2" t="inlineStr">
+        <is>
+          <t>22:02:28.247</t>
+        </is>
+      </c>
+      <c r="M552" s="2" t="inlineStr">
+        <is>
+          <t>22:02:34.783</t>
+        </is>
+      </c>
+      <c r="N552" s="2" t="inlineStr">
+        <is>
+          <t>22:02:34.926</t>
+        </is>
+      </c>
+      <c r="O552" s="2" t="inlineStr">
+        <is>
+          <t>22:02:35.393</t>
+        </is>
+      </c>
+      <c r="P552" s="2" t="n">
+        <v>899</v>
+      </c>
+      <c r="Q552" s="2" t="inlineStr">
+        <is>
+          <t>0.9s</t>
+        </is>
+      </c>
+      <c r="R552" s="2" t="n">
+        <v>7469</v>
+      </c>
+      <c r="S552" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="T552" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="U552" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V552" s="2" t="n">
+        <v>467</v>
+      </c>
+      <c r="W552" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="X552" s="2" t="n">
+        <v>8079</v>
+      </c>
+      <c r="Y552" s="2" t="inlineStr">
+        <is>
+          <t>8.1s</t>
+        </is>
+      </c>
+      <c r="Z552" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA552" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB552" s="2" t="inlineStr"/>
+      <c r="AC552" s="2" t="inlineStr"/>
+      <c r="AD552" s="2" t="inlineStr"/>
+      <c r="AE552" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF552" s="2" t="n">
+        <v>7499</v>
+      </c>
+      <c r="AG552" s="2" t="n">
+        <v>2383</v>
+      </c>
+      <c r="AH552" s="2" t="n">
+        <v>9882</v>
+      </c>
+      <c r="AI552" s="2" t="n">
+        <v>5570</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1867</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G553" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H553" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I553" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J553" s="2" t="inlineStr">
+        <is>
+          <t>22:02:36.941</t>
+        </is>
+      </c>
+      <c r="K553" s="2" t="inlineStr">
+        <is>
+          <t>22:02:36.961</t>
+        </is>
+      </c>
+      <c r="L553" s="2" t="inlineStr">
+        <is>
+          <t>22:02:38.043</t>
+        </is>
+      </c>
+      <c r="M553" s="2" t="inlineStr">
+        <is>
+          <t>22:02:43.951</t>
+        </is>
+      </c>
+      <c r="N553" s="2" t="inlineStr">
+        <is>
+          <t>22:02:44.374</t>
+        </is>
+      </c>
+      <c r="O553" s="2" t="inlineStr">
+        <is>
+          <t>22:02:45.217</t>
+        </is>
+      </c>
+      <c r="P553" s="2" t="n">
+        <v>1082</v>
+      </c>
+      <c r="Q553" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R553" s="2" t="n">
+        <v>7010</v>
+      </c>
+      <c r="S553" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="T553" s="2" t="n">
+        <v>423</v>
+      </c>
+      <c r="U553" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="V553" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="W553" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="X553" s="2" t="n">
+        <v>8276</v>
+      </c>
+      <c r="Y553" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="Z553" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA553" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB553" s="2" t="inlineStr"/>
+      <c r="AC553" s="2" t="inlineStr"/>
+      <c r="AD553" s="2" t="inlineStr"/>
+      <c r="AE553" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF553" s="2" t="n">
+        <v>7499</v>
+      </c>
+      <c r="AG553" s="2" t="n">
+        <v>2383</v>
+      </c>
+      <c r="AH553" s="2" t="n">
+        <v>9882</v>
+      </c>
+      <c r="AI553" s="2" t="n">
+        <v>5570</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1868</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H554" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I554" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J554" s="2" t="inlineStr">
+        <is>
+          <t>22:02:47.025</t>
+        </is>
+      </c>
+      <c r="K554" s="2" t="inlineStr">
+        <is>
+          <t>22:02:47.067</t>
+        </is>
+      </c>
+      <c r="L554" s="2" t="inlineStr">
+        <is>
+          <t>22:02:47.868</t>
+        </is>
+      </c>
+      <c r="M554" s="2" t="inlineStr">
+        <is>
+          <t>22:02:56.335</t>
+        </is>
+      </c>
+      <c r="N554" s="2" t="inlineStr">
+        <is>
+          <t>22:02:56.420</t>
+        </is>
+      </c>
+      <c r="O554" s="2" t="inlineStr">
+        <is>
+          <t>22:02:56.788</t>
+        </is>
+      </c>
+      <c r="P554" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="Q554" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R554" s="2" t="n">
+        <v>9310</v>
+      </c>
+      <c r="S554" s="2" t="inlineStr">
+        <is>
+          <t>9.3s</t>
+        </is>
+      </c>
+      <c r="T554" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="U554" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V554" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="W554" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X554" s="2" t="n">
+        <v>9763</v>
+      </c>
+      <c r="Y554" s="2" t="inlineStr">
+        <is>
+          <t>9.8s</t>
+        </is>
+      </c>
+      <c r="Z554" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA554" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB554" s="2" t="inlineStr"/>
+      <c r="AC554" s="2" t="inlineStr"/>
+      <c r="AD554" s="2" t="inlineStr"/>
+      <c r="AE554" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF554" s="2" t="n">
+        <v>7499</v>
+      </c>
+      <c r="AG554" s="2" t="n">
+        <v>2383</v>
+      </c>
+      <c r="AH554" s="2" t="n">
+        <v>9882</v>
+      </c>
+      <c r="AI554" s="2" t="n">
+        <v>5570</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1869</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F555" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G555" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H555" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I555" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J555" s="2" t="inlineStr">
+        <is>
+          <t>22:03:40.031</t>
+        </is>
+      </c>
+      <c r="K555" s="2" t="inlineStr">
+        <is>
+          <t>22:03:40.059</t>
+        </is>
+      </c>
+      <c r="L555" s="2" t="inlineStr">
+        <is>
+          <t>22:03:41.170</t>
+        </is>
+      </c>
+      <c r="M555" s="2" t="inlineStr">
+        <is>
+          <t>22:03:47.638</t>
+        </is>
+      </c>
+      <c r="N555" s="2" t="inlineStr">
+        <is>
+          <t>22:03:47.776</t>
+        </is>
+      </c>
+      <c r="O555" s="2" t="inlineStr">
+        <is>
+          <t>22:03:48.129</t>
+        </is>
+      </c>
+      <c r="P555" s="2" t="n">
+        <v>1111</v>
+      </c>
+      <c r="Q555" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R555" s="2" t="n">
+        <v>7607</v>
+      </c>
+      <c r="S555" s="2" t="inlineStr">
+        <is>
+          <t>7.6s</t>
+        </is>
+      </c>
+      <c r="T555" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="U555" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V555" s="2" t="n">
+        <v>353</v>
+      </c>
+      <c r="W555" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X555" s="2" t="n">
+        <v>8098</v>
+      </c>
+      <c r="Y555" s="2" t="inlineStr">
+        <is>
+          <t>8.1s</t>
+        </is>
+      </c>
+      <c r="Z555" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA555" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB555" s="2" t="inlineStr"/>
+      <c r="AC555" s="2" t="inlineStr"/>
+      <c r="AD555" s="2" t="inlineStr"/>
+      <c r="AE555" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF555" s="2" t="n">
+        <v>1842</v>
+      </c>
+      <c r="AG555" s="2" t="n">
+        <v>611</v>
+      </c>
+      <c r="AH555" s="2" t="n">
+        <v>2453</v>
+      </c>
+      <c r="AI555" s="2" t="n">
+        <v>5464</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1870</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G556" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H556" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I556" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J556" s="2" t="inlineStr">
+        <is>
+          <t>22:14:14.479</t>
+        </is>
+      </c>
+      <c r="K556" s="2" t="inlineStr">
+        <is>
+          <t>22:14:14.483</t>
+        </is>
+      </c>
+      <c r="L556" s="2" t="inlineStr">
+        <is>
+          <t>22:14:15.819</t>
+        </is>
+      </c>
+      <c r="M556" s="2" t="inlineStr">
+        <is>
+          <t>22:14:22.728</t>
+        </is>
+      </c>
+      <c r="N556" s="2" t="inlineStr">
+        <is>
+          <t>22:14:22.814</t>
+        </is>
+      </c>
+      <c r="O556" s="2" t="inlineStr">
+        <is>
+          <t>22:14:23.197</t>
+        </is>
+      </c>
+      <c r="P556" s="2" t="n">
+        <v>1336</v>
+      </c>
+      <c r="Q556" s="2" t="inlineStr">
+        <is>
+          <t>1.3s</t>
+        </is>
+      </c>
+      <c r="R556" s="2" t="n">
+        <v>8249</v>
+      </c>
+      <c r="S556" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="T556" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="U556" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V556" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="W556" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X556" s="2" t="n">
+        <v>8718</v>
+      </c>
+      <c r="Y556" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="Z556" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA556" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB556" s="2" t="inlineStr"/>
+      <c r="AC556" s="2" t="inlineStr"/>
+      <c r="AD556" s="2" t="inlineStr"/>
+      <c r="AE556" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF556" s="2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="AG556" s="2" t="n">
+        <v>615</v>
+      </c>
+      <c r="AH556" s="2" t="n">
+        <v>2614</v>
+      </c>
+      <c r="AI556" s="2" t="n">
+        <v>6099</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1871</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F557" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G557" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H557" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I557" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J557" s="2" t="inlineStr">
+        <is>
+          <t>22:14:20.877</t>
+        </is>
+      </c>
+      <c r="K557" s="2" t="inlineStr">
+        <is>
+          <t>22:14:20.901</t>
+        </is>
+      </c>
+      <c r="L557" s="2" t="inlineStr">
+        <is>
+          <t>22:14:22.136</t>
+        </is>
+      </c>
+      <c r="M557" s="2" t="inlineStr">
+        <is>
+          <t>22:14:29.185</t>
+        </is>
+      </c>
+      <c r="N557" s="2" t="inlineStr">
+        <is>
+          <t>22:14:29.267</t>
+        </is>
+      </c>
+      <c r="O557" s="2" t="inlineStr">
+        <is>
+          <t>22:14:29.490</t>
+        </is>
+      </c>
+      <c r="P557" s="2" t="n">
+        <v>1235</v>
+      </c>
+      <c r="Q557" s="2" t="inlineStr">
+        <is>
+          <t>1.2s</t>
+        </is>
+      </c>
+      <c r="R557" s="2" t="n">
+        <v>8308</v>
+      </c>
+      <c r="S557" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="T557" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="U557" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V557" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="W557" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X557" s="2" t="n">
+        <v>8613</v>
+      </c>
+      <c r="Y557" s="2" t="inlineStr">
+        <is>
+          <t>8.6s</t>
+        </is>
+      </c>
+      <c r="Z557" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA557" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB557" s="2" t="inlineStr"/>
+      <c r="AC557" s="2" t="inlineStr"/>
+      <c r="AD557" s="2" t="inlineStr"/>
+      <c r="AE557" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF557" s="2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="AG557" s="2" t="n">
+        <v>615</v>
+      </c>
+      <c r="AH557" s="2" t="n">
+        <v>2614</v>
+      </c>
+      <c r="AI557" s="2" t="n">
+        <v>6099</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B558" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="C558" s="4" t="inlineStr">
+        <is>
+          <t>translationjob1872</t>
+        </is>
+      </c>
+      <c r="D558" s="4" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E558" s="4" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F558" s="4" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G558" s="4" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H558" s="4" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I558" s="4" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J558" s="4" t="inlineStr">
+        <is>
+          <t>22:14:28.185</t>
+        </is>
+      </c>
+      <c r="K558" s="4" t="inlineStr">
+        <is>
+          <t>22:14:28.210</t>
+        </is>
+      </c>
+      <c r="L558" s="4" t="inlineStr">
+        <is>
+          <t>22:14:28.385</t>
+        </is>
+      </c>
+      <c r="M558" s="4" t="inlineStr">
+        <is>
+          <t>22:14:28.702</t>
+        </is>
+      </c>
+      <c r="N558" s="4" t="inlineStr"/>
+      <c r="O558" s="4" t="inlineStr"/>
+      <c r="P558" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q558" s="4" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R558" s="4" t="n">
+        <v>517</v>
+      </c>
+      <c r="S558" s="4" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="T558" s="4" t="inlineStr"/>
+      <c r="U558" s="4" t="inlineStr"/>
+      <c r="V558" s="4" t="inlineStr"/>
+      <c r="W558" s="4" t="inlineStr"/>
+      <c r="X558" s="4" t="inlineStr"/>
+      <c r="Y558" s="4" t="inlineStr"/>
+      <c r="Z558" s="4" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:0, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA558" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB558" s="4" t="inlineStr"/>
+      <c r="AC558" s="4" t="inlineStr"/>
+      <c r="AD558" s="4" t="inlineStr"/>
+      <c r="AE558" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF558" s="4" t="n">
+        <v>7826</v>
+      </c>
+      <c r="AG558" s="4" t="n">
+        <v>2836</v>
+      </c>
+      <c r="AH558" s="4" t="n">
+        <v>10662</v>
+      </c>
+      <c r="AI558" s="4" t="n">
+        <v>6959</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B559" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1873</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F559" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G559" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H559" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I559" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J559" s="2" t="inlineStr">
+        <is>
+          <t>22:14:32.357</t>
+        </is>
+      </c>
+      <c r="K559" s="2" t="inlineStr">
+        <is>
+          <t>22:14:32.360</t>
+        </is>
+      </c>
+      <c r="L559" s="2" t="inlineStr">
+        <is>
+          <t>22:14:32.924</t>
+        </is>
+      </c>
+      <c r="M559" s="2" t="inlineStr">
+        <is>
+          <t>22:14:42.191</t>
+        </is>
+      </c>
+      <c r="N559" s="2" t="inlineStr">
+        <is>
+          <t>22:14:42.267</t>
+        </is>
+      </c>
+      <c r="O559" s="2" t="inlineStr">
+        <is>
+          <t>22:14:42.736</t>
+        </is>
+      </c>
+      <c r="P559" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="Q559" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R559" s="2" t="n">
+        <v>9834</v>
+      </c>
+      <c r="S559" s="2" t="inlineStr">
+        <is>
+          <t>9.8s</t>
+        </is>
+      </c>
+      <c r="T559" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U559" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V559" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="W559" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="X559" s="2" t="n">
+        <v>10379</v>
+      </c>
+      <c r="Y559" s="2" t="inlineStr">
+        <is>
+          <t>10.4s</t>
+        </is>
+      </c>
+      <c r="Z559" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA559" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB559" s="2" t="inlineStr"/>
+      <c r="AC559" s="2" t="inlineStr"/>
+      <c r="AD559" s="2" t="inlineStr"/>
+      <c r="AE559" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF559" s="2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="AG559" s="2" t="n">
+        <v>615</v>
+      </c>
+      <c r="AH559" s="2" t="n">
+        <v>2614</v>
+      </c>
+      <c r="AI559" s="2" t="n">
+        <v>6099</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1874</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G560" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H560" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I560" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J560" s="2" t="inlineStr">
+        <is>
+          <t>22:14:47.555</t>
+        </is>
+      </c>
+      <c r="K560" s="2" t="inlineStr">
+        <is>
+          <t>22:14:47.583</t>
+        </is>
+      </c>
+      <c r="L560" s="2" t="inlineStr">
+        <is>
+          <t>22:14:48.663</t>
+        </is>
+      </c>
+      <c r="M560" s="2" t="inlineStr">
+        <is>
+          <t>22:14:55.313</t>
+        </is>
+      </c>
+      <c r="N560" s="2" t="inlineStr">
+        <is>
+          <t>22:14:55.398</t>
+        </is>
+      </c>
+      <c r="O560" s="2" t="inlineStr">
+        <is>
+          <t>22:14:55.610</t>
+        </is>
+      </c>
+      <c r="P560" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="Q560" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R560" s="2" t="n">
+        <v>7758</v>
+      </c>
+      <c r="S560" s="2" t="inlineStr">
+        <is>
+          <t>7.8s</t>
+        </is>
+      </c>
+      <c r="T560" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="U560" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V560" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="W560" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X560" s="2" t="n">
+        <v>8055</v>
+      </c>
+      <c r="Y560" s="2" t="inlineStr">
+        <is>
+          <t>8.1s</t>
+        </is>
+      </c>
+      <c r="Z560" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA560" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB560" s="2" t="inlineStr"/>
+      <c r="AC560" s="2" t="inlineStr"/>
+      <c r="AD560" s="2" t="inlineStr"/>
+      <c r="AE560" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF560" s="2" t="n">
+        <v>7826</v>
+      </c>
+      <c r="AG560" s="2" t="n">
+        <v>2836</v>
+      </c>
+      <c r="AH560" s="2" t="n">
+        <v>10662</v>
+      </c>
+      <c r="AI560" s="2" t="n">
+        <v>6959</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B561" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C561" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1875</t>
+        </is>
+      </c>
+      <c r="D561" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F561" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G561" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H561" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I561" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J561" s="2" t="inlineStr">
+        <is>
+          <t>22:15:00.309</t>
+        </is>
+      </c>
+      <c r="K561" s="2" t="inlineStr">
+        <is>
+          <t>22:15:00.333</t>
+        </is>
+      </c>
+      <c r="L561" s="2" t="inlineStr">
+        <is>
+          <t>22:15:00.859</t>
+        </is>
+      </c>
+      <c r="M561" s="2" t="inlineStr">
+        <is>
+          <t>22:15:10.005</t>
+        </is>
+      </c>
+      <c r="N561" s="2" t="inlineStr">
+        <is>
+          <t>22:15:10.093</t>
+        </is>
+      </c>
+      <c r="O561" s="2" t="inlineStr">
+        <is>
+          <t>22:15:10.574</t>
+        </is>
+      </c>
+      <c r="P561" s="2" t="n">
+        <v>526</v>
+      </c>
+      <c r="Q561" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R561" s="2" t="n">
+        <v>9696</v>
+      </c>
+      <c r="S561" s="2" t="inlineStr">
+        <is>
+          <t>9.7s</t>
+        </is>
+      </c>
+      <c r="T561" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="U561" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V561" s="2" t="n">
+        <v>481</v>
+      </c>
+      <c r="W561" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="X561" s="2" t="n">
+        <v>10265</v>
+      </c>
+      <c r="Y561" s="2" t="inlineStr">
+        <is>
+          <t>10.3s</t>
+        </is>
+      </c>
+      <c r="Z561" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA561" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB561" s="2" t="inlineStr"/>
+      <c r="AC561" s="2" t="inlineStr"/>
+      <c r="AD561" s="2" t="inlineStr"/>
+      <c r="AE561" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF561" s="2" t="n">
+        <v>7826</v>
+      </c>
+      <c r="AG561" s="2" t="n">
+        <v>2836</v>
+      </c>
+      <c r="AH561" s="2" t="n">
+        <v>10662</v>
+      </c>
+      <c r="AI561" s="2" t="n">
+        <v>6959</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AI501"/>
+  <autoFilter ref="A1:AI561"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -68552,7 +76934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68903,6 +77285,58 @@
         <v>1239161</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>22.6s</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>326</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>522927</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>94804</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>617731</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -68914,7 +77348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -68923,6 +77357,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -68956,6 +77391,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -68978,6 +77418,9 @@
       <c r="F2" s="7" t="n">
         <v>8893</v>
       </c>
+      <c r="G2" s="7" t="n">
+        <v>8893</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -69000,6 +77443,9 @@
       <c r="F3" s="6" t="n">
         <v>47</v>
       </c>
+      <c r="G3" s="6" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -69022,6 +77468,9 @@
       <c r="F4" s="6" t="n">
         <v>28</v>
       </c>
+      <c r="G4" s="6" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -69044,6 +77493,9 @@
       <c r="F5" s="7" t="n">
         <v>124</v>
       </c>
+      <c r="G5" s="7" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -69066,6 +77518,9 @@
       <c r="F6" s="7" t="n">
         <v>887</v>
       </c>
+      <c r="G6" s="7" t="n">
+        <v>887</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -69088,6 +77543,9 @@
       <c r="F7" s="7" t="n">
         <v>162</v>
       </c>
+      <c r="G7" s="7" t="n">
+        <v>162</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -69110,6 +77568,9 @@
       <c r="F8" s="7" t="n">
         <v>161</v>
       </c>
+      <c r="G8" s="7" t="n">
+        <v>161</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -69132,6 +77593,9 @@
       <c r="F9" s="7" t="n">
         <v>120362</v>
       </c>
+      <c r="G9" s="7" t="n">
+        <v>120362</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -69154,6 +77618,9 @@
       <c r="F10" s="7" t="n">
         <v>44948</v>
       </c>
+      <c r="G10" s="7" t="n">
+        <v>44948</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -69176,6 +77643,9 @@
       <c r="F11" s="7" t="n">
         <v>2112</v>
       </c>
+      <c r="G11" s="7" t="n">
+        <v>2112</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -69198,6 +77668,9 @@
       <c r="F12" s="7" t="n">
         <v>1830</v>
       </c>
+      <c r="G12" s="7" t="n">
+        <v>1830</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -69220,6 +77693,9 @@
       <c r="F13" s="7" t="n">
         <v>6226</v>
       </c>
+      <c r="G13" s="7" t="n">
+        <v>6226</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -69240,6 +77716,9 @@
         <v>167</v>
       </c>
       <c r="F14" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="G14" s="6" t="n">
         <v>27</v>
       </c>
     </row>
@@ -69254,7 +77733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -69428,6 +77907,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>370</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>370</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>370</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/translation_jobs_all_days.xlsx
+++ b/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AI$325</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AI$386</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI325"/>
+  <dimension ref="A1:AI386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -46212,8 +46212,8463 @@
         <v>1343</v>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2543</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr">
+        <is>
+          <t>09:10:50.105</t>
+        </is>
+      </c>
+      <c r="K326" s="2" t="inlineStr">
+        <is>
+          <t>09:10:50.129</t>
+        </is>
+      </c>
+      <c r="L326" s="2" t="inlineStr">
+        <is>
+          <t>09:10:50.397</t>
+        </is>
+      </c>
+      <c r="M326" s="2" t="inlineStr">
+        <is>
+          <t>09:10:54.841</t>
+        </is>
+      </c>
+      <c r="N326" s="2" t="inlineStr">
+        <is>
+          <t>09:10:54.887</t>
+        </is>
+      </c>
+      <c r="O326" s="2" t="inlineStr">
+        <is>
+          <t>09:10:54.954</t>
+        </is>
+      </c>
+      <c r="P326" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="Q326" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R326" s="2" t="n">
+        <v>4736</v>
+      </c>
+      <c r="S326" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="T326" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U326" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V326" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W326" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X326" s="2" t="n">
+        <v>4849</v>
+      </c>
+      <c r="Y326" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="Z326" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA326" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB326" s="2" t="inlineStr"/>
+      <c r="AC326" s="2" t="inlineStr"/>
+      <c r="AD326" s="2" t="inlineStr"/>
+      <c r="AE326" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF326" s="2" t="n">
+        <v>9081</v>
+      </c>
+      <c r="AG326" s="2" t="n">
+        <v>1125</v>
+      </c>
+      <c r="AH326" s="2" t="n">
+        <v>10206</v>
+      </c>
+      <c r="AI326" s="2" t="n">
+        <v>3401</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2544</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr">
+        <is>
+          <t>09:10:59.623</t>
+        </is>
+      </c>
+      <c r="K327" s="2" t="inlineStr">
+        <is>
+          <t>09:10:59.642</t>
+        </is>
+      </c>
+      <c r="L327" s="2" t="inlineStr">
+        <is>
+          <t>09:10:59.872</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="inlineStr">
+        <is>
+          <t>09:11:02.533</t>
+        </is>
+      </c>
+      <c r="N327" s="2" t="inlineStr">
+        <is>
+          <t>09:11:02.588</t>
+        </is>
+      </c>
+      <c r="O327" s="2" t="inlineStr">
+        <is>
+          <t>09:11:02.660</t>
+        </is>
+      </c>
+      <c r="P327" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q327" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R327" s="2" t="n">
+        <v>2910</v>
+      </c>
+      <c r="S327" s="2" t="inlineStr">
+        <is>
+          <t>2.9s</t>
+        </is>
+      </c>
+      <c r="T327" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U327" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V327" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="W327" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X327" s="2" t="n">
+        <v>3037</v>
+      </c>
+      <c r="Y327" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="Z327" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA327" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB327" s="2" t="inlineStr"/>
+      <c r="AC327" s="2" t="inlineStr"/>
+      <c r="AD327" s="2" t="inlineStr"/>
+      <c r="AE327" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF327" s="2" t="n">
+        <v>9081</v>
+      </c>
+      <c r="AG327" s="2" t="n">
+        <v>1125</v>
+      </c>
+      <c r="AH327" s="2" t="n">
+        <v>10206</v>
+      </c>
+      <c r="AI327" s="2" t="n">
+        <v>3401</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2545</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr">
+        <is>
+          <t>09:11:07.399</t>
+        </is>
+      </c>
+      <c r="K328" s="2" t="inlineStr">
+        <is>
+          <t>09:11:07.418</t>
+        </is>
+      </c>
+      <c r="L328" s="2" t="inlineStr">
+        <is>
+          <t>09:11:07.642</t>
+        </is>
+      </c>
+      <c r="M328" s="2" t="inlineStr">
+        <is>
+          <t>09:11:13.624</t>
+        </is>
+      </c>
+      <c r="N328" s="2" t="inlineStr">
+        <is>
+          <t>09:11:13.675</t>
+        </is>
+      </c>
+      <c r="O328" s="2" t="inlineStr">
+        <is>
+          <t>09:11:13.732</t>
+        </is>
+      </c>
+      <c r="P328" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q328" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R328" s="2" t="n">
+        <v>6225</v>
+      </c>
+      <c r="S328" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="T328" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U328" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V328" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="W328" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X328" s="2" t="n">
+        <v>6333</v>
+      </c>
+      <c r="Y328" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="Z328" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA328" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB328" s="2" t="inlineStr"/>
+      <c r="AC328" s="2" t="inlineStr"/>
+      <c r="AD328" s="2" t="inlineStr"/>
+      <c r="AE328" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF328" s="2" t="n">
+        <v>9081</v>
+      </c>
+      <c r="AG328" s="2" t="n">
+        <v>1125</v>
+      </c>
+      <c r="AH328" s="2" t="n">
+        <v>10206</v>
+      </c>
+      <c r="AI328" s="2" t="n">
+        <v>3401</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2546</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr">
+        <is>
+          <t>09:11:18.344</t>
+        </is>
+      </c>
+      <c r="K329" s="2" t="inlineStr">
+        <is>
+          <t>09:11:18.365</t>
+        </is>
+      </c>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t>09:11:18.588</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="inlineStr">
+        <is>
+          <t>09:11:21.787</t>
+        </is>
+      </c>
+      <c r="N329" s="2" t="inlineStr">
+        <is>
+          <t>09:11:21.831</t>
+        </is>
+      </c>
+      <c r="O329" s="2" t="inlineStr">
+        <is>
+          <t>09:11:21.899</t>
+        </is>
+      </c>
+      <c r="P329" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R329" s="2" t="n">
+        <v>3443</v>
+      </c>
+      <c r="S329" s="2" t="inlineStr">
+        <is>
+          <t>3.4s</t>
+        </is>
+      </c>
+      <c r="T329" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U329" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V329" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="W329" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X329" s="2" t="n">
+        <v>3555</v>
+      </c>
+      <c r="Y329" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="Z329" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA329" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB329" s="2" t="inlineStr"/>
+      <c r="AC329" s="2" t="inlineStr"/>
+      <c r="AD329" s="2" t="inlineStr"/>
+      <c r="AE329" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF329" s="2" t="n">
+        <v>9081</v>
+      </c>
+      <c r="AG329" s="2" t="n">
+        <v>1125</v>
+      </c>
+      <c r="AH329" s="2" t="n">
+        <v>10206</v>
+      </c>
+      <c r="AI329" s="2" t="n">
+        <v>3401</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2547</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr">
+        <is>
+          <t>09:11:26.549</t>
+        </is>
+      </c>
+      <c r="K330" s="2" t="inlineStr">
+        <is>
+          <t>09:11:26.570</t>
+        </is>
+      </c>
+      <c r="L330" s="2" t="inlineStr">
+        <is>
+          <t>09:11:26.845</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="inlineStr">
+        <is>
+          <t>09:11:29.707</t>
+        </is>
+      </c>
+      <c r="N330" s="2" t="inlineStr">
+        <is>
+          <t>09:11:29.768</t>
+        </is>
+      </c>
+      <c r="O330" s="2" t="inlineStr">
+        <is>
+          <t>09:11:29.824</t>
+        </is>
+      </c>
+      <c r="P330" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q330" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R330" s="2" t="n">
+        <v>3158</v>
+      </c>
+      <c r="S330" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="T330" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U330" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V330" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="W330" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X330" s="2" t="n">
+        <v>3275</v>
+      </c>
+      <c r="Y330" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="Z330" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA330" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB330" s="2" t="inlineStr"/>
+      <c r="AC330" s="2" t="inlineStr"/>
+      <c r="AD330" s="2" t="inlineStr"/>
+      <c r="AE330" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF330" s="2" t="n">
+        <v>9081</v>
+      </c>
+      <c r="AG330" s="2" t="n">
+        <v>1125</v>
+      </c>
+      <c r="AH330" s="2" t="n">
+        <v>10206</v>
+      </c>
+      <c r="AI330" s="2" t="n">
+        <v>3401</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2548</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr">
+        <is>
+          <t>09:11:34.793</t>
+        </is>
+      </c>
+      <c r="K331" s="2" t="inlineStr">
+        <is>
+          <t>09:11:34.812</t>
+        </is>
+      </c>
+      <c r="L331" s="2" t="inlineStr">
+        <is>
+          <t>09:11:35.054</t>
+        </is>
+      </c>
+      <c r="M331" s="2" t="inlineStr">
+        <is>
+          <t>09:11:40.091</t>
+        </is>
+      </c>
+      <c r="N331" s="2" t="inlineStr">
+        <is>
+          <t>09:11:40.137</t>
+        </is>
+      </c>
+      <c r="O331" s="2" t="inlineStr">
+        <is>
+          <t>09:11:40.196</t>
+        </is>
+      </c>
+      <c r="P331" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R331" s="2" t="n">
+        <v>5298</v>
+      </c>
+      <c r="S331" s="2" t="inlineStr">
+        <is>
+          <t>5.3s</t>
+        </is>
+      </c>
+      <c r="T331" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U331" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V331" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="W331" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X331" s="2" t="n">
+        <v>5403</v>
+      </c>
+      <c r="Y331" s="2" t="inlineStr">
+        <is>
+          <t>5.4s</t>
+        </is>
+      </c>
+      <c r="Z331" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA331" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB331" s="2" t="inlineStr"/>
+      <c r="AC331" s="2" t="inlineStr"/>
+      <c r="AD331" s="2" t="inlineStr"/>
+      <c r="AE331" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF331" s="2" t="n">
+        <v>9081</v>
+      </c>
+      <c r="AG331" s="2" t="n">
+        <v>1125</v>
+      </c>
+      <c r="AH331" s="2" t="n">
+        <v>10206</v>
+      </c>
+      <c r="AI331" s="2" t="n">
+        <v>3401</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2549</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr">
+        <is>
+          <t>10:23:36.858</t>
+        </is>
+      </c>
+      <c r="K332" s="2" t="inlineStr">
+        <is>
+          <t>10:23:36.876</t>
+        </is>
+      </c>
+      <c r="L332" s="2" t="inlineStr">
+        <is>
+          <t>10:23:41.685</t>
+        </is>
+      </c>
+      <c r="M332" s="2" t="inlineStr">
+        <is>
+          <t>10:23:53.514</t>
+        </is>
+      </c>
+      <c r="N332" s="2" t="inlineStr">
+        <is>
+          <t>10:23:53.591</t>
+        </is>
+      </c>
+      <c r="O332" s="2" t="inlineStr">
+        <is>
+          <t>10:23:55.372</t>
+        </is>
+      </c>
+      <c r="P332" s="2" t="n">
+        <v>4809</v>
+      </c>
+      <c r="Q332" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="R332" s="2" t="n">
+        <v>16656</v>
+      </c>
+      <c r="S332" s="2" t="inlineStr">
+        <is>
+          <t>16.7s</t>
+        </is>
+      </c>
+      <c r="T332" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="U332" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V332" s="2" t="n">
+        <v>1781</v>
+      </c>
+      <c r="W332" s="2" t="inlineStr">
+        <is>
+          <t>1.8s</t>
+        </is>
+      </c>
+      <c r="X332" s="2" t="n">
+        <v>18514</v>
+      </c>
+      <c r="Y332" s="2" t="inlineStr">
+        <is>
+          <t>18.5s</t>
+        </is>
+      </c>
+      <c r="Z332" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:19, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA332" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB332" s="2" t="inlineStr"/>
+      <c r="AC332" s="2" t="inlineStr"/>
+      <c r="AD332" s="2" t="inlineStr"/>
+      <c r="AE332" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF332" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="AG332" s="2" t="n">
+        <v>2070</v>
+      </c>
+      <c r="AH332" s="2" t="n">
+        <v>20070</v>
+      </c>
+      <c r="AI332" s="2" t="n">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2550</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="inlineStr">
+        <is>
+          <t>10:23:57.422</t>
+        </is>
+      </c>
+      <c r="K333" s="2" t="inlineStr">
+        <is>
+          <t>10:23:57.438</t>
+        </is>
+      </c>
+      <c r="L333" s="2" t="inlineStr">
+        <is>
+          <t>10:24:02.656</t>
+        </is>
+      </c>
+      <c r="M333" s="2" t="inlineStr">
+        <is>
+          <t>10:24:08.105</t>
+        </is>
+      </c>
+      <c r="N333" s="2" t="inlineStr">
+        <is>
+          <t>10:24:08.180</t>
+        </is>
+      </c>
+      <c r="O333" s="2" t="inlineStr">
+        <is>
+          <t>10:24:09.987</t>
+        </is>
+      </c>
+      <c r="P333" s="2" t="n">
+        <v>5218</v>
+      </c>
+      <c r="Q333" s="2" t="inlineStr">
+        <is>
+          <t>5.2s</t>
+        </is>
+      </c>
+      <c r="R333" s="2" t="n">
+        <v>10683</v>
+      </c>
+      <c r="S333" s="2" t="inlineStr">
+        <is>
+          <t>10.7s</t>
+        </is>
+      </c>
+      <c r="T333" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="U333" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V333" s="2" t="n">
+        <v>1807</v>
+      </c>
+      <c r="W333" s="2" t="inlineStr">
+        <is>
+          <t>1.8s</t>
+        </is>
+      </c>
+      <c r="X333" s="2" t="n">
+        <v>12565</v>
+      </c>
+      <c r="Y333" s="2" t="inlineStr">
+        <is>
+          <t>12.6s</t>
+        </is>
+      </c>
+      <c r="Z333" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:19, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA333" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB333" s="2" t="inlineStr"/>
+      <c r="AC333" s="2" t="inlineStr"/>
+      <c r="AD333" s="2" t="inlineStr"/>
+      <c r="AE333" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF333" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="AG333" s="2" t="n">
+        <v>2070</v>
+      </c>
+      <c r="AH333" s="2" t="n">
+        <v>20070</v>
+      </c>
+      <c r="AI333" s="2" t="n">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2551</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="inlineStr">
+        <is>
+          <t>10:24:12.152</t>
+        </is>
+      </c>
+      <c r="K334" s="2" t="inlineStr">
+        <is>
+          <t>10:24:12.169</t>
+        </is>
+      </c>
+      <c r="L334" s="2" t="inlineStr">
+        <is>
+          <t>10:24:16.996</t>
+        </is>
+      </c>
+      <c r="M334" s="2" t="inlineStr">
+        <is>
+          <t>10:24:26.057</t>
+        </is>
+      </c>
+      <c r="N334" s="2" t="inlineStr">
+        <is>
+          <t>10:24:26.119</t>
+        </is>
+      </c>
+      <c r="O334" s="2" t="inlineStr">
+        <is>
+          <t>10:24:28.015</t>
+        </is>
+      </c>
+      <c r="P334" s="2" t="n">
+        <v>4827</v>
+      </c>
+      <c r="Q334" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="R334" s="2" t="n">
+        <v>13905</v>
+      </c>
+      <c r="S334" s="2" t="inlineStr">
+        <is>
+          <t>13.9s</t>
+        </is>
+      </c>
+      <c r="T334" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U334" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V334" s="2" t="n">
+        <v>1896</v>
+      </c>
+      <c r="W334" s="2" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="X334" s="2" t="n">
+        <v>15863</v>
+      </c>
+      <c r="Y334" s="2" t="inlineStr">
+        <is>
+          <t>15.9s</t>
+        </is>
+      </c>
+      <c r="Z334" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:19, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA334" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB334" s="2" t="inlineStr"/>
+      <c r="AC334" s="2" t="inlineStr"/>
+      <c r="AD334" s="2" t="inlineStr"/>
+      <c r="AE334" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF334" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="AG334" s="2" t="n">
+        <v>2070</v>
+      </c>
+      <c r="AH334" s="2" t="n">
+        <v>20070</v>
+      </c>
+      <c r="AI334" s="2" t="n">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2552</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr">
+        <is>
+          <t>10:24:30.153</t>
+        </is>
+      </c>
+      <c r="K335" s="2" t="inlineStr">
+        <is>
+          <t>10:24:30.170</t>
+        </is>
+      </c>
+      <c r="L335" s="2" t="inlineStr">
+        <is>
+          <t>10:24:34.724</t>
+        </is>
+      </c>
+      <c r="M335" s="2" t="inlineStr">
+        <is>
+          <t>10:24:41.126</t>
+        </is>
+      </c>
+      <c r="N335" s="2" t="inlineStr">
+        <is>
+          <t>10:24:41.192</t>
+        </is>
+      </c>
+      <c r="O335" s="2" t="inlineStr">
+        <is>
+          <t>10:24:43.209</t>
+        </is>
+      </c>
+      <c r="P335" s="2" t="n">
+        <v>4554</v>
+      </c>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="R335" s="2" t="n">
+        <v>10973</v>
+      </c>
+      <c r="S335" s="2" t="inlineStr">
+        <is>
+          <t>11.0s</t>
+        </is>
+      </c>
+      <c r="T335" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U335" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V335" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="W335" s="2" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="X335" s="2" t="n">
+        <v>13056</v>
+      </c>
+      <c r="Y335" s="2" t="inlineStr">
+        <is>
+          <t>13.1s</t>
+        </is>
+      </c>
+      <c r="Z335" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:19, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA335" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB335" s="2" t="inlineStr"/>
+      <c r="AC335" s="2" t="inlineStr"/>
+      <c r="AD335" s="2" t="inlineStr"/>
+      <c r="AE335" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF335" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="AG335" s="2" t="n">
+        <v>2070</v>
+      </c>
+      <c r="AH335" s="2" t="n">
+        <v>20070</v>
+      </c>
+      <c r="AI335" s="2" t="n">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2553</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr">
+        <is>
+          <t>10:24:45.512</t>
+        </is>
+      </c>
+      <c r="K336" s="2" t="inlineStr">
+        <is>
+          <t>10:24:45.530</t>
+        </is>
+      </c>
+      <c r="L336" s="2" t="inlineStr">
+        <is>
+          <t>10:24:50.181</t>
+        </is>
+      </c>
+      <c r="M336" s="2" t="inlineStr">
+        <is>
+          <t>10:24:57.475</t>
+        </is>
+      </c>
+      <c r="N336" s="2" t="inlineStr">
+        <is>
+          <t>10:24:57.550</t>
+        </is>
+      </c>
+      <c r="O336" s="2" t="inlineStr">
+        <is>
+          <t>10:24:59.513</t>
+        </is>
+      </c>
+      <c r="P336" s="2" t="n">
+        <v>4651</v>
+      </c>
+      <c r="Q336" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="R336" s="2" t="n">
+        <v>11963</v>
+      </c>
+      <c r="S336" s="2" t="inlineStr">
+        <is>
+          <t>12.0s</t>
+        </is>
+      </c>
+      <c r="T336" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="U336" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V336" s="2" t="n">
+        <v>1963</v>
+      </c>
+      <c r="W336" s="2" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="X336" s="2" t="n">
+        <v>14001</v>
+      </c>
+      <c r="Y336" s="2" t="inlineStr">
+        <is>
+          <t>14.0s</t>
+        </is>
+      </c>
+      <c r="Z336" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:19, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA336" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB336" s="2" t="inlineStr"/>
+      <c r="AC336" s="2" t="inlineStr"/>
+      <c r="AD336" s="2" t="inlineStr"/>
+      <c r="AE336" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF336" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="AG336" s="2" t="n">
+        <v>2070</v>
+      </c>
+      <c r="AH336" s="2" t="n">
+        <v>20070</v>
+      </c>
+      <c r="AI336" s="2" t="n">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2554</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr">
+        <is>
+          <t>10:25:01.887</t>
+        </is>
+      </c>
+      <c r="K337" s="2" t="inlineStr">
+        <is>
+          <t>10:25:01.903</t>
+        </is>
+      </c>
+      <c r="L337" s="2" t="inlineStr">
+        <is>
+          <t>10:25:06.622</t>
+        </is>
+      </c>
+      <c r="M337" s="2" t="inlineStr">
+        <is>
+          <t>10:25:14.878</t>
+        </is>
+      </c>
+      <c r="N337" s="2" t="inlineStr">
+        <is>
+          <t>10:25:14.944</t>
+        </is>
+      </c>
+      <c r="O337" s="2" t="inlineStr">
+        <is>
+          <t>10:25:17.012</t>
+        </is>
+      </c>
+      <c r="P337" s="2" t="n">
+        <v>4719</v>
+      </c>
+      <c r="Q337" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="R337" s="2" t="n">
+        <v>12991</v>
+      </c>
+      <c r="S337" s="2" t="inlineStr">
+        <is>
+          <t>13.0s</t>
+        </is>
+      </c>
+      <c r="T337" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U337" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V337" s="2" t="n">
+        <v>2068</v>
+      </c>
+      <c r="W337" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="X337" s="2" t="n">
+        <v>15125</v>
+      </c>
+      <c r="Y337" s="2" t="inlineStr">
+        <is>
+          <t>15.1s</t>
+        </is>
+      </c>
+      <c r="Z337" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:19, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA337" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB337" s="2" t="inlineStr"/>
+      <c r="AC337" s="2" t="inlineStr"/>
+      <c r="AD337" s="2" t="inlineStr"/>
+      <c r="AE337" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF337" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="AG337" s="2" t="n">
+        <v>2070</v>
+      </c>
+      <c r="AH337" s="2" t="n">
+        <v>20070</v>
+      </c>
+      <c r="AI337" s="2" t="n">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2555</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr">
+        <is>
+          <t>11:15:12.559</t>
+        </is>
+      </c>
+      <c r="K338" s="2" t="inlineStr">
+        <is>
+          <t>11:15:12.579</t>
+        </is>
+      </c>
+      <c r="L338" s="2" t="inlineStr">
+        <is>
+          <t>11:15:13.343</t>
+        </is>
+      </c>
+      <c r="M338" s="2" t="inlineStr">
+        <is>
+          <t>11:15:28.002</t>
+        </is>
+      </c>
+      <c r="N338" s="2" t="inlineStr">
+        <is>
+          <t>11:15:28.058</t>
+        </is>
+      </c>
+      <c r="O338" s="2" t="inlineStr">
+        <is>
+          <t>11:15:28.215</t>
+        </is>
+      </c>
+      <c r="P338" s="2" t="n">
+        <v>764</v>
+      </c>
+      <c r="Q338" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R338" s="2" t="n">
+        <v>15443</v>
+      </c>
+      <c r="S338" s="2" t="inlineStr">
+        <is>
+          <t>15.4s</t>
+        </is>
+      </c>
+      <c r="T338" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U338" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V338" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="W338" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X338" s="2" t="n">
+        <v>15656</v>
+      </c>
+      <c r="Y338" s="2" t="inlineStr">
+        <is>
+          <t>15.7s</t>
+        </is>
+      </c>
+      <c r="Z338" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA338" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB338" s="2" t="inlineStr"/>
+      <c r="AC338" s="2" t="inlineStr"/>
+      <c r="AD338" s="2" t="inlineStr"/>
+      <c r="AE338" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF338" s="2" t="n">
+        <v>16419</v>
+      </c>
+      <c r="AG338" s="2" t="n">
+        <v>9456</v>
+      </c>
+      <c r="AH338" s="2" t="n">
+        <v>25875</v>
+      </c>
+      <c r="AI338" s="2" t="n">
+        <v>17584</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2556</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr">
+        <is>
+          <t>11:15:33.745</t>
+        </is>
+      </c>
+      <c r="K339" s="2" t="inlineStr">
+        <is>
+          <t>11:15:33.763</t>
+        </is>
+      </c>
+      <c r="L339" s="2" t="inlineStr">
+        <is>
+          <t>11:15:34.124</t>
+        </is>
+      </c>
+      <c r="M339" s="2" t="inlineStr">
+        <is>
+          <t>11:15:45.411</t>
+        </is>
+      </c>
+      <c r="N339" s="2" t="inlineStr">
+        <is>
+          <t>11:15:45.470</t>
+        </is>
+      </c>
+      <c r="O339" s="2" t="inlineStr">
+        <is>
+          <t>11:15:45.824</t>
+        </is>
+      </c>
+      <c r="P339" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="Q339" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R339" s="2" t="n">
+        <v>11666</v>
+      </c>
+      <c r="S339" s="2" t="inlineStr">
+        <is>
+          <t>11.7s</t>
+        </is>
+      </c>
+      <c r="T339" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U339" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V339" s="2" t="n">
+        <v>354</v>
+      </c>
+      <c r="W339" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="X339" s="2" t="n">
+        <v>12079</v>
+      </c>
+      <c r="Y339" s="2" t="inlineStr">
+        <is>
+          <t>12.1s</t>
+        </is>
+      </c>
+      <c r="Z339" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA339" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB339" s="2" t="inlineStr"/>
+      <c r="AC339" s="2" t="inlineStr"/>
+      <c r="AD339" s="2" t="inlineStr"/>
+      <c r="AE339" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF339" s="2" t="n">
+        <v>16419</v>
+      </c>
+      <c r="AG339" s="2" t="n">
+        <v>9456</v>
+      </c>
+      <c r="AH339" s="2" t="n">
+        <v>25875</v>
+      </c>
+      <c r="AI339" s="2" t="n">
+        <v>17584</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2557</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr">
+        <is>
+          <t>11:15:51.221</t>
+        </is>
+      </c>
+      <c r="K340" s="2" t="inlineStr">
+        <is>
+          <t>11:15:51.239</t>
+        </is>
+      </c>
+      <c r="L340" s="2" t="inlineStr">
+        <is>
+          <t>11:15:52.363</t>
+        </is>
+      </c>
+      <c r="M340" s="2" t="inlineStr">
+        <is>
+          <t>11:16:11.939</t>
+        </is>
+      </c>
+      <c r="N340" s="2" t="inlineStr">
+        <is>
+          <t>11:16:11.997</t>
+        </is>
+      </c>
+      <c r="O340" s="2" t="inlineStr">
+        <is>
+          <t>11:16:12.166</t>
+        </is>
+      </c>
+      <c r="P340" s="2" t="n">
+        <v>1124</v>
+      </c>
+      <c r="Q340" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R340" s="2" t="n">
+        <v>20718</v>
+      </c>
+      <c r="S340" s="2" t="inlineStr">
+        <is>
+          <t>20.7s</t>
+        </is>
+      </c>
+      <c r="T340" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U340" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V340" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="W340" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X340" s="2" t="n">
+        <v>20945</v>
+      </c>
+      <c r="Y340" s="2" t="inlineStr">
+        <is>
+          <t>20.9s</t>
+        </is>
+      </c>
+      <c r="Z340" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA340" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB340" s="2" t="inlineStr"/>
+      <c r="AC340" s="2" t="inlineStr"/>
+      <c r="AD340" s="2" t="inlineStr"/>
+      <c r="AE340" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF340" s="2" t="n">
+        <v>16419</v>
+      </c>
+      <c r="AG340" s="2" t="n">
+        <v>9456</v>
+      </c>
+      <c r="AH340" s="2" t="n">
+        <v>25875</v>
+      </c>
+      <c r="AI340" s="2" t="n">
+        <v>17584</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2558</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr">
+        <is>
+          <t>11:16:14.301</t>
+        </is>
+      </c>
+      <c r="K341" s="2" t="inlineStr">
+        <is>
+          <t>11:16:14.320</t>
+        </is>
+      </c>
+      <c r="L341" s="2" t="inlineStr">
+        <is>
+          <t>11:16:15.375</t>
+        </is>
+      </c>
+      <c r="M341" s="2" t="inlineStr">
+        <is>
+          <t>11:16:32.008</t>
+        </is>
+      </c>
+      <c r="N341" s="2" t="inlineStr">
+        <is>
+          <t>11:16:32.054</t>
+        </is>
+      </c>
+      <c r="O341" s="2" t="inlineStr">
+        <is>
+          <t>11:16:32.554</t>
+        </is>
+      </c>
+      <c r="P341" s="2" t="n">
+        <v>1055</v>
+      </c>
+      <c r="Q341" s="2" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R341" s="2" t="n">
+        <v>17707</v>
+      </c>
+      <c r="S341" s="2" t="inlineStr">
+        <is>
+          <t>17.7s</t>
+        </is>
+      </c>
+      <c r="T341" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U341" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V341" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="W341" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="X341" s="2" t="n">
+        <v>18253</v>
+      </c>
+      <c r="Y341" s="2" t="inlineStr">
+        <is>
+          <t>18.3s</t>
+        </is>
+      </c>
+      <c r="Z341" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA341" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB341" s="2" t="inlineStr"/>
+      <c r="AC341" s="2" t="inlineStr"/>
+      <c r="AD341" s="2" t="inlineStr"/>
+      <c r="AE341" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF341" s="2" t="n">
+        <v>16419</v>
+      </c>
+      <c r="AG341" s="2" t="n">
+        <v>9456</v>
+      </c>
+      <c r="AH341" s="2" t="n">
+        <v>25875</v>
+      </c>
+      <c r="AI341" s="2" t="n">
+        <v>17584</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2559</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr">
+        <is>
+          <t>11:16:33.754</t>
+        </is>
+      </c>
+      <c r="K342" s="2" t="inlineStr">
+        <is>
+          <t>11:16:33.773</t>
+        </is>
+      </c>
+      <c r="L342" s="2" t="inlineStr">
+        <is>
+          <t>11:16:34.296</t>
+        </is>
+      </c>
+      <c r="M342" s="2" t="inlineStr">
+        <is>
+          <t>11:16:56.912</t>
+        </is>
+      </c>
+      <c r="N342" s="2" t="inlineStr">
+        <is>
+          <t>11:16:57.156</t>
+        </is>
+      </c>
+      <c r="O342" s="2" t="inlineStr">
+        <is>
+          <t>11:16:57.315</t>
+        </is>
+      </c>
+      <c r="P342" s="2" t="n">
+        <v>523</v>
+      </c>
+      <c r="Q342" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R342" s="2" t="n">
+        <v>23158</v>
+      </c>
+      <c r="S342" s="2" t="inlineStr">
+        <is>
+          <t>23.2s</t>
+        </is>
+      </c>
+      <c r="T342" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="U342" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V342" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="W342" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X342" s="2" t="n">
+        <v>23561</v>
+      </c>
+      <c r="Y342" s="2" t="inlineStr">
+        <is>
+          <t>23.6s</t>
+        </is>
+      </c>
+      <c r="Z342" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA342" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB342" s="2" t="inlineStr"/>
+      <c r="AC342" s="2" t="inlineStr"/>
+      <c r="AD342" s="2" t="inlineStr"/>
+      <c r="AE342" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF342" s="2" t="n">
+        <v>16419</v>
+      </c>
+      <c r="AG342" s="2" t="n">
+        <v>9456</v>
+      </c>
+      <c r="AH342" s="2" t="n">
+        <v>25875</v>
+      </c>
+      <c r="AI342" s="2" t="n">
+        <v>17584</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2560</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr">
+        <is>
+          <t>11:16:59.597</t>
+        </is>
+      </c>
+      <c r="K343" s="2" t="inlineStr">
+        <is>
+          <t>11:16:59.621</t>
+        </is>
+      </c>
+      <c r="L343" s="2" t="inlineStr">
+        <is>
+          <t>11:17:00.192</t>
+        </is>
+      </c>
+      <c r="M343" s="2" t="inlineStr">
+        <is>
+          <t>11:17:25.189</t>
+        </is>
+      </c>
+      <c r="N343" s="2" t="inlineStr">
+        <is>
+          <t>11:17:25.251</t>
+        </is>
+      </c>
+      <c r="O343" s="2" t="inlineStr">
+        <is>
+          <t>11:17:25.846</t>
+        </is>
+      </c>
+      <c r="P343" s="2" t="n">
+        <v>571</v>
+      </c>
+      <c r="Q343" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R343" s="2" t="n">
+        <v>25592</v>
+      </c>
+      <c r="S343" s="2" t="inlineStr">
+        <is>
+          <t>25.6s</t>
+        </is>
+      </c>
+      <c r="T343" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U343" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V343" s="2" t="n">
+        <v>595</v>
+      </c>
+      <c r="W343" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="X343" s="2" t="n">
+        <v>26249</v>
+      </c>
+      <c r="Y343" s="2" t="inlineStr">
+        <is>
+          <t>26.2s</t>
+        </is>
+      </c>
+      <c r="Z343" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA343" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB343" s="2" t="inlineStr"/>
+      <c r="AC343" s="2" t="inlineStr"/>
+      <c r="AD343" s="2" t="inlineStr"/>
+      <c r="AE343" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF343" s="2" t="n">
+        <v>16419</v>
+      </c>
+      <c r="AG343" s="2" t="n">
+        <v>9456</v>
+      </c>
+      <c r="AH343" s="2" t="n">
+        <v>25875</v>
+      </c>
+      <c r="AI343" s="2" t="n">
+        <v>17584</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2561</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr">
+        <is>
+          <t>11:22:02.618</t>
+        </is>
+      </c>
+      <c r="K344" s="2" t="inlineStr">
+        <is>
+          <t>11:22:02.644</t>
+        </is>
+      </c>
+      <c r="L344" s="2" t="inlineStr">
+        <is>
+          <t>11:22:03.187</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="inlineStr">
+        <is>
+          <t>11:22:05.666</t>
+        </is>
+      </c>
+      <c r="N344" s="2" t="inlineStr">
+        <is>
+          <t>11:22:05.712</t>
+        </is>
+      </c>
+      <c r="O344" s="2" t="inlineStr">
+        <is>
+          <t>11:22:05.771</t>
+        </is>
+      </c>
+      <c r="P344" s="2" t="n">
+        <v>543</v>
+      </c>
+      <c r="Q344" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R344" s="2" t="n">
+        <v>3048</v>
+      </c>
+      <c r="S344" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="T344" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U344" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V344" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="W344" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X344" s="2" t="n">
+        <v>3153</v>
+      </c>
+      <c r="Y344" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="Z344" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA344" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB344" s="2" t="inlineStr"/>
+      <c r="AC344" s="2" t="inlineStr"/>
+      <c r="AD344" s="2" t="inlineStr"/>
+      <c r="AE344" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF344" s="2" t="n">
+        <v>8331</v>
+      </c>
+      <c r="AG344" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="AH344" s="2" t="n">
+        <v>8625</v>
+      </c>
+      <c r="AI344" s="2" t="n">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2562</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr">
+        <is>
+          <t>11:22:10.700</t>
+        </is>
+      </c>
+      <c r="K345" s="2" t="inlineStr">
+        <is>
+          <t>11:22:10.735</t>
+        </is>
+      </c>
+      <c r="L345" s="2" t="inlineStr">
+        <is>
+          <t>11:22:10.936</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="inlineStr">
+        <is>
+          <t>11:22:13.334</t>
+        </is>
+      </c>
+      <c r="N345" s="2" t="inlineStr">
+        <is>
+          <t>11:22:13.386</t>
+        </is>
+      </c>
+      <c r="O345" s="2" t="inlineStr">
+        <is>
+          <t>11:22:13.441</t>
+        </is>
+      </c>
+      <c r="P345" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q345" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R345" s="2" t="n">
+        <v>2634</v>
+      </c>
+      <c r="S345" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="T345" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U345" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V345" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W345" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X345" s="2" t="n">
+        <v>2741</v>
+      </c>
+      <c r="Y345" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="Z345" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA345" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB345" s="2" t="inlineStr"/>
+      <c r="AC345" s="2" t="inlineStr"/>
+      <c r="AD345" s="2" t="inlineStr"/>
+      <c r="AE345" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF345" s="2" t="n">
+        <v>8331</v>
+      </c>
+      <c r="AG345" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="AH345" s="2" t="n">
+        <v>8625</v>
+      </c>
+      <c r="AI345" s="2" t="n">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2563</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr">
+        <is>
+          <t>11:22:18.455</t>
+        </is>
+      </c>
+      <c r="K346" s="2" t="inlineStr">
+        <is>
+          <t>11:22:18.480</t>
+        </is>
+      </c>
+      <c r="L346" s="2" t="inlineStr">
+        <is>
+          <t>11:22:18.876</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="inlineStr">
+        <is>
+          <t>11:22:21.505</t>
+        </is>
+      </c>
+      <c r="N346" s="2" t="inlineStr">
+        <is>
+          <t>11:22:21.553</t>
+        </is>
+      </c>
+      <c r="O346" s="2" t="inlineStr">
+        <is>
+          <t>11:22:21.608</t>
+        </is>
+      </c>
+      <c r="P346" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="Q346" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R346" s="2" t="n">
+        <v>3050</v>
+      </c>
+      <c r="S346" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="T346" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U346" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V346" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W346" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X346" s="2" t="n">
+        <v>3153</v>
+      </c>
+      <c r="Y346" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="Z346" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA346" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB346" s="2" t="inlineStr"/>
+      <c r="AC346" s="2" t="inlineStr"/>
+      <c r="AD346" s="2" t="inlineStr"/>
+      <c r="AE346" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF346" s="2" t="n">
+        <v>8331</v>
+      </c>
+      <c r="AG346" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="AH346" s="2" t="n">
+        <v>8625</v>
+      </c>
+      <c r="AI346" s="2" t="n">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2564</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr">
+        <is>
+          <t>11:22:26.405</t>
+        </is>
+      </c>
+      <c r="K347" s="2" t="inlineStr">
+        <is>
+          <t>11:22:26.423</t>
+        </is>
+      </c>
+      <c r="L347" s="2" t="inlineStr">
+        <is>
+          <t>11:22:26.778</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="inlineStr">
+        <is>
+          <t>11:22:29.077</t>
+        </is>
+      </c>
+      <c r="N347" s="2" t="inlineStr">
+        <is>
+          <t>11:22:29.327</t>
+        </is>
+      </c>
+      <c r="O347" s="2" t="inlineStr">
+        <is>
+          <t>11:22:29.385</t>
+        </is>
+      </c>
+      <c r="P347" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="Q347" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R347" s="2" t="n">
+        <v>2672</v>
+      </c>
+      <c r="S347" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="T347" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="U347" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V347" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W347" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X347" s="2" t="n">
+        <v>2980</v>
+      </c>
+      <c r="Y347" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="Z347" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA347" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB347" s="2" t="inlineStr"/>
+      <c r="AC347" s="2" t="inlineStr"/>
+      <c r="AD347" s="2" t="inlineStr"/>
+      <c r="AE347" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF347" s="2" t="n">
+        <v>8331</v>
+      </c>
+      <c r="AG347" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="AH347" s="2" t="n">
+        <v>8625</v>
+      </c>
+      <c r="AI347" s="2" t="n">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2565</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="inlineStr">
+        <is>
+          <t>11:22:35.000</t>
+        </is>
+      </c>
+      <c r="K348" s="2" t="inlineStr">
+        <is>
+          <t>11:22:35.022</t>
+        </is>
+      </c>
+      <c r="L348" s="2" t="inlineStr">
+        <is>
+          <t>11:22:35.228</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="inlineStr">
+        <is>
+          <t>11:22:37.258</t>
+        </is>
+      </c>
+      <c r="N348" s="2" t="inlineStr">
+        <is>
+          <t>11:22:37.309</t>
+        </is>
+      </c>
+      <c r="O348" s="2" t="inlineStr">
+        <is>
+          <t>11:22:37.359</t>
+        </is>
+      </c>
+      <c r="P348" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="Q348" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R348" s="2" t="n">
+        <v>2258</v>
+      </c>
+      <c r="S348" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="T348" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="U348" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V348" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="W348" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X348" s="2" t="n">
+        <v>2359</v>
+      </c>
+      <c r="Y348" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="Z348" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA348" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB348" s="2" t="inlineStr"/>
+      <c r="AC348" s="2" t="inlineStr"/>
+      <c r="AD348" s="2" t="inlineStr"/>
+      <c r="AE348" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF348" s="2" t="n">
+        <v>8331</v>
+      </c>
+      <c r="AG348" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="AH348" s="2" t="n">
+        <v>8625</v>
+      </c>
+      <c r="AI348" s="2" t="n">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2566</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr">
+        <is>
+          <t>11:22:41.870</t>
+        </is>
+      </c>
+      <c r="K349" s="2" t="inlineStr">
+        <is>
+          <t>11:22:41.893</t>
+        </is>
+      </c>
+      <c r="L349" s="2" t="inlineStr">
+        <is>
+          <t>11:22:42.103</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="inlineStr">
+        <is>
+          <t>11:22:43.957</t>
+        </is>
+      </c>
+      <c r="N349" s="2" t="inlineStr">
+        <is>
+          <t>11:22:44.011</t>
+        </is>
+      </c>
+      <c r="O349" s="2" t="inlineStr">
+        <is>
+          <t>11:22:44.067</t>
+        </is>
+      </c>
+      <c r="P349" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q349" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R349" s="2" t="n">
+        <v>2087</v>
+      </c>
+      <c r="S349" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="T349" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="U349" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V349" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="W349" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X349" s="2" t="n">
+        <v>2197</v>
+      </c>
+      <c r="Y349" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="Z349" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA349" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB349" s="2" t="inlineStr"/>
+      <c r="AC349" s="2" t="inlineStr"/>
+      <c r="AD349" s="2" t="inlineStr"/>
+      <c r="AE349" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF349" s="2" t="n">
+        <v>8331</v>
+      </c>
+      <c r="AG349" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="AH349" s="2" t="n">
+        <v>8625</v>
+      </c>
+      <c r="AI349" s="2" t="n">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2567</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr">
+        <is>
+          <t>12:00:02.721</t>
+        </is>
+      </c>
+      <c r="K350" s="2" t="inlineStr">
+        <is>
+          <t>12:00:02.737</t>
+        </is>
+      </c>
+      <c r="L350" s="2" t="inlineStr">
+        <is>
+          <t>12:00:10.382</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="inlineStr">
+        <is>
+          <t>12:00:19.506</t>
+        </is>
+      </c>
+      <c r="N350" s="2" t="inlineStr">
+        <is>
+          <t>12:00:19.607</t>
+        </is>
+      </c>
+      <c r="O350" s="2" t="inlineStr">
+        <is>
+          <t>12:00:21.700</t>
+        </is>
+      </c>
+      <c r="P350" s="2" t="n">
+        <v>7645</v>
+      </c>
+      <c r="Q350" s="2" t="inlineStr">
+        <is>
+          <t>7.6s</t>
+        </is>
+      </c>
+      <c r="R350" s="2" t="n">
+        <v>16785</v>
+      </c>
+      <c r="S350" s="2" t="inlineStr">
+        <is>
+          <t>16.8s</t>
+        </is>
+      </c>
+      <c r="T350" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="U350" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V350" s="2" t="n">
+        <v>2093</v>
+      </c>
+      <c r="W350" s="2" t="inlineStr">
+        <is>
+          <t>2.1s</t>
+        </is>
+      </c>
+      <c r="X350" s="2" t="n">
+        <v>18979</v>
+      </c>
+      <c r="Y350" s="2" t="inlineStr">
+        <is>
+          <t>19.0s</t>
+        </is>
+      </c>
+      <c r="Z350" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:16, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA350" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB350" s="2" t="inlineStr"/>
+      <c r="AC350" s="2" t="inlineStr"/>
+      <c r="AD350" s="2" t="inlineStr"/>
+      <c r="AE350" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF350" s="2" t="n">
+        <v>17688</v>
+      </c>
+      <c r="AG350" s="2" t="n">
+        <v>1709</v>
+      </c>
+      <c r="AH350" s="2" t="n">
+        <v>19397</v>
+      </c>
+      <c r="AI350" s="2" t="n">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2568</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J351" s="2" t="inlineStr">
+        <is>
+          <t>12:00:23.310</t>
+        </is>
+      </c>
+      <c r="K351" s="2" t="inlineStr">
+        <is>
+          <t>12:00:23.330</t>
+        </is>
+      </c>
+      <c r="L351" s="2" t="inlineStr">
+        <is>
+          <t>12:00:29.566</t>
+        </is>
+      </c>
+      <c r="M351" s="2" t="inlineStr">
+        <is>
+          <t>12:00:37.099</t>
+        </is>
+      </c>
+      <c r="N351" s="2" t="inlineStr">
+        <is>
+          <t>12:00:37.206</t>
+        </is>
+      </c>
+      <c r="O351" s="2" t="inlineStr">
+        <is>
+          <t>12:00:39.403</t>
+        </is>
+      </c>
+      <c r="P351" s="2" t="n">
+        <v>6236</v>
+      </c>
+      <c r="Q351" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="R351" s="2" t="n">
+        <v>13789</v>
+      </c>
+      <c r="S351" s="2" t="inlineStr">
+        <is>
+          <t>13.8s</t>
+        </is>
+      </c>
+      <c r="T351" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="U351" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V351" s="2" t="n">
+        <v>2197</v>
+      </c>
+      <c r="W351" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="X351" s="2" t="n">
+        <v>16093</v>
+      </c>
+      <c r="Y351" s="2" t="inlineStr">
+        <is>
+          <t>16.1s</t>
+        </is>
+      </c>
+      <c r="Z351" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:16, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA351" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB351" s="2" t="inlineStr"/>
+      <c r="AC351" s="2" t="inlineStr"/>
+      <c r="AD351" s="2" t="inlineStr"/>
+      <c r="AE351" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF351" s="2" t="n">
+        <v>17688</v>
+      </c>
+      <c r="AG351" s="2" t="n">
+        <v>1709</v>
+      </c>
+      <c r="AH351" s="2" t="n">
+        <v>19397</v>
+      </c>
+      <c r="AI351" s="2" t="n">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2569</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="inlineStr">
+        <is>
+          <t>12:00:42.350</t>
+        </is>
+      </c>
+      <c r="K352" s="2" t="inlineStr">
+        <is>
+          <t>12:00:42.373</t>
+        </is>
+      </c>
+      <c r="L352" s="2" t="inlineStr">
+        <is>
+          <t>12:00:52.019</t>
+        </is>
+      </c>
+      <c r="M352" s="2" t="inlineStr">
+        <is>
+          <t>12:01:00.662</t>
+        </is>
+      </c>
+      <c r="N352" s="2" t="inlineStr">
+        <is>
+          <t>12:01:00.758</t>
+        </is>
+      </c>
+      <c r="O352" s="2" t="inlineStr">
+        <is>
+          <t>12:01:03.107</t>
+        </is>
+      </c>
+      <c r="P352" s="2" t="n">
+        <v>9646</v>
+      </c>
+      <c r="Q352" s="2" t="inlineStr">
+        <is>
+          <t>9.6s</t>
+        </is>
+      </c>
+      <c r="R352" s="2" t="n">
+        <v>18312</v>
+      </c>
+      <c r="S352" s="2" t="inlineStr">
+        <is>
+          <t>18.3s</t>
+        </is>
+      </c>
+      <c r="T352" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="U352" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V352" s="2" t="n">
+        <v>2349</v>
+      </c>
+      <c r="W352" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="X352" s="2" t="n">
+        <v>20757</v>
+      </c>
+      <c r="Y352" s="2" t="inlineStr">
+        <is>
+          <t>20.8s</t>
+        </is>
+      </c>
+      <c r="Z352" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:16, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA352" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB352" s="2" t="inlineStr"/>
+      <c r="AC352" s="2" t="inlineStr"/>
+      <c r="AD352" s="2" t="inlineStr"/>
+      <c r="AE352" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF352" s="2" t="n">
+        <v>17688</v>
+      </c>
+      <c r="AG352" s="2" t="n">
+        <v>1709</v>
+      </c>
+      <c r="AH352" s="2" t="n">
+        <v>19397</v>
+      </c>
+      <c r="AI352" s="2" t="n">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2570</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="inlineStr">
+        <is>
+          <t>12:01:07.291</t>
+        </is>
+      </c>
+      <c r="K353" s="2" t="inlineStr">
+        <is>
+          <t>12:01:07.311</t>
+        </is>
+      </c>
+      <c r="L353" s="2" t="inlineStr">
+        <is>
+          <t>12:01:13.400</t>
+        </is>
+      </c>
+      <c r="M353" s="2" t="inlineStr">
+        <is>
+          <t>12:01:21.449</t>
+        </is>
+      </c>
+      <c r="N353" s="2" t="inlineStr">
+        <is>
+          <t>12:01:21.557</t>
+        </is>
+      </c>
+      <c r="O353" s="2" t="inlineStr">
+        <is>
+          <t>12:01:23.325</t>
+        </is>
+      </c>
+      <c r="P353" s="2" t="n">
+        <v>6089</v>
+      </c>
+      <c r="Q353" s="2" t="inlineStr">
+        <is>
+          <t>6.1s</t>
+        </is>
+      </c>
+      <c r="R353" s="2" t="n">
+        <v>14158</v>
+      </c>
+      <c r="S353" s="2" t="inlineStr">
+        <is>
+          <t>14.2s</t>
+        </is>
+      </c>
+      <c r="T353" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="U353" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V353" s="2" t="n">
+        <v>1768</v>
+      </c>
+      <c r="W353" s="2" t="inlineStr">
+        <is>
+          <t>1.8s</t>
+        </is>
+      </c>
+      <c r="X353" s="2" t="n">
+        <v>16034</v>
+      </c>
+      <c r="Y353" s="2" t="inlineStr">
+        <is>
+          <t>16.0s</t>
+        </is>
+      </c>
+      <c r="Z353" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:16, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA353" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB353" s="2" t="inlineStr"/>
+      <c r="AC353" s="2" t="inlineStr"/>
+      <c r="AD353" s="2" t="inlineStr"/>
+      <c r="AE353" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF353" s="2" t="n">
+        <v>17688</v>
+      </c>
+      <c r="AG353" s="2" t="n">
+        <v>1709</v>
+      </c>
+      <c r="AH353" s="2" t="n">
+        <v>19397</v>
+      </c>
+      <c r="AI353" s="2" t="n">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2571</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="inlineStr">
+        <is>
+          <t>12:01:28.709</t>
+        </is>
+      </c>
+      <c r="K354" s="2" t="inlineStr">
+        <is>
+          <t>12:01:28.740</t>
+        </is>
+      </c>
+      <c r="L354" s="2" t="inlineStr">
+        <is>
+          <t>12:01:36.068</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="inlineStr">
+        <is>
+          <t>12:01:43.997</t>
+        </is>
+      </c>
+      <c r="N354" s="2" t="inlineStr">
+        <is>
+          <t>12:01:44.090</t>
+        </is>
+      </c>
+      <c r="O354" s="2" t="inlineStr">
+        <is>
+          <t>12:01:46.434</t>
+        </is>
+      </c>
+      <c r="P354" s="2" t="n">
+        <v>7328</v>
+      </c>
+      <c r="Q354" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="R354" s="2" t="n">
+        <v>15288</v>
+      </c>
+      <c r="S354" s="2" t="inlineStr">
+        <is>
+          <t>15.3s</t>
+        </is>
+      </c>
+      <c r="T354" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="U354" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V354" s="2" t="n">
+        <v>2344</v>
+      </c>
+      <c r="W354" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="X354" s="2" t="n">
+        <v>17725</v>
+      </c>
+      <c r="Y354" s="2" t="inlineStr">
+        <is>
+          <t>17.7s</t>
+        </is>
+      </c>
+      <c r="Z354" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:16, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA354" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB354" s="2" t="inlineStr"/>
+      <c r="AC354" s="2" t="inlineStr"/>
+      <c r="AD354" s="2" t="inlineStr"/>
+      <c r="AE354" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF354" s="2" t="n">
+        <v>17688</v>
+      </c>
+      <c r="AG354" s="2" t="n">
+        <v>1709</v>
+      </c>
+      <c r="AH354" s="2" t="n">
+        <v>19397</v>
+      </c>
+      <c r="AI354" s="2" t="n">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2572</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr">
+        <is>
+          <t>12:01:52.251</t>
+        </is>
+      </c>
+      <c r="K355" s="2" t="inlineStr">
+        <is>
+          <t>12:01:52.437</t>
+        </is>
+      </c>
+      <c r="L355" s="2" t="inlineStr">
+        <is>
+          <t>12:02:01.105</t>
+        </is>
+      </c>
+      <c r="M355" s="2" t="inlineStr">
+        <is>
+          <t>12:02:08.730</t>
+        </is>
+      </c>
+      <c r="N355" s="2" t="inlineStr">
+        <is>
+          <t>12:02:08.825</t>
+        </is>
+      </c>
+      <c r="O355" s="2" t="inlineStr">
+        <is>
+          <t>12:02:10.788</t>
+        </is>
+      </c>
+      <c r="P355" s="2" t="n">
+        <v>8668</v>
+      </c>
+      <c r="Q355" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="R355" s="2" t="n">
+        <v>16479</v>
+      </c>
+      <c r="S355" s="2" t="inlineStr">
+        <is>
+          <t>16.5s</t>
+        </is>
+      </c>
+      <c r="T355" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="U355" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V355" s="2" t="n">
+        <v>1963</v>
+      </c>
+      <c r="W355" s="2" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="X355" s="2" t="n">
+        <v>18537</v>
+      </c>
+      <c r="Y355" s="2" t="inlineStr">
+        <is>
+          <t>18.5s</t>
+        </is>
+      </c>
+      <c r="Z355" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:16, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA355" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB355" s="2" t="inlineStr"/>
+      <c r="AC355" s="2" t="inlineStr"/>
+      <c r="AD355" s="2" t="inlineStr"/>
+      <c r="AE355" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF355" s="2" t="n">
+        <v>17688</v>
+      </c>
+      <c r="AG355" s="2" t="n">
+        <v>1709</v>
+      </c>
+      <c r="AH355" s="2" t="n">
+        <v>19397</v>
+      </c>
+      <c r="AI355" s="2" t="n">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2573</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr">
+        <is>
+          <t>12:15:22.146</t>
+        </is>
+      </c>
+      <c r="K356" s="2" t="inlineStr">
+        <is>
+          <t>12:15:22.165</t>
+        </is>
+      </c>
+      <c r="L356" s="2" t="inlineStr">
+        <is>
+          <t>12:15:22.367</t>
+        </is>
+      </c>
+      <c r="M356" s="2" t="inlineStr">
+        <is>
+          <t>12:15:41.422</t>
+        </is>
+      </c>
+      <c r="N356" s="2" t="inlineStr">
+        <is>
+          <t>12:15:41.471</t>
+        </is>
+      </c>
+      <c r="O356" s="2" t="inlineStr">
+        <is>
+          <t>12:15:41.536</t>
+        </is>
+      </c>
+      <c r="P356" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q356" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R356" s="2" t="n">
+        <v>19276</v>
+      </c>
+      <c r="S356" s="2" t="inlineStr">
+        <is>
+          <t>19.3s</t>
+        </is>
+      </c>
+      <c r="T356" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U356" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V356" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="W356" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X356" s="2" t="n">
+        <v>19390</v>
+      </c>
+      <c r="Y356" s="2" t="inlineStr">
+        <is>
+          <t>19.4s</t>
+        </is>
+      </c>
+      <c r="Z356" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA356" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB356" s="2" t="inlineStr"/>
+      <c r="AC356" s="2" t="inlineStr"/>
+      <c r="AD356" s="2" t="inlineStr"/>
+      <c r="AE356" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF356" s="2" t="n">
+        <v>27558</v>
+      </c>
+      <c r="AG356" s="2" t="n">
+        <v>12574</v>
+      </c>
+      <c r="AH356" s="2" t="n">
+        <v>40132</v>
+      </c>
+      <c r="AI356" s="2" t="n">
+        <v>14263</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2574</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr">
+        <is>
+          <t>12:15:42.892</t>
+        </is>
+      </c>
+      <c r="K357" s="2" t="inlineStr">
+        <is>
+          <t>12:15:42.911</t>
+        </is>
+      </c>
+      <c r="L357" s="2" t="inlineStr">
+        <is>
+          <t>12:15:43.156</t>
+        </is>
+      </c>
+      <c r="M357" s="2" t="inlineStr">
+        <is>
+          <t>12:16:06.883</t>
+        </is>
+      </c>
+      <c r="N357" s="2" t="inlineStr">
+        <is>
+          <t>12:16:06.946</t>
+        </is>
+      </c>
+      <c r="O357" s="2" t="inlineStr">
+        <is>
+          <t>12:16:07.013</t>
+        </is>
+      </c>
+      <c r="P357" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="Q357" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R357" s="2" t="n">
+        <v>23991</v>
+      </c>
+      <c r="S357" s="2" t="inlineStr">
+        <is>
+          <t>24.0s</t>
+        </is>
+      </c>
+      <c r="T357" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U357" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V357" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W357" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X357" s="2" t="n">
+        <v>24121</v>
+      </c>
+      <c r="Y357" s="2" t="inlineStr">
+        <is>
+          <t>24.1s</t>
+        </is>
+      </c>
+      <c r="Z357" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA357" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB357" s="2" t="inlineStr"/>
+      <c r="AC357" s="2" t="inlineStr"/>
+      <c r="AD357" s="2" t="inlineStr"/>
+      <c r="AE357" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF357" s="2" t="n">
+        <v>27558</v>
+      </c>
+      <c r="AG357" s="2" t="n">
+        <v>12574</v>
+      </c>
+      <c r="AH357" s="2" t="n">
+        <v>40132</v>
+      </c>
+      <c r="AI357" s="2" t="n">
+        <v>14263</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2575</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="inlineStr">
+        <is>
+          <t>12:16:08.186</t>
+        </is>
+      </c>
+      <c r="K358" s="2" t="inlineStr">
+        <is>
+          <t>12:16:08.203</t>
+        </is>
+      </c>
+      <c r="L358" s="2" t="inlineStr">
+        <is>
+          <t>12:16:08.424</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="inlineStr">
+        <is>
+          <t>12:16:43.988</t>
+        </is>
+      </c>
+      <c r="N358" s="2" t="inlineStr">
+        <is>
+          <t>12:16:44.037</t>
+        </is>
+      </c>
+      <c r="O358" s="2" t="inlineStr">
+        <is>
+          <t>12:16:44.092</t>
+        </is>
+      </c>
+      <c r="P358" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q358" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R358" s="2" t="n">
+        <v>35802</v>
+      </c>
+      <c r="S358" s="2" t="inlineStr">
+        <is>
+          <t>35.8s</t>
+        </is>
+      </c>
+      <c r="T358" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U358" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V358" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W358" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X358" s="2" t="n">
+        <v>35906</v>
+      </c>
+      <c r="Y358" s="2" t="inlineStr">
+        <is>
+          <t>35.9s</t>
+        </is>
+      </c>
+      <c r="Z358" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA358" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB358" s="2" t="inlineStr"/>
+      <c r="AC358" s="2" t="inlineStr"/>
+      <c r="AD358" s="2" t="inlineStr"/>
+      <c r="AE358" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF358" s="2" t="n">
+        <v>27558</v>
+      </c>
+      <c r="AG358" s="2" t="n">
+        <v>12574</v>
+      </c>
+      <c r="AH358" s="2" t="n">
+        <v>40132</v>
+      </c>
+      <c r="AI358" s="2" t="n">
+        <v>14263</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2576</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="inlineStr">
+        <is>
+          <t>12:16:45.903</t>
+        </is>
+      </c>
+      <c r="K359" s="2" t="inlineStr">
+        <is>
+          <t>12:16:45.918</t>
+        </is>
+      </c>
+      <c r="L359" s="2" t="inlineStr">
+        <is>
+          <t>12:16:46.120</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="inlineStr">
+        <is>
+          <t>12:17:13.797</t>
+        </is>
+      </c>
+      <c r="N359" s="2" t="inlineStr">
+        <is>
+          <t>12:17:13.853</t>
+        </is>
+      </c>
+      <c r="O359" s="2" t="inlineStr">
+        <is>
+          <t>12:17:13.910</t>
+        </is>
+      </c>
+      <c r="P359" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q359" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R359" s="2" t="n">
+        <v>27894</v>
+      </c>
+      <c r="S359" s="2" t="inlineStr">
+        <is>
+          <t>27.9s</t>
+        </is>
+      </c>
+      <c r="T359" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U359" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V359" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="W359" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X359" s="2" t="n">
+        <v>28007</v>
+      </c>
+      <c r="Y359" s="2" t="inlineStr">
+        <is>
+          <t>28.0s</t>
+        </is>
+      </c>
+      <c r="Z359" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA359" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB359" s="2" t="inlineStr"/>
+      <c r="AC359" s="2" t="inlineStr"/>
+      <c r="AD359" s="2" t="inlineStr"/>
+      <c r="AE359" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF359" s="2" t="n">
+        <v>27558</v>
+      </c>
+      <c r="AG359" s="2" t="n">
+        <v>12574</v>
+      </c>
+      <c r="AH359" s="2" t="n">
+        <v>40132</v>
+      </c>
+      <c r="AI359" s="2" t="n">
+        <v>14263</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2577</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr">
+        <is>
+          <t>12:17:15.774</t>
+        </is>
+      </c>
+      <c r="K360" s="2" t="inlineStr">
+        <is>
+          <t>12:17:15.791</t>
+        </is>
+      </c>
+      <c r="L360" s="2" t="inlineStr">
+        <is>
+          <t>12:17:16.007</t>
+        </is>
+      </c>
+      <c r="M360" s="2" t="inlineStr">
+        <is>
+          <t>12:17:53.873</t>
+        </is>
+      </c>
+      <c r="N360" s="2" t="inlineStr">
+        <is>
+          <t>12:17:53.926</t>
+        </is>
+      </c>
+      <c r="O360" s="2" t="inlineStr">
+        <is>
+          <t>12:17:53.976</t>
+        </is>
+      </c>
+      <c r="P360" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="Q360" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R360" s="2" t="n">
+        <v>38099</v>
+      </c>
+      <c r="S360" s="2" t="inlineStr">
+        <is>
+          <t>38.1s</t>
+        </is>
+      </c>
+      <c r="T360" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U360" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V360" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="W360" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X360" s="2" t="n">
+        <v>38202</v>
+      </c>
+      <c r="Y360" s="2" t="inlineStr">
+        <is>
+          <t>38.2s</t>
+        </is>
+      </c>
+      <c r="Z360" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA360" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB360" s="2" t="inlineStr"/>
+      <c r="AC360" s="2" t="inlineStr"/>
+      <c r="AD360" s="2" t="inlineStr"/>
+      <c r="AE360" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF360" s="2" t="n">
+        <v>27558</v>
+      </c>
+      <c r="AG360" s="2" t="n">
+        <v>12574</v>
+      </c>
+      <c r="AH360" s="2" t="n">
+        <v>40132</v>
+      </c>
+      <c r="AI360" s="2" t="n">
+        <v>14263</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2578</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr">
+        <is>
+          <t>12:17:55.924</t>
+        </is>
+      </c>
+      <c r="K361" s="2" t="inlineStr">
+        <is>
+          <t>12:17:55.941</t>
+        </is>
+      </c>
+      <c r="L361" s="2" t="inlineStr">
+        <is>
+          <t>12:17:56.151</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="inlineStr">
+        <is>
+          <t>12:18:29.680</t>
+        </is>
+      </c>
+      <c r="N361" s="2" t="inlineStr">
+        <is>
+          <t>12:18:29.739</t>
+        </is>
+      </c>
+      <c r="O361" s="2" t="inlineStr">
+        <is>
+          <t>12:18:29.798</t>
+        </is>
+      </c>
+      <c r="P361" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q361" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R361" s="2" t="n">
+        <v>33756</v>
+      </c>
+      <c r="S361" s="2" t="inlineStr">
+        <is>
+          <t>33.8s</t>
+        </is>
+      </c>
+      <c r="T361" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U361" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V361" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="W361" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X361" s="2" t="n">
+        <v>33874</v>
+      </c>
+      <c r="Y361" s="2" t="inlineStr">
+        <is>
+          <t>33.9s</t>
+        </is>
+      </c>
+      <c r="Z361" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA361" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB361" s="2" t="inlineStr"/>
+      <c r="AC361" s="2" t="inlineStr"/>
+      <c r="AD361" s="2" t="inlineStr"/>
+      <c r="AE361" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF361" s="2" t="n">
+        <v>27558</v>
+      </c>
+      <c r="AG361" s="2" t="n">
+        <v>12574</v>
+      </c>
+      <c r="AH361" s="2" t="n">
+        <v>40132</v>
+      </c>
+      <c r="AI361" s="2" t="n">
+        <v>14263</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>translationjob739</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr">
+        <is>
+          <t>12:57:27.147</t>
+        </is>
+      </c>
+      <c r="K362" s="2" t="inlineStr">
+        <is>
+          <t>12:57:27.168</t>
+        </is>
+      </c>
+      <c r="L362" s="2" t="inlineStr">
+        <is>
+          <t>12:57:27.503</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="inlineStr">
+        <is>
+          <t>12:57:31.936</t>
+        </is>
+      </c>
+      <c r="N362" s="2" t="inlineStr">
+        <is>
+          <t>12:57:32.007</t>
+        </is>
+      </c>
+      <c r="O362" s="2" t="inlineStr">
+        <is>
+          <t>12:57:32.081</t>
+        </is>
+      </c>
+      <c r="P362" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="Q362" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R362" s="2" t="n">
+        <v>4789</v>
+      </c>
+      <c r="S362" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="T362" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="U362" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V362" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="W362" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X362" s="2" t="n">
+        <v>4934</v>
+      </c>
+      <c r="Y362" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="Z362" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA362" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB362" s="2" t="inlineStr"/>
+      <c r="AC362" s="2" t="inlineStr"/>
+      <c r="AD362" s="2" t="inlineStr"/>
+      <c r="AE362" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF362" s="2" t="n">
+        <v>9963</v>
+      </c>
+      <c r="AG362" s="2" t="n">
+        <v>2098</v>
+      </c>
+      <c r="AH362" s="2" t="n">
+        <v>12061</v>
+      </c>
+      <c r="AI362" s="2" t="n">
+        <v>3911</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>translationjob740</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr">
+        <is>
+          <t>12:57:33.709</t>
+        </is>
+      </c>
+      <c r="K363" s="2" t="inlineStr">
+        <is>
+          <t>12:57:33.730</t>
+        </is>
+      </c>
+      <c r="L363" s="2" t="inlineStr">
+        <is>
+          <t>12:57:34.209</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="inlineStr">
+        <is>
+          <t>12:57:37.635</t>
+        </is>
+      </c>
+      <c r="N363" s="2" t="inlineStr">
+        <is>
+          <t>12:57:37.693</t>
+        </is>
+      </c>
+      <c r="O363" s="2" t="inlineStr">
+        <is>
+          <t>12:57:37.762</t>
+        </is>
+      </c>
+      <c r="P363" s="2" t="n">
+        <v>479</v>
+      </c>
+      <c r="Q363" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R363" s="2" t="n">
+        <v>3926</v>
+      </c>
+      <c r="S363" s="2" t="inlineStr">
+        <is>
+          <t>3.9s</t>
+        </is>
+      </c>
+      <c r="T363" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U363" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V363" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="W363" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X363" s="2" t="n">
+        <v>4053</v>
+      </c>
+      <c r="Y363" s="2" t="inlineStr">
+        <is>
+          <t>4.1s</t>
+        </is>
+      </c>
+      <c r="Z363" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA363" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB363" s="2" t="inlineStr"/>
+      <c r="AC363" s="2" t="inlineStr"/>
+      <c r="AD363" s="2" t="inlineStr"/>
+      <c r="AE363" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF363" s="2" t="n">
+        <v>9963</v>
+      </c>
+      <c r="AG363" s="2" t="n">
+        <v>2098</v>
+      </c>
+      <c r="AH363" s="2" t="n">
+        <v>12061</v>
+      </c>
+      <c r="AI363" s="2" t="n">
+        <v>3911</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>translationjob741</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr">
+        <is>
+          <t>12:57:39.528</t>
+        </is>
+      </c>
+      <c r="K364" s="2" t="inlineStr">
+        <is>
+          <t>12:57:39.550</t>
+        </is>
+      </c>
+      <c r="L364" s="2" t="inlineStr">
+        <is>
+          <t>12:57:39.824</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="inlineStr">
+        <is>
+          <t>12:57:45.147</t>
+        </is>
+      </c>
+      <c r="N364" s="2" t="inlineStr">
+        <is>
+          <t>12:57:45.211</t>
+        </is>
+      </c>
+      <c r="O364" s="2" t="inlineStr">
+        <is>
+          <t>12:57:45.271</t>
+        </is>
+      </c>
+      <c r="P364" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q364" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R364" s="2" t="n">
+        <v>5619</v>
+      </c>
+      <c r="S364" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="T364" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U364" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V364" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W364" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X364" s="2" t="n">
+        <v>5743</v>
+      </c>
+      <c r="Y364" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="Z364" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA364" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB364" s="2" t="inlineStr"/>
+      <c r="AC364" s="2" t="inlineStr"/>
+      <c r="AD364" s="2" t="inlineStr"/>
+      <c r="AE364" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF364" s="2" t="n">
+        <v>9963</v>
+      </c>
+      <c r="AG364" s="2" t="n">
+        <v>2098</v>
+      </c>
+      <c r="AH364" s="2" t="n">
+        <v>12061</v>
+      </c>
+      <c r="AI364" s="2" t="n">
+        <v>3911</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>translationjob742</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr">
+        <is>
+          <t>12:57:46.874</t>
+        </is>
+      </c>
+      <c r="K365" s="2" t="inlineStr">
+        <is>
+          <t>12:57:46.893</t>
+        </is>
+      </c>
+      <c r="L365" s="2" t="inlineStr">
+        <is>
+          <t>12:57:47.450</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="inlineStr">
+        <is>
+          <t>12:57:53.885</t>
+        </is>
+      </c>
+      <c r="N365" s="2" t="inlineStr">
+        <is>
+          <t>12:57:53.954</t>
+        </is>
+      </c>
+      <c r="O365" s="2" t="inlineStr">
+        <is>
+          <t>12:57:54.017</t>
+        </is>
+      </c>
+      <c r="P365" s="2" t="n">
+        <v>557</v>
+      </c>
+      <c r="Q365" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R365" s="2" t="n">
+        <v>7011</v>
+      </c>
+      <c r="S365" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="T365" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="U365" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V365" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W365" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X365" s="2" t="n">
+        <v>7143</v>
+      </c>
+      <c r="Y365" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="Z365" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA365" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB365" s="2" t="inlineStr"/>
+      <c r="AC365" s="2" t="inlineStr"/>
+      <c r="AD365" s="2" t="inlineStr"/>
+      <c r="AE365" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF365" s="2" t="n">
+        <v>9963</v>
+      </c>
+      <c r="AG365" s="2" t="n">
+        <v>2098</v>
+      </c>
+      <c r="AH365" s="2" t="n">
+        <v>12061</v>
+      </c>
+      <c r="AI365" s="2" t="n">
+        <v>3911</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>translationjob743</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr">
+        <is>
+          <t>12:57:55.561</t>
+        </is>
+      </c>
+      <c r="K366" s="2" t="inlineStr">
+        <is>
+          <t>12:57:55.582</t>
+        </is>
+      </c>
+      <c r="L366" s="2" t="inlineStr">
+        <is>
+          <t>12:57:55.825</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="inlineStr">
+        <is>
+          <t>12:57:59.997</t>
+        </is>
+      </c>
+      <c r="N366" s="2" t="inlineStr">
+        <is>
+          <t>12:58:00.059</t>
+        </is>
+      </c>
+      <c r="O366" s="2" t="inlineStr">
+        <is>
+          <t>12:58:00.152</t>
+        </is>
+      </c>
+      <c r="P366" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="Q366" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R366" s="2" t="n">
+        <v>4436</v>
+      </c>
+      <c r="S366" s="2" t="inlineStr">
+        <is>
+          <t>4.4s</t>
+        </is>
+      </c>
+      <c r="T366" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U366" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V366" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="W366" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X366" s="2" t="n">
+        <v>4591</v>
+      </c>
+      <c r="Y366" s="2" t="inlineStr">
+        <is>
+          <t>4.6s</t>
+        </is>
+      </c>
+      <c r="Z366" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA366" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB366" s="2" t="inlineStr"/>
+      <c r="AC366" s="2" t="inlineStr"/>
+      <c r="AD366" s="2" t="inlineStr"/>
+      <c r="AE366" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF366" s="2" t="n">
+        <v>9963</v>
+      </c>
+      <c r="AG366" s="2" t="n">
+        <v>2098</v>
+      </c>
+      <c r="AH366" s="2" t="n">
+        <v>12061</v>
+      </c>
+      <c r="AI366" s="2" t="n">
+        <v>3911</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>translationjob744</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr">
+        <is>
+          <t>12:58:01.906</t>
+        </is>
+      </c>
+      <c r="K367" s="2" t="inlineStr">
+        <is>
+          <t>12:58:01.925</t>
+        </is>
+      </c>
+      <c r="L367" s="2" t="inlineStr">
+        <is>
+          <t>12:58:02.189</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="inlineStr">
+        <is>
+          <t>12:58:07.562</t>
+        </is>
+      </c>
+      <c r="N367" s="2" t="inlineStr">
+        <is>
+          <t>12:58:07.632</t>
+        </is>
+      </c>
+      <c r="O367" s="2" t="inlineStr">
+        <is>
+          <t>12:58:07.704</t>
+        </is>
+      </c>
+      <c r="P367" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="Q367" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R367" s="2" t="n">
+        <v>5656</v>
+      </c>
+      <c r="S367" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="T367" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="U367" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V367" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="W367" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X367" s="2" t="n">
+        <v>5798</v>
+      </c>
+      <c r="Y367" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="Z367" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA367" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB367" s="2" t="inlineStr"/>
+      <c r="AC367" s="2" t="inlineStr"/>
+      <c r="AD367" s="2" t="inlineStr"/>
+      <c r="AE367" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF367" s="2" t="n">
+        <v>9963</v>
+      </c>
+      <c r="AG367" s="2" t="n">
+        <v>2098</v>
+      </c>
+      <c r="AH367" s="2" t="n">
+        <v>12061</v>
+      </c>
+      <c r="AI367" s="2" t="n">
+        <v>3911</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2579</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr">
+        <is>
+          <t>14:31:07.737</t>
+        </is>
+      </c>
+      <c r="K368" s="2" t="inlineStr">
+        <is>
+          <t>14:31:07.762</t>
+        </is>
+      </c>
+      <c r="L368" s="2" t="inlineStr">
+        <is>
+          <t>14:31:08.216</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="inlineStr">
+        <is>
+          <t>14:31:14.628</t>
+        </is>
+      </c>
+      <c r="N368" s="2" t="inlineStr">
+        <is>
+          <t>14:31:14.710</t>
+        </is>
+      </c>
+      <c r="O368" s="2" t="inlineStr">
+        <is>
+          <t>14:31:14.811</t>
+        </is>
+      </c>
+      <c r="P368" s="2" t="n">
+        <v>454</v>
+      </c>
+      <c r="Q368" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R368" s="2" t="n">
+        <v>6891</v>
+      </c>
+      <c r="S368" s="2" t="inlineStr">
+        <is>
+          <t>6.9s</t>
+        </is>
+      </c>
+      <c r="T368" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="U368" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V368" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="W368" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X368" s="2" t="n">
+        <v>7074</v>
+      </c>
+      <c r="Y368" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="Z368" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA368" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB368" s="2" t="inlineStr"/>
+      <c r="AC368" s="2" t="inlineStr"/>
+      <c r="AD368" s="2" t="inlineStr"/>
+      <c r="AE368" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF368" s="2" t="n">
+        <v>10809</v>
+      </c>
+      <c r="AG368" s="2" t="n">
+        <v>2926</v>
+      </c>
+      <c r="AH368" s="2" t="n">
+        <v>13735</v>
+      </c>
+      <c r="AI368" s="2" t="n">
+        <v>5812</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2580</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr">
+        <is>
+          <t>14:31:17.382</t>
+        </is>
+      </c>
+      <c r="K369" s="2" t="inlineStr">
+        <is>
+          <t>14:31:17.407</t>
+        </is>
+      </c>
+      <c r="L369" s="2" t="inlineStr">
+        <is>
+          <t>14:31:17.689</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="inlineStr">
+        <is>
+          <t>14:31:22.362</t>
+        </is>
+      </c>
+      <c r="N369" s="2" t="inlineStr">
+        <is>
+          <t>14:31:22.459</t>
+        </is>
+      </c>
+      <c r="O369" s="2" t="inlineStr">
+        <is>
+          <t>14:31:22.546</t>
+        </is>
+      </c>
+      <c r="P369" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="Q369" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R369" s="2" t="n">
+        <v>4980</v>
+      </c>
+      <c r="S369" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="T369" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="U369" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V369" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="W369" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X369" s="2" t="n">
+        <v>5164</v>
+      </c>
+      <c r="Y369" s="2" t="inlineStr">
+        <is>
+          <t>5.2s</t>
+        </is>
+      </c>
+      <c r="Z369" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA369" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB369" s="2" t="inlineStr"/>
+      <c r="AC369" s="2" t="inlineStr"/>
+      <c r="AD369" s="2" t="inlineStr"/>
+      <c r="AE369" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF369" s="2" t="n">
+        <v>10809</v>
+      </c>
+      <c r="AG369" s="2" t="n">
+        <v>2926</v>
+      </c>
+      <c r="AH369" s="2" t="n">
+        <v>13735</v>
+      </c>
+      <c r="AI369" s="2" t="n">
+        <v>5812</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2581</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr">
+        <is>
+          <t>14:31:25.960</t>
+        </is>
+      </c>
+      <c r="K370" s="2" t="inlineStr">
+        <is>
+          <t>14:31:25.982</t>
+        </is>
+      </c>
+      <c r="L370" s="2" t="inlineStr">
+        <is>
+          <t>14:31:26.254</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="inlineStr">
+        <is>
+          <t>14:31:33.338</t>
+        </is>
+      </c>
+      <c r="N370" s="2" t="inlineStr">
+        <is>
+          <t>14:31:33.398</t>
+        </is>
+      </c>
+      <c r="O370" s="2" t="inlineStr">
+        <is>
+          <t>14:31:33.465</t>
+        </is>
+      </c>
+      <c r="P370" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="Q370" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R370" s="2" t="n">
+        <v>7378</v>
+      </c>
+      <c r="S370" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="T370" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U370" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V370" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W370" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X370" s="2" t="n">
+        <v>7505</v>
+      </c>
+      <c r="Y370" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="Z370" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA370" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB370" s="2" t="inlineStr"/>
+      <c r="AC370" s="2" t="inlineStr"/>
+      <c r="AD370" s="2" t="inlineStr"/>
+      <c r="AE370" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF370" s="2" t="n">
+        <v>10809</v>
+      </c>
+      <c r="AG370" s="2" t="n">
+        <v>2926</v>
+      </c>
+      <c r="AH370" s="2" t="n">
+        <v>13735</v>
+      </c>
+      <c r="AI370" s="2" t="n">
+        <v>5812</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2582</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr">
+        <is>
+          <t>14:31:36.577</t>
+        </is>
+      </c>
+      <c r="K371" s="2" t="inlineStr">
+        <is>
+          <t>14:31:36.600</t>
+        </is>
+      </c>
+      <c r="L371" s="2" t="inlineStr">
+        <is>
+          <t>14:31:36.889</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="inlineStr">
+        <is>
+          <t>14:31:45.286</t>
+        </is>
+      </c>
+      <c r="N371" s="2" t="inlineStr">
+        <is>
+          <t>14:31:45.400</t>
+        </is>
+      </c>
+      <c r="O371" s="2" t="inlineStr">
+        <is>
+          <t>14:31:45.486</t>
+        </is>
+      </c>
+      <c r="P371" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="Q371" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R371" s="2" t="n">
+        <v>8709</v>
+      </c>
+      <c r="S371" s="2" t="inlineStr">
+        <is>
+          <t>8.7s</t>
+        </is>
+      </c>
+      <c r="T371" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="U371" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V371" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="W371" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X371" s="2" t="n">
+        <v>8909</v>
+      </c>
+      <c r="Y371" s="2" t="inlineStr">
+        <is>
+          <t>8.9s</t>
+        </is>
+      </c>
+      <c r="Z371" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA371" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB371" s="2" t="inlineStr"/>
+      <c r="AC371" s="2" t="inlineStr"/>
+      <c r="AD371" s="2" t="inlineStr"/>
+      <c r="AE371" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF371" s="2" t="n">
+        <v>10809</v>
+      </c>
+      <c r="AG371" s="2" t="n">
+        <v>2926</v>
+      </c>
+      <c r="AH371" s="2" t="n">
+        <v>13735</v>
+      </c>
+      <c r="AI371" s="2" t="n">
+        <v>5812</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2583</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr">
+        <is>
+          <t>14:31:49.076</t>
+        </is>
+      </c>
+      <c r="K372" s="2" t="inlineStr">
+        <is>
+          <t>14:31:49.197</t>
+        </is>
+      </c>
+      <c r="L372" s="2" t="inlineStr">
+        <is>
+          <t>14:31:49.510</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="inlineStr">
+        <is>
+          <t>14:31:54.750</t>
+        </is>
+      </c>
+      <c r="N372" s="2" t="inlineStr">
+        <is>
+          <t>14:31:54.836</t>
+        </is>
+      </c>
+      <c r="O372" s="2" t="inlineStr">
+        <is>
+          <t>14:31:54.906</t>
+        </is>
+      </c>
+      <c r="P372" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="Q372" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R372" s="2" t="n">
+        <v>5674</v>
+      </c>
+      <c r="S372" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="T372" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="U372" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V372" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="W372" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X372" s="2" t="n">
+        <v>5830</v>
+      </c>
+      <c r="Y372" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="Z372" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA372" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB372" s="2" t="inlineStr"/>
+      <c r="AC372" s="2" t="inlineStr"/>
+      <c r="AD372" s="2" t="inlineStr"/>
+      <c r="AE372" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF372" s="2" t="n">
+        <v>10809</v>
+      </c>
+      <c r="AG372" s="2" t="n">
+        <v>2926</v>
+      </c>
+      <c r="AH372" s="2" t="n">
+        <v>13735</v>
+      </c>
+      <c r="AI372" s="2" t="n">
+        <v>5812</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2584</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>14:31:58.457</t>
+        </is>
+      </c>
+      <c r="K373" s="2" t="inlineStr">
+        <is>
+          <t>14:31:58.476</t>
+        </is>
+      </c>
+      <c r="L373" s="2" t="inlineStr">
+        <is>
+          <t>14:31:58.835</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="inlineStr">
+        <is>
+          <t>14:32:06.498</t>
+        </is>
+      </c>
+      <c r="N373" s="2" t="inlineStr">
+        <is>
+          <t>14:32:06.594</t>
+        </is>
+      </c>
+      <c r="O373" s="2" t="inlineStr">
+        <is>
+          <t>14:32:06.708</t>
+        </is>
+      </c>
+      <c r="P373" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="Q373" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R373" s="2" t="n">
+        <v>8041</v>
+      </c>
+      <c r="S373" s="2" t="inlineStr">
+        <is>
+          <t>8.0s</t>
+        </is>
+      </c>
+      <c r="T373" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="U373" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V373" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="W373" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X373" s="2" t="n">
+        <v>8251</v>
+      </c>
+      <c r="Y373" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="Z373" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA373" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB373" s="2" t="inlineStr"/>
+      <c r="AC373" s="2" t="inlineStr"/>
+      <c r="AD373" s="2" t="inlineStr"/>
+      <c r="AE373" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF373" s="2" t="n">
+        <v>10809</v>
+      </c>
+      <c r="AG373" s="2" t="n">
+        <v>2926</v>
+      </c>
+      <c r="AH373" s="2" t="n">
+        <v>13735</v>
+      </c>
+      <c r="AI373" s="2" t="n">
+        <v>5812</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2081</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>18:41:40.680</t>
+        </is>
+      </c>
+      <c r="K374" s="2" t="inlineStr">
+        <is>
+          <t>18:41:40.683</t>
+        </is>
+      </c>
+      <c r="L374" s="2" t="inlineStr">
+        <is>
+          <t>18:41:41.397</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="inlineStr">
+        <is>
+          <t>18:41:47.455</t>
+        </is>
+      </c>
+      <c r="N374" s="2" t="inlineStr">
+        <is>
+          <t>18:41:47.521</t>
+        </is>
+      </c>
+      <c r="O374" s="2" t="inlineStr">
+        <is>
+          <t>18:41:47.593</t>
+        </is>
+      </c>
+      <c r="P374" s="2" t="n">
+        <v>714</v>
+      </c>
+      <c r="Q374" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R374" s="2" t="n">
+        <v>6775</v>
+      </c>
+      <c r="S374" s="2" t="inlineStr">
+        <is>
+          <t>6.8s</t>
+        </is>
+      </c>
+      <c r="T374" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U374" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V374" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="W374" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X374" s="2" t="n">
+        <v>6913</v>
+      </c>
+      <c r="Y374" s="2" t="inlineStr">
+        <is>
+          <t>6.9s</t>
+        </is>
+      </c>
+      <c r="Z374" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA374" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB374" s="2" t="inlineStr"/>
+      <c r="AC374" s="2" t="inlineStr"/>
+      <c r="AD374" s="2" t="inlineStr"/>
+      <c r="AE374" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF374" s="2" t="n">
+        <v>2031</v>
+      </c>
+      <c r="AG374" s="2" t="n">
+        <v>632</v>
+      </c>
+      <c r="AH374" s="2" t="n">
+        <v>2663</v>
+      </c>
+      <c r="AI374" s="2" t="n">
+        <v>11855</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2082</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr">
+        <is>
+          <t>18:41:46.549</t>
+        </is>
+      </c>
+      <c r="K375" s="2" t="inlineStr">
+        <is>
+          <t>18:41:46.570</t>
+        </is>
+      </c>
+      <c r="L375" s="2" t="inlineStr">
+        <is>
+          <t>18:41:46.885</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="inlineStr">
+        <is>
+          <t>18:41:59.306</t>
+        </is>
+      </c>
+      <c r="N375" s="2" t="inlineStr">
+        <is>
+          <t>18:41:59.375</t>
+        </is>
+      </c>
+      <c r="O375" s="2" t="inlineStr">
+        <is>
+          <t>18:41:59.506</t>
+        </is>
+      </c>
+      <c r="P375" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="Q375" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R375" s="2" t="n">
+        <v>12757</v>
+      </c>
+      <c r="S375" s="2" t="inlineStr">
+        <is>
+          <t>12.8s</t>
+        </is>
+      </c>
+      <c r="T375" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="U375" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V375" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="W375" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X375" s="2" t="n">
+        <v>12957</v>
+      </c>
+      <c r="Y375" s="2" t="inlineStr">
+        <is>
+          <t>13.0s</t>
+        </is>
+      </c>
+      <c r="Z375" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA375" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB375" s="2" t="inlineStr"/>
+      <c r="AC375" s="2" t="inlineStr"/>
+      <c r="AD375" s="2" t="inlineStr"/>
+      <c r="AE375" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF375" s="2" t="n">
+        <v>2031</v>
+      </c>
+      <c r="AG375" s="2" t="n">
+        <v>632</v>
+      </c>
+      <c r="AH375" s="2" t="n">
+        <v>2663</v>
+      </c>
+      <c r="AI375" s="2" t="n">
+        <v>11855</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2083</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr">
+        <is>
+          <t>18:41:57.003</t>
+        </is>
+      </c>
+      <c r="K376" s="2" t="inlineStr">
+        <is>
+          <t>18:41:57.041</t>
+        </is>
+      </c>
+      <c r="L376" s="2" t="inlineStr">
+        <is>
+          <t>18:41:57.360</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="inlineStr">
+        <is>
+          <t>18:42:15.773</t>
+        </is>
+      </c>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>18:42:15.850</t>
+        </is>
+      </c>
+      <c r="O376" s="2" t="inlineStr">
+        <is>
+          <t>18:42:15.921</t>
+        </is>
+      </c>
+      <c r="P376" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q376" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R376" s="2" t="n">
+        <v>18770</v>
+      </c>
+      <c r="S376" s="2" t="inlineStr">
+        <is>
+          <t>18.8s</t>
+        </is>
+      </c>
+      <c r="T376" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="U376" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V376" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="W376" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X376" s="2" t="n">
+        <v>18918</v>
+      </c>
+      <c r="Y376" s="2" t="inlineStr">
+        <is>
+          <t>18.9s</t>
+        </is>
+      </c>
+      <c r="Z376" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA376" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB376" s="2" t="inlineStr"/>
+      <c r="AC376" s="2" t="inlineStr"/>
+      <c r="AD376" s="2" t="inlineStr"/>
+      <c r="AE376" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF376" s="2" t="n">
+        <v>3953</v>
+      </c>
+      <c r="AG376" s="2" t="n">
+        <v>1324</v>
+      </c>
+      <c r="AH376" s="2" t="n">
+        <v>5277</v>
+      </c>
+      <c r="AI376" s="2" t="n">
+        <v>11659</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2084</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr">
+        <is>
+          <t>21:56:19.979</t>
+        </is>
+      </c>
+      <c r="K377" s="2" t="inlineStr">
+        <is>
+          <t>21:56:20.028</t>
+        </is>
+      </c>
+      <c r="L377" s="2" t="inlineStr">
+        <is>
+          <t>21:56:21.479</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="inlineStr">
+        <is>
+          <t>21:56:27.455</t>
+        </is>
+      </c>
+      <c r="N377" s="2" t="inlineStr">
+        <is>
+          <t>21:56:27.535</t>
+        </is>
+      </c>
+      <c r="O377" s="2" t="inlineStr">
+        <is>
+          <t>21:56:27.881</t>
+        </is>
+      </c>
+      <c r="P377" s="2" t="n">
+        <v>1451</v>
+      </c>
+      <c r="Q377" s="2" t="inlineStr">
+        <is>
+          <t>1.5s</t>
+        </is>
+      </c>
+      <c r="R377" s="2" t="n">
+        <v>7476</v>
+      </c>
+      <c r="S377" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="T377" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="U377" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V377" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="W377" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X377" s="2" t="n">
+        <v>7902</v>
+      </c>
+      <c r="Y377" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="Z377" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA377" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB377" s="2" t="inlineStr"/>
+      <c r="AC377" s="2" t="inlineStr"/>
+      <c r="AD377" s="2" t="inlineStr"/>
+      <c r="AE377" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF377" s="2" t="n">
+        <v>4510</v>
+      </c>
+      <c r="AG377" s="2" t="n">
+        <v>1864</v>
+      </c>
+      <c r="AH377" s="2" t="n">
+        <v>6374</v>
+      </c>
+      <c r="AI377" s="2" t="n">
+        <v>7732</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2085</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr">
+        <is>
+          <t>21:56:24.356</t>
+        </is>
+      </c>
+      <c r="K378" s="2" t="inlineStr">
+        <is>
+          <t>21:56:24.380</t>
+        </is>
+      </c>
+      <c r="L378" s="2" t="inlineStr">
+        <is>
+          <t>21:56:25.019</t>
+        </is>
+      </c>
+      <c r="M378" s="2" t="inlineStr">
+        <is>
+          <t>21:56:34.760</t>
+        </is>
+      </c>
+      <c r="N378" s="2" t="inlineStr">
+        <is>
+          <t>21:56:34.819</t>
+        </is>
+      </c>
+      <c r="O378" s="2" t="inlineStr">
+        <is>
+          <t>21:56:35.014</t>
+        </is>
+      </c>
+      <c r="P378" s="2" t="n">
+        <v>639</v>
+      </c>
+      <c r="Q378" s="2" t="inlineStr">
+        <is>
+          <t>0.6s</t>
+        </is>
+      </c>
+      <c r="R378" s="2" t="n">
+        <v>10404</v>
+      </c>
+      <c r="S378" s="2" t="inlineStr">
+        <is>
+          <t>10.4s</t>
+        </is>
+      </c>
+      <c r="T378" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U378" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V378" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="W378" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X378" s="2" t="n">
+        <v>10658</v>
+      </c>
+      <c r="Y378" s="2" t="inlineStr">
+        <is>
+          <t>10.7s</t>
+        </is>
+      </c>
+      <c r="Z378" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA378" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB378" s="2" t="inlineStr"/>
+      <c r="AC378" s="2" t="inlineStr"/>
+      <c r="AD378" s="2" t="inlineStr"/>
+      <c r="AE378" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF378" s="2" t="n">
+        <v>4510</v>
+      </c>
+      <c r="AG378" s="2" t="n">
+        <v>1864</v>
+      </c>
+      <c r="AH378" s="2" t="n">
+        <v>6374</v>
+      </c>
+      <c r="AI378" s="2" t="n">
+        <v>7732</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B379" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="C379" s="3" t="inlineStr">
+        <is>
+          <t>translationjob2086</t>
+        </is>
+      </c>
+      <c r="D379" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E379" s="3" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F379" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G379" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H379" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I379" s="3" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="J379" s="3" t="inlineStr">
+        <is>
+          <t>21:56:32.495</t>
+        </is>
+      </c>
+      <c r="K379" s="3" t="inlineStr">
+        <is>
+          <t>21:56:32.519</t>
+        </is>
+      </c>
+      <c r="L379" s="3" t="inlineStr">
+        <is>
+          <t>21:56:33.605</t>
+        </is>
+      </c>
+      <c r="M379" s="3" t="inlineStr">
+        <is>
+          <t>21:56:34.080</t>
+        </is>
+      </c>
+      <c r="N379" s="3" t="inlineStr"/>
+      <c r="O379" s="3" t="inlineStr"/>
+      <c r="P379" s="3" t="n">
+        <v>1086</v>
+      </c>
+      <c r="Q379" s="3" t="inlineStr">
+        <is>
+          <t>1.1s</t>
+        </is>
+      </c>
+      <c r="R379" s="3" t="n">
+        <v>1585</v>
+      </c>
+      <c r="S379" s="3" t="inlineStr">
+        <is>
+          <t>1.6s</t>
+        </is>
+      </c>
+      <c r="T379" s="3" t="inlineStr"/>
+      <c r="U379" s="3" t="inlineStr"/>
+      <c r="V379" s="3" t="inlineStr"/>
+      <c r="W379" s="3" t="inlineStr"/>
+      <c r="X379" s="3" t="inlineStr"/>
+      <c r="Y379" s="3" t="inlineStr"/>
+      <c r="Z379" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:0, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA379" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB379" s="3" t="inlineStr"/>
+      <c r="AC379" s="3" t="inlineStr"/>
+      <c r="AD379" s="3" t="inlineStr"/>
+      <c r="AE379" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF379" s="3" t="n">
+        <v>2278</v>
+      </c>
+      <c r="AG379" s="3" t="n">
+        <v>893</v>
+      </c>
+      <c r="AH379" s="3" t="n">
+        <v>3171</v>
+      </c>
+      <c r="AI379" s="3" t="n">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2087</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr">
+        <is>
+          <t>21:56:37.384</t>
+        </is>
+      </c>
+      <c r="K380" s="2" t="inlineStr">
+        <is>
+          <t>21:56:37.441</t>
+        </is>
+      </c>
+      <c r="L380" s="2" t="inlineStr">
+        <is>
+          <t>21:56:38.265</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="inlineStr">
+        <is>
+          <t>21:56:45.535</t>
+        </is>
+      </c>
+      <c r="N380" s="2" t="inlineStr">
+        <is>
+          <t>21:56:45.607</t>
+        </is>
+      </c>
+      <c r="O380" s="2" t="inlineStr">
+        <is>
+          <t>21:56:45.899</t>
+        </is>
+      </c>
+      <c r="P380" s="2" t="n">
+        <v>824</v>
+      </c>
+      <c r="Q380" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R380" s="2" t="n">
+        <v>8151</v>
+      </c>
+      <c r="S380" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="T380" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="U380" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V380" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="W380" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X380" s="2" t="n">
+        <v>8515</v>
+      </c>
+      <c r="Y380" s="2" t="inlineStr">
+        <is>
+          <t>8.5s</t>
+        </is>
+      </c>
+      <c r="Z380" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA380" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB380" s="2" t="inlineStr"/>
+      <c r="AC380" s="2" t="inlineStr"/>
+      <c r="AD380" s="2" t="inlineStr"/>
+      <c r="AE380" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF380" s="2" t="n">
+        <v>4510</v>
+      </c>
+      <c r="AG380" s="2" t="n">
+        <v>1864</v>
+      </c>
+      <c r="AH380" s="2" t="n">
+        <v>6374</v>
+      </c>
+      <c r="AI380" s="2" t="n">
+        <v>7732</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2088</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr">
+        <is>
+          <t>22:11:42.961</t>
+        </is>
+      </c>
+      <c r="K381" s="2" t="inlineStr">
+        <is>
+          <t>22:11:42.987</t>
+        </is>
+      </c>
+      <c r="L381" s="2" t="inlineStr">
+        <is>
+          <t>22:11:43.462</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="inlineStr">
+        <is>
+          <t>22:11:48.837</t>
+        </is>
+      </c>
+      <c r="N381" s="2" t="inlineStr">
+        <is>
+          <t>22:11:48.902</t>
+        </is>
+      </c>
+      <c r="O381" s="2" t="inlineStr">
+        <is>
+          <t>22:11:49.163</t>
+        </is>
+      </c>
+      <c r="P381" s="2" t="n">
+        <v>475</v>
+      </c>
+      <c r="Q381" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R381" s="2" t="n">
+        <v>5876</v>
+      </c>
+      <c r="S381" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="T381" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U381" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V381" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="W381" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="X381" s="2" t="n">
+        <v>6202</v>
+      </c>
+      <c r="Y381" s="2" t="inlineStr">
+        <is>
+          <t>6.2s</t>
+        </is>
+      </c>
+      <c r="Z381" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:2, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA381" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB381" s="2" t="inlineStr"/>
+      <c r="AC381" s="2" t="inlineStr"/>
+      <c r="AD381" s="2" t="inlineStr"/>
+      <c r="AE381" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF381" s="2" t="n">
+        <v>5531</v>
+      </c>
+      <c r="AG381" s="2" t="n">
+        <v>1508</v>
+      </c>
+      <c r="AH381" s="2" t="n">
+        <v>7039</v>
+      </c>
+      <c r="AI381" s="2" t="n">
+        <v>5177</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2089</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>22:11:51.221</t>
+        </is>
+      </c>
+      <c r="K382" s="2" t="inlineStr">
+        <is>
+          <t>22:11:51.239</t>
+        </is>
+      </c>
+      <c r="L382" s="2" t="inlineStr">
+        <is>
+          <t>22:11:51.659</t>
+        </is>
+      </c>
+      <c r="M382" s="2" t="inlineStr">
+        <is>
+          <t>22:11:59.119</t>
+        </is>
+      </c>
+      <c r="N382" s="2" t="inlineStr">
+        <is>
+          <t>22:11:59.183</t>
+        </is>
+      </c>
+      <c r="O382" s="2" t="inlineStr">
+        <is>
+          <t>22:11:59.373</t>
+        </is>
+      </c>
+      <c r="P382" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="Q382" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R382" s="2" t="n">
+        <v>7898</v>
+      </c>
+      <c r="S382" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="T382" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U382" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V382" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="W382" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X382" s="2" t="n">
+        <v>8152</v>
+      </c>
+      <c r="Y382" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="Z382" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA382" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB382" s="2" t="inlineStr"/>
+      <c r="AC382" s="2" t="inlineStr"/>
+      <c r="AD382" s="2" t="inlineStr"/>
+      <c r="AE382" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF382" s="2" t="n">
+        <v>5531</v>
+      </c>
+      <c r="AG382" s="2" t="n">
+        <v>1508</v>
+      </c>
+      <c r="AH382" s="2" t="n">
+        <v>7039</v>
+      </c>
+      <c r="AI382" s="2" t="n">
+        <v>5177</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2090</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr">
+        <is>
+          <t>22:12:01.540</t>
+        </is>
+      </c>
+      <c r="K383" s="2" t="inlineStr">
+        <is>
+          <t>22:12:01.558</t>
+        </is>
+      </c>
+      <c r="L383" s="2" t="inlineStr">
+        <is>
+          <t>22:12:02.213</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="inlineStr">
+        <is>
+          <t>22:12:07.174</t>
+        </is>
+      </c>
+      <c r="N383" s="2" t="inlineStr">
+        <is>
+          <t>22:12:07.258</t>
+        </is>
+      </c>
+      <c r="O383" s="2" t="inlineStr">
+        <is>
+          <t>22:12:07.473</t>
+        </is>
+      </c>
+      <c r="P383" s="2" t="n">
+        <v>655</v>
+      </c>
+      <c r="Q383" s="2" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+      <c r="R383" s="2" t="n">
+        <v>5634</v>
+      </c>
+      <c r="S383" s="2" t="inlineStr">
+        <is>
+          <t>5.6s</t>
+        </is>
+      </c>
+      <c r="T383" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="U383" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V383" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="W383" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X383" s="2" t="n">
+        <v>5933</v>
+      </c>
+      <c r="Y383" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="Z383" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA383" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB383" s="2" t="inlineStr"/>
+      <c r="AC383" s="2" t="inlineStr"/>
+      <c r="AD383" s="2" t="inlineStr"/>
+      <c r="AE383" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF383" s="2" t="n">
+        <v>5531</v>
+      </c>
+      <c r="AG383" s="2" t="n">
+        <v>1508</v>
+      </c>
+      <c r="AH383" s="2" t="n">
+        <v>7039</v>
+      </c>
+      <c r="AI383" s="2" t="n">
+        <v>5177</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="C384" s="3" t="inlineStr">
+        <is>
+          <t>translationjob2002</t>
+        </is>
+      </c>
+      <c r="D384" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E384" s="3" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F384" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G384" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H384" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I384" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J384" s="3" t="inlineStr"/>
+      <c r="K384" s="3" t="inlineStr">
+        <is>
+          <t>22:11:35.023</t>
+        </is>
+      </c>
+      <c r="L384" s="3" t="inlineStr">
+        <is>
+          <t>22:11:40.975</t>
+        </is>
+      </c>
+      <c r="M384" s="3" t="inlineStr"/>
+      <c r="N384" s="3" t="inlineStr"/>
+      <c r="O384" s="3" t="inlineStr"/>
+      <c r="P384" s="3" t="n">
+        <v>5952</v>
+      </c>
+      <c r="Q384" s="3" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="R384" s="3" t="inlineStr"/>
+      <c r="S384" s="3" t="inlineStr"/>
+      <c r="T384" s="3" t="inlineStr"/>
+      <c r="U384" s="3" t="inlineStr"/>
+      <c r="V384" s="3" t="inlineStr"/>
+      <c r="W384" s="3" t="inlineStr"/>
+      <c r="X384" s="3" t="inlineStr"/>
+      <c r="Y384" s="3" t="inlineStr"/>
+      <c r="Z384" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:11, contentFragment:45, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA384" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB384" s="3" t="inlineStr"/>
+      <c r="AC384" s="3" t="inlineStr"/>
+      <c r="AD384" s="3" t="inlineStr"/>
+      <c r="AE384" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF384" s="3" t="n">
+        <v>5531</v>
+      </c>
+      <c r="AG384" s="3" t="n">
+        <v>1508</v>
+      </c>
+      <c r="AH384" s="3" t="n">
+        <v>7039</v>
+      </c>
+      <c r="AI384" s="3" t="n">
+        <v>5177</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B385" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="C385" s="3" t="inlineStr">
+        <is>
+          <t>translationjob2006</t>
+        </is>
+      </c>
+      <c r="D385" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E385" s="3" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F385" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G385" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H385" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I385" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J385" s="3" t="inlineStr"/>
+      <c r="K385" s="3" t="inlineStr">
+        <is>
+          <t>22:12:10.114</t>
+        </is>
+      </c>
+      <c r="L385" s="3" t="inlineStr">
+        <is>
+          <t>22:12:20.160</t>
+        </is>
+      </c>
+      <c r="M385" s="3" t="inlineStr"/>
+      <c r="N385" s="3" t="inlineStr"/>
+      <c r="O385" s="3" t="inlineStr"/>
+      <c r="P385" s="3" t="n">
+        <v>10046</v>
+      </c>
+      <c r="Q385" s="3" t="inlineStr">
+        <is>
+          <t>10.0s</t>
+        </is>
+      </c>
+      <c r="R385" s="3" t="inlineStr"/>
+      <c r="S385" s="3" t="inlineStr"/>
+      <c r="T385" s="3" t="inlineStr"/>
+      <c r="U385" s="3" t="inlineStr"/>
+      <c r="V385" s="3" t="inlineStr"/>
+      <c r="W385" s="3" t="inlineStr"/>
+      <c r="X385" s="3" t="inlineStr"/>
+      <c r="Y385" s="3" t="inlineStr"/>
+      <c r="Z385" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:7, contentFragment:40, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA385" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB385" s="3" t="inlineStr"/>
+      <c r="AC385" s="3" t="inlineStr"/>
+      <c r="AD385" s="3" t="inlineStr"/>
+      <c r="AE385" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF385" s="3" t="n">
+        <v>5531</v>
+      </c>
+      <c r="AG385" s="3" t="n">
+        <v>1508</v>
+      </c>
+      <c r="AH385" s="3" t="n">
+        <v>7039</v>
+      </c>
+      <c r="AI385" s="3" t="n">
+        <v>5177</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="C386" s="3" t="inlineStr">
+        <is>
+          <t>translationjob2007</t>
+        </is>
+      </c>
+      <c r="D386" s="3" t="inlineStr">
+        <is>
+          <t>Maria Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E386" s="3" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F386" s="3" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G386" s="3" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H386" s="3" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I386" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J386" s="3" t="inlineStr"/>
+      <c r="K386" s="3" t="inlineStr">
+        <is>
+          <t>22:12:22.355</t>
+        </is>
+      </c>
+      <c r="L386" s="3" t="inlineStr">
+        <is>
+          <t>22:12:24.769</t>
+        </is>
+      </c>
+      <c r="M386" s="3" t="inlineStr"/>
+      <c r="N386" s="3" t="inlineStr"/>
+      <c r="O386" s="3" t="inlineStr"/>
+      <c r="P386" s="3" t="n">
+        <v>2414</v>
+      </c>
+      <c r="Q386" s="3" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="R386" s="3" t="inlineStr"/>
+      <c r="S386" s="3" t="inlineStr"/>
+      <c r="T386" s="3" t="inlineStr"/>
+      <c r="U386" s="3" t="inlineStr"/>
+      <c r="V386" s="3" t="inlineStr"/>
+      <c r="W386" s="3" t="inlineStr"/>
+      <c r="X386" s="3" t="inlineStr"/>
+      <c r="Y386" s="3" t="inlineStr"/>
+      <c r="Z386" s="3" t="inlineStr">
+        <is>
+          <t>page:0, asset:10, contentFragment:42, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA386" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB386" s="3" t="inlineStr"/>
+      <c r="AC386" s="3" t="inlineStr"/>
+      <c r="AD386" s="3" t="inlineStr"/>
+      <c r="AE386" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF386" s="3" t="n">
+        <v>5531</v>
+      </c>
+      <c r="AG386" s="3" t="n">
+        <v>1508</v>
+      </c>
+      <c r="AH386" s="3" t="n">
+        <v>7039</v>
+      </c>
+      <c r="AI386" s="3" t="n">
+        <v>5177</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AI325"/>
+  <autoFilter ref="A1:AI386"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46224,7 +54679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -46523,6 +54978,58 @@
         <v>901958</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>12.2s</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>38.2s</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>425</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>764103</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>211633</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>975736</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46534,7 +55041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -46542,6 +55049,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -46570,6 +55078,11 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -46589,6 +55102,9 @@
       <c r="E2" s="7" t="n">
         <v>933</v>
       </c>
+      <c r="F2" s="7" t="n">
+        <v>482</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -46608,6 +55124,7 @@
       <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="F3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -46627,6 +55144,9 @@
       <c r="E4" s="6" t="n">
         <v>23</v>
       </c>
+      <c r="F4" s="6" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -46646,6 +55166,9 @@
       <c r="E5" s="7" t="n">
         <v>132</v>
       </c>
+      <c r="F5" s="7" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -46665,6 +55188,9 @@
       <c r="E6" s="7" t="n">
         <v>1339</v>
       </c>
+      <c r="F6" s="7" t="n">
+        <v>744</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -46684,6 +55210,9 @@
       <c r="E7" s="7" t="n">
         <v>140</v>
       </c>
+      <c r="F7" s="7" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -46703,6 +55232,9 @@
       <c r="E8" s="7" t="n">
         <v>167</v>
       </c>
+      <c r="F8" s="7" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -46722,6 +55254,9 @@
       <c r="E9" s="7" t="n">
         <v>84256</v>
       </c>
+      <c r="F9" s="7" t="n">
+        <v>141728</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -46741,6 +55276,9 @@
       <c r="E10" s="7" t="n">
         <v>16102</v>
       </c>
+      <c r="F10" s="7" t="n">
+        <v>61280</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -46760,6 +55298,9 @@
       <c r="E11" s="7" t="n">
         <v>2029</v>
       </c>
+      <c r="F11" s="6" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -46779,6 +55320,9 @@
       <c r="E12" s="7" t="n">
         <v>1766</v>
       </c>
+      <c r="F12" s="7" t="n">
+        <v>1784</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -46798,6 +55342,9 @@
       <c r="E13" s="7" t="n">
         <v>8198</v>
       </c>
+      <c r="F13" s="7" t="n">
+        <v>2724</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -46817,6 +55364,9 @@
       <c r="E14" s="6" t="n">
         <v>92</v>
       </c>
+      <c r="F14" s="7" t="n">
+        <v>957</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -46832,6 +55382,7 @@
         <v>22</v>
       </c>
       <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -46844,7 +55395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -46993,6 +55544,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>646</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>129</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>129</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>129</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/translation_jobs_all_days.xlsx
+++ b/translation_jobs_all_days.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RMTranslationRequest" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AI$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translation Jobs'!$A$1:$AI$209</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI150"/>
+  <dimension ref="A1:AI209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21456,8 +21456,8327 @@
         <v>2351</v>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>translationjob833</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Ana Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>08:39:34.435</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>08:39:34.468</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>08:39:34.866</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>08:39:51.343</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>08:39:51.445</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>08:39:51.553</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="n">
+        <v>398</v>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="n">
+        <v>16908</v>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>16.9s</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="U151" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V151" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="W151" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X151" s="2" t="n">
+        <v>17118</v>
+      </c>
+      <c r="Y151" s="2" t="inlineStr">
+        <is>
+          <t>17.1s</t>
+        </is>
+      </c>
+      <c r="Z151" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB151" s="2" t="inlineStr"/>
+      <c r="AC151" s="2" t="inlineStr"/>
+      <c r="AD151" s="2" t="inlineStr"/>
+      <c r="AE151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF151" s="2" t="n">
+        <v>3260</v>
+      </c>
+      <c r="AG151" s="2" t="n">
+        <v>1740</v>
+      </c>
+      <c r="AH151" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AI151" s="2" t="n">
+        <v>14473</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2357</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>09:11:40.437</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>09:11:40.462</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>09:11:40.790</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>09:11:43.728</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>09:11:43.861</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>09:11:44.020</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="n">
+        <v>3291</v>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>3.3s</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="U152" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V152" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X152" s="2" t="n">
+        <v>3583</v>
+      </c>
+      <c r="Y152" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="Z152" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB152" s="2" t="inlineStr"/>
+      <c r="AC152" s="2" t="inlineStr"/>
+      <c r="AD152" s="2" t="inlineStr"/>
+      <c r="AE152" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF152" s="2" t="n">
+        <v>8373</v>
+      </c>
+      <c r="AG152" s="2" t="n">
+        <v>352</v>
+      </c>
+      <c r="AH152" s="2" t="n">
+        <v>8725</v>
+      </c>
+      <c r="AI152" s="2" t="n">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2358</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>09:11:47.669</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>09:11:47.697</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>09:11:47.997</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>09:11:50.162</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>09:11:50.250</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>09:11:50.342</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="n">
+        <v>2493</v>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="U153" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V153" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="W153" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X153" s="2" t="n">
+        <v>2673</v>
+      </c>
+      <c r="Y153" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="Z153" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB153" s="2" t="inlineStr"/>
+      <c r="AC153" s="2" t="inlineStr"/>
+      <c r="AD153" s="2" t="inlineStr"/>
+      <c r="AE153" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF153" s="2" t="n">
+        <v>8373</v>
+      </c>
+      <c r="AG153" s="2" t="n">
+        <v>352</v>
+      </c>
+      <c r="AH153" s="2" t="n">
+        <v>8725</v>
+      </c>
+      <c r="AI153" s="2" t="n">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2359</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>09:11:55.074</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>09:11:55.106</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>09:11:55.399</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>09:12:03.235</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>09:12:03.317</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>09:12:03.406</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="n">
+        <v>8161</v>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="U154" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V154" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X154" s="2" t="n">
+        <v>8332</v>
+      </c>
+      <c r="Y154" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="Z154" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB154" s="2" t="inlineStr"/>
+      <c r="AC154" s="2" t="inlineStr"/>
+      <c r="AD154" s="2" t="inlineStr"/>
+      <c r="AE154" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF154" s="2" t="n">
+        <v>8373</v>
+      </c>
+      <c r="AG154" s="2" t="n">
+        <v>352</v>
+      </c>
+      <c r="AH154" s="2" t="n">
+        <v>8725</v>
+      </c>
+      <c r="AI154" s="2" t="n">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2360</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>09:12:07.570</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>09:12:07.598</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>09:12:07.913</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>09:12:10.121</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>09:12:10.200</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>09:12:10.281</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="n">
+        <v>2551</v>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="U155" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V155" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X155" s="2" t="n">
+        <v>2711</v>
+      </c>
+      <c r="Y155" s="2" t="inlineStr">
+        <is>
+          <t>2.7s</t>
+        </is>
+      </c>
+      <c r="Z155" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB155" s="2" t="inlineStr"/>
+      <c r="AC155" s="2" t="inlineStr"/>
+      <c r="AD155" s="2" t="inlineStr"/>
+      <c r="AE155" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF155" s="2" t="n">
+        <v>8373</v>
+      </c>
+      <c r="AG155" s="2" t="n">
+        <v>352</v>
+      </c>
+      <c r="AH155" s="2" t="n">
+        <v>8725</v>
+      </c>
+      <c r="AI155" s="2" t="n">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2361</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>09:12:14.429</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>09:12:14.466</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>09:12:14.846</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>09:12:17.910</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>09:12:17.976</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>09:12:18.122</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="n">
+        <v>3481</v>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>3.5s</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U156" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V156" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="W156" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X156" s="2" t="n">
+        <v>3693</v>
+      </c>
+      <c r="Y156" s="2" t="inlineStr">
+        <is>
+          <t>3.7s</t>
+        </is>
+      </c>
+      <c r="Z156" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB156" s="2" t="inlineStr"/>
+      <c r="AC156" s="2" t="inlineStr"/>
+      <c r="AD156" s="2" t="inlineStr"/>
+      <c r="AE156" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF156" s="2" t="n">
+        <v>8373</v>
+      </c>
+      <c r="AG156" s="2" t="n">
+        <v>352</v>
+      </c>
+      <c r="AH156" s="2" t="n">
+        <v>8725</v>
+      </c>
+      <c r="AI156" s="2" t="n">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2362</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>09:12:22.939</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>09:12:22.962</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>09:12:23.295</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>09:12:25.781</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>09:12:25.861</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>09:12:25.936</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="n">
+        <v>2842</v>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>2.8s</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="U157" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V157" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W157" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X157" s="2" t="n">
+        <v>2997</v>
+      </c>
+      <c r="Y157" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="Z157" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB157" s="2" t="inlineStr"/>
+      <c r="AC157" s="2" t="inlineStr"/>
+      <c r="AD157" s="2" t="inlineStr"/>
+      <c r="AE157" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF157" s="2" t="n">
+        <v>8373</v>
+      </c>
+      <c r="AG157" s="2" t="n">
+        <v>352</v>
+      </c>
+      <c r="AH157" s="2" t="n">
+        <v>8725</v>
+      </c>
+      <c r="AI157" s="2" t="n">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2644</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>11:32:11.961</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>11:32:11.988</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>11:32:12.337</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>11:32:18.959</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>11:32:19.042</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>11:32:19.139</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="n">
+        <v>6998</v>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="U158" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V158" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="W158" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X158" s="2" t="n">
+        <v>7178</v>
+      </c>
+      <c r="Y158" s="2" t="inlineStr">
+        <is>
+          <t>7.2s</t>
+        </is>
+      </c>
+      <c r="Z158" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB158" s="2" t="inlineStr"/>
+      <c r="AC158" s="2" t="inlineStr"/>
+      <c r="AD158" s="2" t="inlineStr"/>
+      <c r="AE158" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF158" s="2" t="n">
+        <v>10881</v>
+      </c>
+      <c r="AG158" s="2" t="n">
+        <v>3071</v>
+      </c>
+      <c r="AH158" s="2" t="n">
+        <v>13952</v>
+      </c>
+      <c r="AI158" s="2" t="n">
+        <v>6882</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2645</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>11:32:21.918</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>11:32:21.936</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>11:32:22.213</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>11:32:26.861</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>11:32:26.929</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>11:32:27.004</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="n">
+        <v>4943</v>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="U159" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V159" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X159" s="2" t="n">
+        <v>5086</v>
+      </c>
+      <c r="Y159" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="Z159" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA159" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB159" s="2" t="inlineStr"/>
+      <c r="AC159" s="2" t="inlineStr"/>
+      <c r="AD159" s="2" t="inlineStr"/>
+      <c r="AE159" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF159" s="2" t="n">
+        <v>10881</v>
+      </c>
+      <c r="AG159" s="2" t="n">
+        <v>3071</v>
+      </c>
+      <c r="AH159" s="2" t="n">
+        <v>13952</v>
+      </c>
+      <c r="AI159" s="2" t="n">
+        <v>6882</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2646</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>11:32:30.116</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>11:32:30.137</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>11:32:30.536</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>11:32:40.099</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>11:32:40.282</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>11:32:40.348</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="n">
+        <v>9983</v>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>10.0s</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="U160" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="V160" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="W160" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X160" s="2" t="n">
+        <v>10232</v>
+      </c>
+      <c r="Y160" s="2" t="inlineStr">
+        <is>
+          <t>10.2s</t>
+        </is>
+      </c>
+      <c r="Z160" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB160" s="2" t="inlineStr"/>
+      <c r="AC160" s="2" t="inlineStr"/>
+      <c r="AD160" s="2" t="inlineStr"/>
+      <c r="AE160" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF160" s="2" t="n">
+        <v>10881</v>
+      </c>
+      <c r="AG160" s="2" t="n">
+        <v>3071</v>
+      </c>
+      <c r="AH160" s="2" t="n">
+        <v>13952</v>
+      </c>
+      <c r="AI160" s="2" t="n">
+        <v>6882</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2647</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>11:32:43.271</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>11:32:43.290</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>11:32:43.555</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>11:32:51.215</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>11:32:51.274</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>11:32:51.341</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="n">
+        <v>7944</v>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U161" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V161" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X161" s="2" t="n">
+        <v>8070</v>
+      </c>
+      <c r="Y161" s="2" t="inlineStr">
+        <is>
+          <t>8.1s</t>
+        </is>
+      </c>
+      <c r="Z161" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB161" s="2" t="inlineStr"/>
+      <c r="AC161" s="2" t="inlineStr"/>
+      <c r="AD161" s="2" t="inlineStr"/>
+      <c r="AE161" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF161" s="2" t="n">
+        <v>10881</v>
+      </c>
+      <c r="AG161" s="2" t="n">
+        <v>3071</v>
+      </c>
+      <c r="AH161" s="2" t="n">
+        <v>13952</v>
+      </c>
+      <c r="AI161" s="2" t="n">
+        <v>6882</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2648</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>11:32:54.437</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>11:32:54.456</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>11:32:54.841</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>11:33:05.562</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>11:33:05.648</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>11:33:05.719</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="n">
+        <v>11125</v>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>11.1s</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="U162" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V162" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="W162" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X162" s="2" t="n">
+        <v>11282</v>
+      </c>
+      <c r="Y162" s="2" t="inlineStr">
+        <is>
+          <t>11.3s</t>
+        </is>
+      </c>
+      <c r="Z162" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB162" s="2" t="inlineStr"/>
+      <c r="AC162" s="2" t="inlineStr"/>
+      <c r="AD162" s="2" t="inlineStr"/>
+      <c r="AE162" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF162" s="2" t="n">
+        <v>10881</v>
+      </c>
+      <c r="AG162" s="2" t="n">
+        <v>3071</v>
+      </c>
+      <c r="AH162" s="2" t="n">
+        <v>13952</v>
+      </c>
+      <c r="AI162" s="2" t="n">
+        <v>6882</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2649</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>11:33:08.980</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>11:33:09.001</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>11:33:09.341</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>11:33:15.317</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>11:33:15.386</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>11:33:15.466</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="n">
+        <v>6337</v>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>6.3s</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="U163" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V163" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="W163" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X163" s="2" t="n">
+        <v>6486</v>
+      </c>
+      <c r="Y163" s="2" t="inlineStr">
+        <is>
+          <t>6.5s</t>
+        </is>
+      </c>
+      <c r="Z163" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB163" s="2" t="inlineStr"/>
+      <c r="AC163" s="2" t="inlineStr"/>
+      <c r="AD163" s="2" t="inlineStr"/>
+      <c r="AE163" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF163" s="2" t="n">
+        <v>10881</v>
+      </c>
+      <c r="AG163" s="2" t="n">
+        <v>3071</v>
+      </c>
+      <c r="AH163" s="2" t="n">
+        <v>13952</v>
+      </c>
+      <c r="AI163" s="2" t="n">
+        <v>6882</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2650</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>13:52:17.345</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>13:52:17.364</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>13:52:17.615</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>13:52:20.989</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>13:52:21.120</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>13:52:21.187</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="n">
+        <v>3644</v>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>3.6s</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="U164" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V164" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W164" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X164" s="2" t="n">
+        <v>3842</v>
+      </c>
+      <c r="Y164" s="2" t="inlineStr">
+        <is>
+          <t>3.8s</t>
+        </is>
+      </c>
+      <c r="Z164" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB164" s="2" t="inlineStr"/>
+      <c r="AC164" s="2" t="inlineStr"/>
+      <c r="AD164" s="2" t="inlineStr"/>
+      <c r="AE164" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF164" s="2" t="n">
+        <v>5584</v>
+      </c>
+      <c r="AG164" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="AH164" s="2" t="n">
+        <v>5768</v>
+      </c>
+      <c r="AI164" s="2" t="n">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2651</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>13:52:22.796</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>13:52:22.813</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>13:52:23.041</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>13:52:25.071</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>13:52:25.201</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>13:52:25.268</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="n">
+        <v>2275</v>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="U165" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V165" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W165" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X165" s="2" t="n">
+        <v>2472</v>
+      </c>
+      <c r="Y165" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="Z165" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB165" s="2" t="inlineStr"/>
+      <c r="AC165" s="2" t="inlineStr"/>
+      <c r="AD165" s="2" t="inlineStr"/>
+      <c r="AE165" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF165" s="2" t="n">
+        <v>5584</v>
+      </c>
+      <c r="AG165" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="AH165" s="2" t="n">
+        <v>5768</v>
+      </c>
+      <c r="AI165" s="2" t="n">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2652</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>13:52:27.907</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>13:52:27.927</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>13:52:28.243</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>13:52:30.168</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>13:52:30.245</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>13:52:30.353</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="n">
+        <v>2261</v>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="U166" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V166" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="W166" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X166" s="2" t="n">
+        <v>2446</v>
+      </c>
+      <c r="Y166" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="Z166" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB166" s="2" t="inlineStr"/>
+      <c r="AC166" s="2" t="inlineStr"/>
+      <c r="AD166" s="2" t="inlineStr"/>
+      <c r="AE166" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF166" s="2" t="n">
+        <v>5584</v>
+      </c>
+      <c r="AG166" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="AH166" s="2" t="n">
+        <v>5768</v>
+      </c>
+      <c r="AI166" s="2" t="n">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2653</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Ignacio Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>13:52:32.965</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>13:52:32.981</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>13:52:33.239</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>13:52:35.367</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>13:52:35.431</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>13:52:35.512</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="n">
+        <v>2402</v>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="U167" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V167" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="W167" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X167" s="2" t="n">
+        <v>2547</v>
+      </c>
+      <c r="Y167" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="Z167" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB167" s="2" t="inlineStr"/>
+      <c r="AC167" s="2" t="inlineStr"/>
+      <c r="AD167" s="2" t="inlineStr"/>
+      <c r="AE167" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF167" s="2" t="n">
+        <v>5584</v>
+      </c>
+      <c r="AG167" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="AH167" s="2" t="n">
+        <v>5768</v>
+      </c>
+      <c r="AI167" s="2" t="n">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2363</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>14:14:12.223</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>14:14:12.244</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>14:14:12.535</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>14:14:20.987</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>14:14:21.052</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>14:14:21.125</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="n">
+        <v>8764</v>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>8.8s</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U168" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V168" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X168" s="2" t="n">
+        <v>8902</v>
+      </c>
+      <c r="Y168" s="2" t="inlineStr">
+        <is>
+          <t>8.9s</t>
+        </is>
+      </c>
+      <c r="Z168" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB168" s="2" t="inlineStr"/>
+      <c r="AC168" s="2" t="inlineStr"/>
+      <c r="AD168" s="2" t="inlineStr"/>
+      <c r="AE168" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF168" s="2" t="n">
+        <v>10695</v>
+      </c>
+      <c r="AG168" s="2" t="n">
+        <v>2933</v>
+      </c>
+      <c r="AH168" s="2" t="n">
+        <v>13628</v>
+      </c>
+      <c r="AI168" s="2" t="n">
+        <v>8742</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2364</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>14:14:22.829</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>14:14:22.849</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>14:14:23.092</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>14:14:29.196</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>14:14:29.262</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>14:14:29.359</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="n">
+        <v>6367</v>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>6.4s</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U169" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V169" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X169" s="2" t="n">
+        <v>6530</v>
+      </c>
+      <c r="Y169" s="2" t="inlineStr">
+        <is>
+          <t>6.5s</t>
+        </is>
+      </c>
+      <c r="Z169" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA169" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB169" s="2" t="inlineStr"/>
+      <c r="AC169" s="2" t="inlineStr"/>
+      <c r="AD169" s="2" t="inlineStr"/>
+      <c r="AE169" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF169" s="2" t="n">
+        <v>10695</v>
+      </c>
+      <c r="AG169" s="2" t="n">
+        <v>2933</v>
+      </c>
+      <c r="AH169" s="2" t="n">
+        <v>13628</v>
+      </c>
+      <c r="AI169" s="2" t="n">
+        <v>8742</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2365</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>14:14:31.161</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>14:14:31.182</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>14:14:31.442</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>14:14:50.763</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>14:14:50.813</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>14:14:50.878</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="n">
+        <v>19602</v>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>19.6s</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U170" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V170" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X170" s="2" t="n">
+        <v>19717</v>
+      </c>
+      <c r="Y170" s="2" t="inlineStr">
+        <is>
+          <t>19.7s</t>
+        </is>
+      </c>
+      <c r="Z170" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB170" s="2" t="inlineStr"/>
+      <c r="AC170" s="2" t="inlineStr"/>
+      <c r="AD170" s="2" t="inlineStr"/>
+      <c r="AE170" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF170" s="2" t="n">
+        <v>10695</v>
+      </c>
+      <c r="AG170" s="2" t="n">
+        <v>2933</v>
+      </c>
+      <c r="AH170" s="2" t="n">
+        <v>13628</v>
+      </c>
+      <c r="AI170" s="2" t="n">
+        <v>8742</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2366</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>14:14:52.906</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>14:14:52.928</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>14:14:53.256</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>14:15:00.848</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>14:15:00.928</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>14:15:01.101</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="n">
+        <v>7942</v>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="U171" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V171" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="W171" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X171" s="2" t="n">
+        <v>8195</v>
+      </c>
+      <c r="Y171" s="2" t="inlineStr">
+        <is>
+          <t>8.2s</t>
+        </is>
+      </c>
+      <c r="Z171" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB171" s="2" t="inlineStr"/>
+      <c r="AC171" s="2" t="inlineStr"/>
+      <c r="AD171" s="2" t="inlineStr"/>
+      <c r="AE171" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF171" s="2" t="n">
+        <v>10695</v>
+      </c>
+      <c r="AG171" s="2" t="n">
+        <v>2933</v>
+      </c>
+      <c r="AH171" s="2" t="n">
+        <v>13628</v>
+      </c>
+      <c r="AI171" s="2" t="n">
+        <v>8742</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2367</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>14:15:03.364</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>14:15:03.380</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>14:15:03.633</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>14:15:09.183</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>14:15:09.236</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>14:15:09.310</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="n">
+        <v>5819</v>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>5.8s</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="U172" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V172" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="n">
+        <v>5946</v>
+      </c>
+      <c r="Y172" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="Z172" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB172" s="2" t="inlineStr"/>
+      <c r="AC172" s="2" t="inlineStr"/>
+      <c r="AD172" s="2" t="inlineStr"/>
+      <c r="AE172" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF172" s="2" t="n">
+        <v>10695</v>
+      </c>
+      <c r="AG172" s="2" t="n">
+        <v>2933</v>
+      </c>
+      <c r="AH172" s="2" t="n">
+        <v>13628</v>
+      </c>
+      <c r="AI172" s="2" t="n">
+        <v>8742</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2368</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>14:15:11.497</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>14:15:11.514</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>14:15:11.748</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>14:15:22.063</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>14:15:22.141</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>14:15:22.213</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="n">
+        <v>10566</v>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>10.6s</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="U173" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V173" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="W173" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X173" s="2" t="n">
+        <v>10716</v>
+      </c>
+      <c r="Y173" s="2" t="inlineStr">
+        <is>
+          <t>10.7s</t>
+        </is>
+      </c>
+      <c r="Z173" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB173" s="2" t="inlineStr"/>
+      <c r="AC173" s="2" t="inlineStr"/>
+      <c r="AD173" s="2" t="inlineStr"/>
+      <c r="AE173" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF173" s="2" t="n">
+        <v>10695</v>
+      </c>
+      <c r="AG173" s="2" t="n">
+        <v>2933</v>
+      </c>
+      <c r="AH173" s="2" t="n">
+        <v>13628</v>
+      </c>
+      <c r="AI173" s="2" t="n">
+        <v>8742</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>translationjob749</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>14:27:46.545</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>14:27:46.565</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>14:27:46.881</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>14:27:54.020</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>14:27:54.083</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>14:27:54.150</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="n">
+        <v>7475</v>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U174" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V174" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X174" s="2" t="n">
+        <v>7605</v>
+      </c>
+      <c r="Y174" s="2" t="inlineStr">
+        <is>
+          <t>7.6s</t>
+        </is>
+      </c>
+      <c r="Z174" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB174" s="2" t="inlineStr"/>
+      <c r="AC174" s="2" t="inlineStr"/>
+      <c r="AD174" s="2" t="inlineStr"/>
+      <c r="AE174" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF174" s="2" t="n">
+        <v>12796</v>
+      </c>
+      <c r="AG174" s="2" t="n">
+        <v>3866</v>
+      </c>
+      <c r="AH174" s="2" t="n">
+        <v>16662</v>
+      </c>
+      <c r="AI174" s="2" t="n">
+        <v>10256</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>translationjob750</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>14:27:55.019</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>14:27:55.037</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>14:27:55.314</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>14:28:02.520</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>14:28:02.586</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>14:28:02.670</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="n">
+        <v>7501</v>
+      </c>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="U175" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V175" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="W175" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X175" s="2" t="n">
+        <v>7651</v>
+      </c>
+      <c r="Y175" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="Z175" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB175" s="2" t="inlineStr"/>
+      <c r="AC175" s="2" t="inlineStr"/>
+      <c r="AD175" s="2" t="inlineStr"/>
+      <c r="AE175" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF175" s="2" t="n">
+        <v>12796</v>
+      </c>
+      <c r="AG175" s="2" t="n">
+        <v>3866</v>
+      </c>
+      <c r="AH175" s="2" t="n">
+        <v>16662</v>
+      </c>
+      <c r="AI175" s="2" t="n">
+        <v>10256</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>translationjob751</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>14:28:03.583</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>14:28:03.605</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>14:28:03.843</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>14:28:20.487</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>14:28:20.543</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>14:28:20.610</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="n">
+        <v>16904</v>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>16.9s</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U176" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V176" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W176" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X176" s="2" t="n">
+        <v>17027</v>
+      </c>
+      <c r="Y176" s="2" t="inlineStr">
+        <is>
+          <t>17.0s</t>
+        </is>
+      </c>
+      <c r="Z176" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB176" s="2" t="inlineStr"/>
+      <c r="AC176" s="2" t="inlineStr"/>
+      <c r="AD176" s="2" t="inlineStr"/>
+      <c r="AE176" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF176" s="2" t="n">
+        <v>12796</v>
+      </c>
+      <c r="AG176" s="2" t="n">
+        <v>3866</v>
+      </c>
+      <c r="AH176" s="2" t="n">
+        <v>16662</v>
+      </c>
+      <c r="AI176" s="2" t="n">
+        <v>10256</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>translationjob752</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>14:28:11.929</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>14:28:11.949</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>14:28:12.190</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>14:28:16.816</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>14:28:16.874</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>14:28:16.964</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="n">
+        <v>4887</v>
+      </c>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U177" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V177" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="W177" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X177" s="2" t="n">
+        <v>5035</v>
+      </c>
+      <c r="Y177" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="Z177" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB177" s="2" t="inlineStr"/>
+      <c r="AC177" s="2" t="inlineStr"/>
+      <c r="AD177" s="2" t="inlineStr"/>
+      <c r="AE177" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF177" s="2" t="n">
+        <v>8186</v>
+      </c>
+      <c r="AG177" s="2" t="n">
+        <v>1630</v>
+      </c>
+      <c r="AH177" s="2" t="n">
+        <v>9816</v>
+      </c>
+      <c r="AI177" s="2" t="n">
+        <v>6502</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>translationjob753</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>14:28:17.990</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>14:28:18.023</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>14:28:18.390</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>14:28:25.871</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>14:28:25.930</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>14:28:25.988</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="n">
+        <v>367</v>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="n">
+        <v>7881</v>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>7.9s</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U178" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V178" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W178" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X178" s="2" t="n">
+        <v>7998</v>
+      </c>
+      <c r="Y178" s="2" t="inlineStr">
+        <is>
+          <t>8.0s</t>
+        </is>
+      </c>
+      <c r="Z178" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB178" s="2" t="inlineStr"/>
+      <c r="AC178" s="2" t="inlineStr"/>
+      <c r="AD178" s="2" t="inlineStr"/>
+      <c r="AE178" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF178" s="2" t="n">
+        <v>8186</v>
+      </c>
+      <c r="AG178" s="2" t="n">
+        <v>1630</v>
+      </c>
+      <c r="AH178" s="2" t="n">
+        <v>9816</v>
+      </c>
+      <c r="AI178" s="2" t="n">
+        <v>6502</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>translationjob754</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>14:28:21.582</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>14:28:21.612</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>14:28:21.840</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>14:28:43.715</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>14:28:43.767</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>14:28:43.824</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="n">
+        <v>22133</v>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>22.1s</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U179" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V179" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="W179" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X179" s="2" t="n">
+        <v>22242</v>
+      </c>
+      <c r="Y179" s="2" t="inlineStr">
+        <is>
+          <t>22.2s</t>
+        </is>
+      </c>
+      <c r="Z179" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB179" s="2" t="inlineStr"/>
+      <c r="AC179" s="2" t="inlineStr"/>
+      <c r="AD179" s="2" t="inlineStr"/>
+      <c r="AE179" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF179" s="2" t="n">
+        <v>12796</v>
+      </c>
+      <c r="AG179" s="2" t="n">
+        <v>3866</v>
+      </c>
+      <c r="AH179" s="2" t="n">
+        <v>16662</v>
+      </c>
+      <c r="AI179" s="2" t="n">
+        <v>10256</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>translationjob755</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>14:28:26.893</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>14:28:26.912</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>14:28:27.144</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>14:28:40.393</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>14:28:40.456</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>14:28:40.519</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R180" s="2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>13.5s</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U180" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V180" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W180" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X180" s="2" t="n">
+        <v>13626</v>
+      </c>
+      <c r="Y180" s="2" t="inlineStr">
+        <is>
+          <t>13.6s</t>
+        </is>
+      </c>
+      <c r="Z180" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB180" s="2" t="inlineStr"/>
+      <c r="AC180" s="2" t="inlineStr"/>
+      <c r="AD180" s="2" t="inlineStr"/>
+      <c r="AE180" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF180" s="2" t="n">
+        <v>8186</v>
+      </c>
+      <c r="AG180" s="2" t="n">
+        <v>1630</v>
+      </c>
+      <c r="AH180" s="2" t="n">
+        <v>9816</v>
+      </c>
+      <c r="AI180" s="2" t="n">
+        <v>6502</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>translationjob756</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>14:28:41.324</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>14:28:41.343</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>14:28:41.572</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>14:28:46.016</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>14:28:46.075</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>14:28:46.202</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="n">
+        <v>4692</v>
+      </c>
+      <c r="S181" s="2" t="inlineStr">
+        <is>
+          <t>4.7s</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="U181" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V181" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="W181" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X181" s="2" t="n">
+        <v>4878</v>
+      </c>
+      <c r="Y181" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="Z181" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB181" s="2" t="inlineStr"/>
+      <c r="AC181" s="2" t="inlineStr"/>
+      <c r="AD181" s="2" t="inlineStr"/>
+      <c r="AE181" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF181" s="2" t="n">
+        <v>8186</v>
+      </c>
+      <c r="AG181" s="2" t="n">
+        <v>1630</v>
+      </c>
+      <c r="AH181" s="2" t="n">
+        <v>9816</v>
+      </c>
+      <c r="AI181" s="2" t="n">
+        <v>6502</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>translationjob757</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>14:28:44.700</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>14:28:44.720</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>14:28:45.044</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>14:28:52.225</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>14:28:52.287</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>14:28:52.353</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R182" s="2" t="n">
+        <v>7525</v>
+      </c>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U182" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V182" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="W182" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X182" s="2" t="n">
+        <v>7653</v>
+      </c>
+      <c r="Y182" s="2" t="inlineStr">
+        <is>
+          <t>7.7s</t>
+        </is>
+      </c>
+      <c r="Z182" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB182" s="2" t="inlineStr"/>
+      <c r="AC182" s="2" t="inlineStr"/>
+      <c r="AD182" s="2" t="inlineStr"/>
+      <c r="AE182" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF182" s="2" t="n">
+        <v>12796</v>
+      </c>
+      <c r="AG182" s="2" t="n">
+        <v>3866</v>
+      </c>
+      <c r="AH182" s="2" t="n">
+        <v>16662</v>
+      </c>
+      <c r="AI182" s="2" t="n">
+        <v>10256</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>translationjob758</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>14:28:47.020</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>14:28:47.038</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>14:28:47.287</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>14:28:52.562</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>14:28:52.624</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>14:28:52.699</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="n">
+        <v>5542</v>
+      </c>
+      <c r="S183" s="2" t="inlineStr">
+        <is>
+          <t>5.5s</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U183" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V183" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W183" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X183" s="2" t="n">
+        <v>5679</v>
+      </c>
+      <c r="Y183" s="2" t="inlineStr">
+        <is>
+          <t>5.7s</t>
+        </is>
+      </c>
+      <c r="Z183" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB183" s="2" t="inlineStr"/>
+      <c r="AC183" s="2" t="inlineStr"/>
+      <c r="AD183" s="2" t="inlineStr"/>
+      <c r="AE183" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF183" s="2" t="n">
+        <v>8186</v>
+      </c>
+      <c r="AG183" s="2" t="n">
+        <v>1630</v>
+      </c>
+      <c r="AH183" s="2" t="n">
+        <v>9816</v>
+      </c>
+      <c r="AI183" s="2" t="n">
+        <v>6502</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>translationjob759</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Raquel Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>14:28:53.506</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>14:28:53.509</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>14:28:54.292</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>14:29:08.957</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>14:29:09.040</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>14:29:09.175</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="n">
+        <v>15451</v>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>15.5s</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="U184" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V184" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="W184" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X184" s="2" t="n">
+        <v>15669</v>
+      </c>
+      <c r="Y184" s="2" t="inlineStr">
+        <is>
+          <t>15.7s</t>
+        </is>
+      </c>
+      <c r="Z184" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:2, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB184" s="2" t="inlineStr"/>
+      <c r="AC184" s="2" t="inlineStr"/>
+      <c r="AD184" s="2" t="inlineStr"/>
+      <c r="AE184" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF184" s="2" t="n">
+        <v>8186</v>
+      </c>
+      <c r="AG184" s="2" t="n">
+        <v>1630</v>
+      </c>
+      <c r="AH184" s="2" t="n">
+        <v>9816</v>
+      </c>
+      <c r="AI184" s="2" t="n">
+        <v>6502</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>translationjob2369</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Nathalie Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>14:49:45.400</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>14:49:45.434</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>14:49:45.680</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>14:49:48.441</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>14:49:48.503</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>14:49:48.562</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="n">
+        <v>3041</v>
+      </c>
+      <c r="S185" s="2" t="inlineStr">
+        <is>
+          <t>3.0s</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U185" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V185" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="W185" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X185" s="2" t="n">
+        <v>3162</v>
+      </c>
+      <c r="Y185" s="2" t="inlineStr">
+        <is>
+          <t>3.2s</t>
+        </is>
+      </c>
+      <c r="Z185" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA185" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB185" s="2" t="inlineStr"/>
+      <c r="AC185" s="2" t="inlineStr"/>
+      <c r="AD185" s="2" t="inlineStr"/>
+      <c r="AE185" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF185" s="2" t="n">
+        <v>1418</v>
+      </c>
+      <c r="AG185" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH185" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="AI185" s="2" t="n">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1523</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>17:51:51.980</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>17:51:52.000</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>17:51:52.257</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>17:51:59.375</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>17:51:59.425</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>17:51:59.498</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R186" s="2" t="n">
+        <v>7395</v>
+      </c>
+      <c r="S186" s="2" t="inlineStr">
+        <is>
+          <t>7.4s</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U186" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V186" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="W186" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X186" s="2" t="n">
+        <v>7518</v>
+      </c>
+      <c r="Y186" s="2" t="inlineStr">
+        <is>
+          <t>7.5s</t>
+        </is>
+      </c>
+      <c r="Z186" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB186" s="2" t="inlineStr"/>
+      <c r="AC186" s="2" t="inlineStr"/>
+      <c r="AD186" s="2" t="inlineStr"/>
+      <c r="AE186" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF186" s="2" t="n">
+        <v>11025</v>
+      </c>
+      <c r="AG186" s="2" t="n">
+        <v>3201</v>
+      </c>
+      <c r="AH186" s="2" t="n">
+        <v>14226</v>
+      </c>
+      <c r="AI186" s="2" t="n">
+        <v>7062</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1524</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>17:52:01.030</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>17:52:01.048</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>17:52:01.268</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>17:52:06.121</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>17:52:06.181</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>17:52:06.239</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R187" s="2" t="n">
+        <v>5091</v>
+      </c>
+      <c r="S187" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="T187" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U187" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V187" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W187" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X187" s="2" t="n">
+        <v>5209</v>
+      </c>
+      <c r="Y187" s="2" t="inlineStr">
+        <is>
+          <t>5.2s</t>
+        </is>
+      </c>
+      <c r="Z187" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA187" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB187" s="2" t="inlineStr"/>
+      <c r="AC187" s="2" t="inlineStr"/>
+      <c r="AD187" s="2" t="inlineStr"/>
+      <c r="AE187" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF187" s="2" t="n">
+        <v>11025</v>
+      </c>
+      <c r="AG187" s="2" t="n">
+        <v>3201</v>
+      </c>
+      <c r="AH187" s="2" t="n">
+        <v>14226</v>
+      </c>
+      <c r="AI187" s="2" t="n">
+        <v>7062</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1525</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>17:52:07.593</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>17:52:07.617</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>17:52:07.865</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>17:52:16.544</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>17:52:16.605</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>17:52:16.684</t>
+        </is>
+      </c>
+      <c r="P188" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="Q188" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R188" s="2" t="n">
+        <v>8951</v>
+      </c>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>9.0s</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U188" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V188" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="W188" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X188" s="2" t="n">
+        <v>9091</v>
+      </c>
+      <c r="Y188" s="2" t="inlineStr">
+        <is>
+          <t>9.1s</t>
+        </is>
+      </c>
+      <c r="Z188" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA188" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB188" s="2" t="inlineStr"/>
+      <c r="AC188" s="2" t="inlineStr"/>
+      <c r="AD188" s="2" t="inlineStr"/>
+      <c r="AE188" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF188" s="2" t="n">
+        <v>11025</v>
+      </c>
+      <c r="AG188" s="2" t="n">
+        <v>3201</v>
+      </c>
+      <c r="AH188" s="2" t="n">
+        <v>14226</v>
+      </c>
+      <c r="AI188" s="2" t="n">
+        <v>7062</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1526</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>17:52:18.156</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>17:52:18.175</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>17:52:18.418</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>17:52:27.826</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>17:52:27.875</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t>17:52:27.993</t>
+        </is>
+      </c>
+      <c r="P189" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R189" s="2" t="n">
+        <v>9670</v>
+      </c>
+      <c r="S189" s="2" t="inlineStr">
+        <is>
+          <t>9.7s</t>
+        </is>
+      </c>
+      <c r="T189" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U189" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V189" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="W189" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X189" s="2" t="n">
+        <v>9837</v>
+      </c>
+      <c r="Y189" s="2" t="inlineStr">
+        <is>
+          <t>9.8s</t>
+        </is>
+      </c>
+      <c r="Z189" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA189" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB189" s="2" t="inlineStr"/>
+      <c r="AC189" s="2" t="inlineStr"/>
+      <c r="AD189" s="2" t="inlineStr"/>
+      <c r="AE189" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF189" s="2" t="n">
+        <v>11025</v>
+      </c>
+      <c r="AG189" s="2" t="n">
+        <v>3201</v>
+      </c>
+      <c r="AH189" s="2" t="n">
+        <v>14226</v>
+      </c>
+      <c r="AI189" s="2" t="n">
+        <v>7062</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1527</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>17:52:29.315</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>17:52:29.333</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>17:52:29.619</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>17:52:34.358</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>17:52:34.416</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>17:52:34.475</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R190" s="2" t="n">
+        <v>5043</v>
+      </c>
+      <c r="S190" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U190" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V190" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="W190" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X190" s="2" t="n">
+        <v>5160</v>
+      </c>
+      <c r="Y190" s="2" t="inlineStr">
+        <is>
+          <t>5.2s</t>
+        </is>
+      </c>
+      <c r="Z190" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB190" s="2" t="inlineStr"/>
+      <c r="AC190" s="2" t="inlineStr"/>
+      <c r="AD190" s="2" t="inlineStr"/>
+      <c r="AE190" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF190" s="2" t="n">
+        <v>11025</v>
+      </c>
+      <c r="AG190" s="2" t="n">
+        <v>3201</v>
+      </c>
+      <c r="AH190" s="2" t="n">
+        <v>14226</v>
+      </c>
+      <c r="AI190" s="2" t="n">
+        <v>7062</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1528</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>17:52:36.116</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>17:52:36.132</t>
+        </is>
+      </c>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>17:52:36.353</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>17:52:47.587</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>17:52:47.658</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>17:52:47.711</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="n">
+        <v>11471</v>
+      </c>
+      <c r="S191" s="2" t="inlineStr">
+        <is>
+          <t>11.5s</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="U191" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V191" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="W191" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X191" s="2" t="n">
+        <v>11595</v>
+      </c>
+      <c r="Y191" s="2" t="inlineStr">
+        <is>
+          <t>11.6s</t>
+        </is>
+      </c>
+      <c r="Z191" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA191" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB191" s="2" t="inlineStr"/>
+      <c r="AC191" s="2" t="inlineStr"/>
+      <c r="AD191" s="2" t="inlineStr"/>
+      <c r="AE191" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF191" s="2" t="n">
+        <v>11025</v>
+      </c>
+      <c r="AG191" s="2" t="n">
+        <v>3201</v>
+      </c>
+      <c r="AH191" s="2" t="n">
+        <v>14226</v>
+      </c>
+      <c r="AI191" s="2" t="n">
+        <v>7062</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1529</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>19:24:54.526</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>19:24:54.541</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>19:24:54.737</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>19:24:56.928</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>19:24:56.970</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>19:24:57.028</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R192" s="2" t="n">
+        <v>2402</v>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U192" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V192" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W192" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X192" s="2" t="n">
+        <v>2502</v>
+      </c>
+      <c r="Y192" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="Z192" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA192" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB192" s="2" t="inlineStr"/>
+      <c r="AC192" s="2" t="inlineStr"/>
+      <c r="AD192" s="2" t="inlineStr"/>
+      <c r="AE192" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF192" s="2" t="n">
+        <v>8271</v>
+      </c>
+      <c r="AG192" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AH192" s="2" t="n">
+        <v>8501</v>
+      </c>
+      <c r="AI192" s="2" t="n">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1530</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>19:24:58.256</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>19:24:58.269</t>
+        </is>
+      </c>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>19:24:58.468</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr">
+        <is>
+          <t>19:25:00.747</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>19:25:00.807</t>
+        </is>
+      </c>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>19:25:00.864</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R193" s="2" t="n">
+        <v>2491</v>
+      </c>
+      <c r="S193" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U193" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V193" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="W193" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X193" s="2" t="n">
+        <v>2608</v>
+      </c>
+      <c r="Y193" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="Z193" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA193" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB193" s="2" t="inlineStr"/>
+      <c r="AC193" s="2" t="inlineStr"/>
+      <c r="AD193" s="2" t="inlineStr"/>
+      <c r="AE193" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF193" s="2" t="n">
+        <v>8271</v>
+      </c>
+      <c r="AG193" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AH193" s="2" t="n">
+        <v>8501</v>
+      </c>
+      <c r="AI193" s="2" t="n">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1531</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>19:25:02.102</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>19:25:02.117</t>
+        </is>
+      </c>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>19:25:02.281</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
+          <t>19:25:04.654</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>19:25:04.702</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>19:25:04.747</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="n">
+        <v>2552</v>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U194" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V194" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="W194" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X194" s="2" t="n">
+        <v>2645</v>
+      </c>
+      <c r="Y194" s="2" t="inlineStr">
+        <is>
+          <t>2.6s</t>
+        </is>
+      </c>
+      <c r="Z194" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA194" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB194" s="2" t="inlineStr"/>
+      <c r="AC194" s="2" t="inlineStr"/>
+      <c r="AD194" s="2" t="inlineStr"/>
+      <c r="AE194" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF194" s="2" t="n">
+        <v>8271</v>
+      </c>
+      <c r="AG194" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AH194" s="2" t="n">
+        <v>8501</v>
+      </c>
+      <c r="AI194" s="2" t="n">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1532</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>19:25:05.786</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>19:25:05.802</t>
+        </is>
+      </c>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>19:25:05.973</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
+          <t>19:25:07.720</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>19:25:07.756</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>19:25:07.804</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R195" s="2" t="n">
+        <v>1934</v>
+      </c>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
+          <t>1.9s</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="U195" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V195" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="W195" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X195" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="Y195" s="2" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="Z195" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA195" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB195" s="2" t="inlineStr"/>
+      <c r="AC195" s="2" t="inlineStr"/>
+      <c r="AD195" s="2" t="inlineStr"/>
+      <c r="AE195" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF195" s="2" t="n">
+        <v>8271</v>
+      </c>
+      <c r="AG195" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AH195" s="2" t="n">
+        <v>8501</v>
+      </c>
+      <c r="AI195" s="2" t="n">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1533</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>19:25:08.949</t>
+        </is>
+      </c>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>19:25:08.963</t>
+        </is>
+      </c>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>19:25:09.166</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr">
+        <is>
+          <t>19:25:11.153</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>19:25:11.190</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>19:25:11.298</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R196" s="2" t="n">
+        <v>2204</v>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>2.2s</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="U196" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V196" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="W196" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X196" s="2" t="n">
+        <v>2349</v>
+      </c>
+      <c r="Y196" s="2" t="inlineStr">
+        <is>
+          <t>2.3s</t>
+        </is>
+      </c>
+      <c r="Z196" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA196" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB196" s="2" t="inlineStr"/>
+      <c r="AC196" s="2" t="inlineStr"/>
+      <c r="AD196" s="2" t="inlineStr"/>
+      <c r="AE196" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF196" s="2" t="n">
+        <v>8271</v>
+      </c>
+      <c r="AG196" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AH196" s="2" t="n">
+        <v>8501</v>
+      </c>
+      <c r="AI196" s="2" t="n">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1534</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Gonzalo Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>19:25:12.470</t>
+        </is>
+      </c>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>19:25:12.484</t>
+        </is>
+      </c>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>19:25:12.743</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>19:25:14.896</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>19:25:14.948</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>19:25:14.999</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R197" s="2" t="n">
+        <v>2426</v>
+      </c>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>2.4s</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U197" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V197" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="W197" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X197" s="2" t="n">
+        <v>2529</v>
+      </c>
+      <c r="Y197" s="2" t="inlineStr">
+        <is>
+          <t>2.5s</t>
+        </is>
+      </c>
+      <c r="Z197" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA197" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB197" s="2" t="inlineStr"/>
+      <c r="AC197" s="2" t="inlineStr"/>
+      <c r="AD197" s="2" t="inlineStr"/>
+      <c r="AE197" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF197" s="2" t="n">
+        <v>8271</v>
+      </c>
+      <c r="AG197" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AH197" s="2" t="n">
+        <v>8501</v>
+      </c>
+      <c r="AI197" s="2" t="n">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1423</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>23:00:06.947</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>23:00:06.970</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>23:00:07.198</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
+          <t>23:00:12.811</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>23:00:12.869</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>23:00:12.926</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="n">
+        <v>5864</v>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>5.9s</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="U198" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V198" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="W198" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X198" s="2" t="n">
+        <v>5979</v>
+      </c>
+      <c r="Y198" s="2" t="inlineStr">
+        <is>
+          <t>6.0s</t>
+        </is>
+      </c>
+      <c r="Z198" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA198" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB198" s="2" t="inlineStr"/>
+      <c r="AC198" s="2" t="inlineStr"/>
+      <c r="AD198" s="2" t="inlineStr"/>
+      <c r="AE198" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF198" s="2" t="n">
+        <v>10845</v>
+      </c>
+      <c r="AG198" s="2" t="n">
+        <v>3014</v>
+      </c>
+      <c r="AH198" s="2" t="n">
+        <v>13859</v>
+      </c>
+      <c r="AI198" s="2" t="n">
+        <v>5009</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1424</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>23:00:13.776</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>23:00:13.797</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>23:00:13.979</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
+          <t>23:00:18.795</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>23:00:18.839</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>23:00:18.889</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R199" s="2" t="n">
+        <v>5019</v>
+      </c>
+      <c r="S199" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U199" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V199" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="W199" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X199" s="2" t="n">
+        <v>5113</v>
+      </c>
+      <c r="Y199" s="2" t="inlineStr">
+        <is>
+          <t>5.1s</t>
+        </is>
+      </c>
+      <c r="Z199" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA199" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB199" s="2" t="inlineStr"/>
+      <c r="AC199" s="2" t="inlineStr"/>
+      <c r="AD199" s="2" t="inlineStr"/>
+      <c r="AE199" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF199" s="2" t="n">
+        <v>10845</v>
+      </c>
+      <c r="AG199" s="2" t="n">
+        <v>3014</v>
+      </c>
+      <c r="AH199" s="2" t="n">
+        <v>13859</v>
+      </c>
+      <c r="AI199" s="2" t="n">
+        <v>5009</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1425</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>23:00:19.766</t>
+        </is>
+      </c>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>23:00:19.785</t>
+        </is>
+      </c>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>23:00:19.946</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>23:00:26.978</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>23:00:27.045</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>23:00:27.100</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R200" s="2" t="n">
+        <v>7212</v>
+      </c>
+      <c r="S200" s="2" t="inlineStr">
+        <is>
+          <t>7.2s</t>
+        </is>
+      </c>
+      <c r="T200" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="U200" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V200" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W200" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X200" s="2" t="n">
+        <v>7334</v>
+      </c>
+      <c r="Y200" s="2" t="inlineStr">
+        <is>
+          <t>7.3s</t>
+        </is>
+      </c>
+      <c r="Z200" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA200" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB200" s="2" t="inlineStr"/>
+      <c r="AC200" s="2" t="inlineStr"/>
+      <c r="AD200" s="2" t="inlineStr"/>
+      <c r="AE200" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF200" s="2" t="n">
+        <v>10845</v>
+      </c>
+      <c r="AG200" s="2" t="n">
+        <v>3014</v>
+      </c>
+      <c r="AH200" s="2" t="n">
+        <v>13859</v>
+      </c>
+      <c r="AI200" s="2" t="n">
+        <v>5009</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1426</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>23:00:28.177</t>
+        </is>
+      </c>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>23:00:28.195</t>
+        </is>
+      </c>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>23:00:28.347</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>23:00:33.102</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>23:00:33.152</t>
+        </is>
+      </c>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>23:00:33.202</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R201" s="2" t="n">
+        <v>4925</v>
+      </c>
+      <c r="S201" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="T201" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U201" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V201" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="W201" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X201" s="2" t="n">
+        <v>5025</v>
+      </c>
+      <c r="Y201" s="2" t="inlineStr">
+        <is>
+          <t>5.0s</t>
+        </is>
+      </c>
+      <c r="Z201" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA201" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB201" s="2" t="inlineStr"/>
+      <c r="AC201" s="2" t="inlineStr"/>
+      <c r="AD201" s="2" t="inlineStr"/>
+      <c r="AE201" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF201" s="2" t="n">
+        <v>10845</v>
+      </c>
+      <c r="AG201" s="2" t="n">
+        <v>3014</v>
+      </c>
+      <c r="AH201" s="2" t="n">
+        <v>13859</v>
+      </c>
+      <c r="AI201" s="2" t="n">
+        <v>5009</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1427</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>23:00:34.107</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t>23:00:34.122</t>
+        </is>
+      </c>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>23:00:34.298</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t>23:00:38.931</t>
+        </is>
+      </c>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>23:00:38.973</t>
+        </is>
+      </c>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>23:00:39.034</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R202" s="2" t="n">
+        <v>4824</v>
+      </c>
+      <c r="S202" s="2" t="inlineStr">
+        <is>
+          <t>4.8s</t>
+        </is>
+      </c>
+      <c r="T202" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="U202" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V202" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="W202" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X202" s="2" t="n">
+        <v>4927</v>
+      </c>
+      <c r="Y202" s="2" t="inlineStr">
+        <is>
+          <t>4.9s</t>
+        </is>
+      </c>
+      <c r="Z202" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA202" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB202" s="2" t="inlineStr"/>
+      <c r="AC202" s="2" t="inlineStr"/>
+      <c r="AD202" s="2" t="inlineStr"/>
+      <c r="AE202" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF202" s="2" t="n">
+        <v>10845</v>
+      </c>
+      <c r="AG202" s="2" t="n">
+        <v>3014</v>
+      </c>
+      <c r="AH202" s="2" t="n">
+        <v>13859</v>
+      </c>
+      <c r="AI202" s="2" t="n">
+        <v>5009</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1428</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>23:00:40.091</t>
+        </is>
+      </c>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t>23:00:40.111</t>
+        </is>
+      </c>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>23:00:40.289</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
+          <t>23:00:46.780</t>
+        </is>
+      </c>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t>23:00:46.821</t>
+        </is>
+      </c>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>23:00:46.868</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="n">
+        <v>6689</v>
+      </c>
+      <c r="S203" s="2" t="inlineStr">
+        <is>
+          <t>6.7s</t>
+        </is>
+      </c>
+      <c r="T203" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U203" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V203" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="W203" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="X203" s="2" t="n">
+        <v>6777</v>
+      </c>
+      <c r="Y203" s="2" t="inlineStr">
+        <is>
+          <t>6.8s</t>
+        </is>
+      </c>
+      <c r="Z203" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:0, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA203" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB203" s="2" t="inlineStr"/>
+      <c r="AC203" s="2" t="inlineStr"/>
+      <c r="AD203" s="2" t="inlineStr"/>
+      <c r="AE203" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF203" s="2" t="n">
+        <v>10845</v>
+      </c>
+      <c r="AG203" s="2" t="n">
+        <v>3014</v>
+      </c>
+      <c r="AH203" s="2" t="n">
+        <v>13859</v>
+      </c>
+      <c r="AI203" s="2" t="n">
+        <v>5009</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1429</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>DE-DE</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>23:12:43.757</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
+          <t>23:12:43.776</t>
+        </is>
+      </c>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>23:12:44.238</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t>23:12:50.505</t>
+        </is>
+      </c>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>23:12:50.560</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>23:12:50.723</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="n">
+        <v>6748</v>
+      </c>
+      <c r="S204" s="2" t="inlineStr">
+        <is>
+          <t>6.7s</t>
+        </is>
+      </c>
+      <c r="T204" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="U204" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V204" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="W204" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X204" s="2" t="n">
+        <v>6966</v>
+      </c>
+      <c r="Y204" s="2" t="inlineStr">
+        <is>
+          <t>7.0s</t>
+        </is>
+      </c>
+      <c r="Z204" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA204" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB204" s="2" t="inlineStr"/>
+      <c r="AC204" s="2" t="inlineStr"/>
+      <c r="AD204" s="2" t="inlineStr"/>
+      <c r="AE204" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF204" s="2" t="n">
+        <v>12243</v>
+      </c>
+      <c r="AG204" s="2" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AH204" s="2" t="n">
+        <v>16690</v>
+      </c>
+      <c r="AI204" s="2" t="n">
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1430</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>PT-PT</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>23:12:51.552</t>
+        </is>
+      </c>
+      <c r="K205" s="2" t="inlineStr">
+        <is>
+          <t>23:12:51.573</t>
+        </is>
+      </c>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>23:12:52.113</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr">
+        <is>
+          <t>23:12:58.102</t>
+        </is>
+      </c>
+      <c r="N205" s="2" t="inlineStr">
+        <is>
+          <t>23:12:58.164</t>
+        </is>
+      </c>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>23:12:58.407</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R205" s="2" t="n">
+        <v>6550</v>
+      </c>
+      <c r="S205" s="2" t="inlineStr">
+        <is>
+          <t>6.5s</t>
+        </is>
+      </c>
+      <c r="T205" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U205" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V205" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="W205" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X205" s="2" t="n">
+        <v>6855</v>
+      </c>
+      <c r="Y205" s="2" t="inlineStr">
+        <is>
+          <t>6.9s</t>
+        </is>
+      </c>
+      <c r="Z205" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA205" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB205" s="2" t="inlineStr"/>
+      <c r="AC205" s="2" t="inlineStr"/>
+      <c r="AD205" s="2" t="inlineStr"/>
+      <c r="AE205" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF205" s="2" t="n">
+        <v>12243</v>
+      </c>
+      <c r="AG205" s="2" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AH205" s="2" t="n">
+        <v>16690</v>
+      </c>
+      <c r="AI205" s="2" t="n">
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1431</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>EN-US</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>23:12:59.402</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
+          <t>23:12:59.421</t>
+        </is>
+      </c>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>23:12:59.765</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>23:13:07.693</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>23:13:07.753</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>23:13:07.942</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>0.3s</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="n">
+        <v>8291</v>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>8.3s</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U206" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V206" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="W206" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X206" s="2" t="n">
+        <v>8540</v>
+      </c>
+      <c r="Y206" s="2" t="inlineStr">
+        <is>
+          <t>8.5s</t>
+        </is>
+      </c>
+      <c r="Z206" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA206" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB206" s="2" t="inlineStr"/>
+      <c r="AC206" s="2" t="inlineStr"/>
+      <c r="AD206" s="2" t="inlineStr"/>
+      <c r="AE206" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF206" s="2" t="n">
+        <v>12243</v>
+      </c>
+      <c r="AG206" s="2" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AH206" s="2" t="n">
+        <v>16690</v>
+      </c>
+      <c r="AI206" s="2" t="n">
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1432</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>AR-AE</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>23:13:08.960</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr">
+        <is>
+          <t>23:13:08.979</t>
+        </is>
+      </c>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>23:13:09.492</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>23:13:17.536</t>
+        </is>
+      </c>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>23:13:17.597</t>
+        </is>
+      </c>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>23:13:17.788</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="n">
+        <v>513</v>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="n">
+        <v>8576</v>
+      </c>
+      <c r="S207" s="2" t="inlineStr">
+        <is>
+          <t>8.6s</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="U207" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V207" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="W207" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X207" s="2" t="n">
+        <v>8828</v>
+      </c>
+      <c r="Y207" s="2" t="inlineStr">
+        <is>
+          <t>8.8s</t>
+        </is>
+      </c>
+      <c r="Z207" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA207" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB207" s="2" t="inlineStr"/>
+      <c r="AC207" s="2" t="inlineStr"/>
+      <c r="AD207" s="2" t="inlineStr"/>
+      <c r="AE207" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF207" s="2" t="n">
+        <v>12243</v>
+      </c>
+      <c r="AG207" s="2" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AH207" s="2" t="n">
+        <v>16690</v>
+      </c>
+      <c r="AI207" s="2" t="n">
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1433</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>FR-FR</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>23:13:18.990</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>23:13:19.017</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>23:13:19.544</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>23:13:25.887</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>23:13:25.936</t>
+        </is>
+      </c>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>23:13:26.084</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="n">
+        <v>527</v>
+      </c>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="R208" s="2" t="n">
+        <v>6897</v>
+      </c>
+      <c r="S208" s="2" t="inlineStr">
+        <is>
+          <t>6.9s</t>
+        </is>
+      </c>
+      <c r="T208" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="U208" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="V208" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="W208" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="X208" s="2" t="n">
+        <v>7094</v>
+      </c>
+      <c r="Y208" s="2" t="inlineStr">
+        <is>
+          <t>7.1s</t>
+        </is>
+      </c>
+      <c r="Z208" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA208" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB208" s="2" t="inlineStr"/>
+      <c r="AC208" s="2" t="inlineStr"/>
+      <c r="AD208" s="2" t="inlineStr"/>
+      <c r="AE208" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF208" s="2" t="n">
+        <v>12243</v>
+      </c>
+      <c r="AG208" s="2" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AH208" s="2" t="n">
+        <v>16690</v>
+      </c>
+      <c r="AI208" s="2" t="n">
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>translationjob1434</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Ai Translation Project</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>JA-JP</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>es_es</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>rmcf-ai-translatorion-connector</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>MACHINE_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>23:13:27.331</t>
+        </is>
+      </c>
+      <c r="K209" s="2" t="inlineStr">
+        <is>
+          <t>23:13:27.350</t>
+        </is>
+      </c>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>23:13:27.797</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>23:13:38.524</t>
+        </is>
+      </c>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>23:13:38.587</t>
+        </is>
+      </c>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>23:13:38.765</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="n">
+        <v>447</v>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>0.4s</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="n">
+        <v>11193</v>
+      </c>
+      <c r="S209" s="2" t="inlineStr">
+        <is>
+          <t>11.2s</t>
+        </is>
+      </c>
+      <c r="T209" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U209" s="2" t="inlineStr">
+        <is>
+          <t>0.1s</t>
+        </is>
+      </c>
+      <c r="V209" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="W209" s="2" t="inlineStr">
+        <is>
+          <t>0.2s</t>
+        </is>
+      </c>
+      <c r="X209" s="2" t="n">
+        <v>11434</v>
+      </c>
+      <c r="Y209" s="2" t="inlineStr">
+        <is>
+          <t>11.4s</t>
+        </is>
+      </c>
+      <c r="Z209" s="2" t="inlineStr">
+        <is>
+          <t>page:0, asset:1, contentFragment:1, i18nComponentStringDict:0, assetMetaData:0, tagMetadata:0, tag:0</t>
+        </is>
+      </c>
+      <c r="AA209" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB209" s="2" t="inlineStr"/>
+      <c r="AC209" s="2" t="inlineStr"/>
+      <c r="AD209" s="2" t="inlineStr"/>
+      <c r="AE209" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF209" s="2" t="n">
+        <v>12243</v>
+      </c>
+      <c r="AG209" s="2" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AH209" s="2" t="n">
+        <v>16690</v>
+      </c>
+      <c r="AI209" s="2" t="n">
+        <v>6960</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AI150"/>
+  <autoFilter ref="A1:AI209"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21468,7 +29787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -21663,6 +29982,58 @@
         <v>1929926</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>7.2s</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>2.0s</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>22.2s</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>335</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>574108</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>135084</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>709192</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21674,12 +30045,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21698,6 +30070,11 @@
           <t>2026-10-25</t>
         </is>
       </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -21711,6 +30088,9 @@
       <c r="C2" s="6" t="n">
         <v>52949</v>
       </c>
+      <c r="D2" s="6" t="n">
+        <v>25638</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -21724,6 +30104,9 @@
       <c r="C3" s="5" t="n">
         <v>68</v>
       </c>
+      <c r="D3" s="5" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -21737,6 +30120,9 @@
       <c r="C4" s="5" t="n">
         <v>3</v>
       </c>
+      <c r="D4" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -21750,6 +30136,9 @@
       <c r="C5" s="5" t="n">
         <v>79</v>
       </c>
+      <c r="D5" s="5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -21763,6 +30152,9 @@
       <c r="C6" s="6" t="n">
         <v>137</v>
       </c>
+      <c r="D6" s="6" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -21776,6 +30168,9 @@
       <c r="C7" s="6" t="n">
         <v>685</v>
       </c>
+      <c r="D7" s="6" t="n">
+        <v>741</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -21789,6 +30184,9 @@
       <c r="C8" s="6" t="n">
         <v>180</v>
       </c>
+      <c r="D8" s="6" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -21802,6 +30200,9 @@
       <c r="C9" s="6" t="n">
         <v>187</v>
       </c>
+      <c r="D9" s="6" t="n">
+        <v>217</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -21815,6 +30216,9 @@
       <c r="C10" s="6" t="n">
         <v>130402</v>
       </c>
+      <c r="D10" s="6" t="n">
+        <v>133140</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -21828,6 +30232,9 @@
       <c r="C11" s="6" t="n">
         <v>32441</v>
       </c>
+      <c r="D11" s="6" t="n">
+        <v>58995</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -21841,6 +30248,9 @@
       <c r="C12" s="6" t="n">
         <v>848</v>
       </c>
+      <c r="D12" s="6" t="n">
+        <v>538</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -21854,6 +30264,9 @@
       <c r="C13" s="6" t="n">
         <v>1608</v>
       </c>
+      <c r="D13" s="6" t="n">
+        <v>1390</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -21867,6 +30280,9 @@
       <c r="C14" s="6" t="n">
         <v>5955</v>
       </c>
+      <c r="D14" s="6" t="n">
+        <v>5391</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -21879,6 +30295,9 @@
       </c>
       <c r="C15" s="6" t="n">
         <v>1138</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1250</v>
       </c>
     </row>
   </sheetData>
@@ -21892,7 +30311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21991,6 +30410,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1030</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
